--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="437">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -951,13 +951,20 @@
   </si>
   <si>
     <t>1、.\run_distributed_v2.ps1 -Mode local -WorkerCount 4 -Headless -Users 500 -SpawnRate 10 -RunTime 2m -OnlySummary
-2、.\run_distributed_v2.ps1 -Mode local -WorkerCount 2 -Headless -Users 500 -SpawnRate 10 -RunTime 15m30s -ResetStats -OnlySummary -CsvPrefix result\single_list_lite_u500_r10 -HtmlReport result\single_list_lite_u500_r10.html</t>
+2、.\run_distributed_v2.ps1 -Mode local -WorkerCount 4 -Headless -Users 500 -SpawnRate 10 -RunTime 15m30s -ResetStats -OnlySummary -CsvPrefix result\single_list_lite_u500_r10 -HtmlReport result\single_list_lite_u500_r10.html</t>
   </si>
   <si>
     <t>R04</t>
   </si>
   <si>
     <t>单接口-冲击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预热：
+master：窗口1、.\run_distributed_v2.ps1 -Mode master -WebPort 8089
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 0 -TotalWorkerCount 3 -TokenFile D:\ckj_locust\user_token.txt
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 2 -TotalWorkerCount 3 -TokenFile C:\ckj_locust\user_token.txt
+</t>
   </si>
   <si>
     <t>W01</t>
@@ -2084,7 +2091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2110,6 +2117,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2716,6 +2726,174 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>128905</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>1219200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>669925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="图片 14"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23512780" y="6127750"/>
+          <a:ext cx="1090295" cy="536575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>1512570</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>2124075</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>724535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="图片 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24896445" y="6146800"/>
+          <a:ext cx="611505" cy="572135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>825500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>1181100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1334135</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="图片 16"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23834725" y="6819900"/>
+          <a:ext cx="730250" cy="508635"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>1337945</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>967740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>2459990</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1539240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="图片 18"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24721820" y="6962140"/>
+          <a:ext cx="1122045" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3007,237 +3185,237 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18" style="19" customWidth="1"/>
-    <col min="2" max="2" width="34" style="19" customWidth="1"/>
-    <col min="3" max="3" width="42" style="19" customWidth="1"/>
-    <col min="4" max="4" width="14" style="19" customWidth="1"/>
-    <col min="5" max="5" width="22.75" style="19" customWidth="1"/>
-    <col min="6" max="6" width="25.25" style="19" customWidth="1"/>
-    <col min="7" max="7" width="14" style="19" customWidth="1"/>
-    <col min="8" max="8" width="30" style="19" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="18" style="20" customWidth="1"/>
+    <col min="2" max="2" width="34" style="20" customWidth="1"/>
+    <col min="3" max="3" width="42" style="20" customWidth="1"/>
+    <col min="4" max="4" width="14" style="20" customWidth="1"/>
+    <col min="5" max="5" width="22.75" style="20" customWidth="1"/>
+    <col min="6" max="6" width="25.25" style="20" customWidth="1"/>
+    <col min="7" max="7" width="14" style="20" customWidth="1"/>
+    <col min="8" max="8" width="30" style="20" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="22" t="s">
+      <c r="F4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:8">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="25" t="s">
+      <c r="D5" s="27"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="22" t="s">
+      <c r="D6" s="27"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>500</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="25" t="s">
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="22" t="s">
+      <c r="D8" s="27"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="25" t="s">
+      <c r="D9" s="29"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8">
       <c r="A14" s="7" t="s">
@@ -4512,176 +4690,176 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:9">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="17" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:9">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="18">
         <v>500</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="18">
         <v>500</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:9">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:9">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:9">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="18" t="s">
+      <c r="G7" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="19" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:9">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="17" t="s">
+      <c r="G8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="18" t="s">
         <v>276</v>
       </c>
     </row>
@@ -4841,39 +5019,39 @@
       <c r="H4" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="11" t="e">
+      <c r="I4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="12" t="e">
         <f>IF(I4&gt;0,K4/I4,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="T4" s="10" t="s">
+      <c r="M4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T4" s="11" t="s">
         <v>14</v>
       </c>
       <c r="U4" s="4" t="s">
@@ -4915,7 +5093,7 @@
       <c r="K5" s="9">
         <v>0</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="13">
         <f>IF(I5&gt;0,K5/I5,0)</f>
         <v>0</v>
       </c>
@@ -4932,12 +5110,12 @@
         <v>171</v>
       </c>
       <c r="Q5" s="9">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="R5" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="13">
         <v>0.0166</v>
       </c>
       <c r="T5" s="9">
@@ -4982,7 +5160,7 @@
       <c r="K6" s="9">
         <v>0</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="13">
         <f>IF(I6&gt;0,K6/I6,0)</f>
         <v>0</v>
       </c>
@@ -4999,12 +5177,12 @@
         <v>173</v>
       </c>
       <c r="Q6" s="9">
-        <v>418</v>
+        <v>0</v>
       </c>
       <c r="R6" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="13">
         <v>0.0209</v>
       </c>
       <c r="T6" s="9"/>
@@ -5040,40 +5218,42 @@
       <c r="H7" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="12" t="e">
+      <c r="I7" s="9">
+        <v>36167</v>
+      </c>
+      <c r="J7" s="9">
+        <v>36167</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
         <f>IF(I7&gt;0,K7/I7,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="M7" s="9">
+        <v>210.2</v>
+      </c>
+      <c r="N7" s="9">
+        <v>180</v>
+      </c>
+      <c r="O7" s="9">
+        <v>40.38</v>
+      </c>
+      <c r="P7" s="9">
+        <v>162</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="S7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>14</v>
+        <v>298</v>
+      </c>
+      <c r="S7" s="13">
+        <v>0.0214</v>
+      </c>
+      <c r="T7" s="9">
+        <v>76</v>
       </c>
       <c r="U7" s="9" t="s">
         <v>29</v>
@@ -5082,7 +5262,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" s="8" customFormat="1" ht="114" customHeight="1" spans="1:22">
+    <row r="8" s="8" customFormat="1" ht="287" customHeight="1" spans="1:22">
       <c r="A8" s="9" t="s">
         <v>303</v>
       </c>
@@ -5095,8 +5275,8 @@
       <c r="D8" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>158</v>
+      <c r="E8" s="10" t="s">
+        <v>305</v>
       </c>
       <c r="F8" s="9">
         <v>500</v>
@@ -5114,7 +5294,7 @@
       <c r="K8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="12" t="e">
+      <c r="L8" s="13" t="e">
         <f>IF(I8&gt;0,K8/I8,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -5136,7 +5316,7 @@
       <c r="R8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S8" s="12" t="s">
+      <c r="S8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T8" s="9" t="s">
@@ -5151,7 +5331,7 @@
     </row>
     <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A9" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
@@ -5172,18 +5352,18 @@
       <c r="H9" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="10"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="11"/>
       <c r="U9" s="4" t="s">
         <v>295</v>
       </c>
@@ -5191,7 +5371,7 @@
     </row>
     <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A10" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -5221,7 +5401,7 @@
       <c r="K10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="13" t="e">
+      <c r="L10" s="14" t="e">
         <f t="shared" ref="L10:L18" si="0">IF(I10&gt;0,K10/I10,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -5243,7 +5423,7 @@
       <c r="R10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S10" s="13" t="s">
+      <c r="S10" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T10" s="2" t="s">
@@ -5258,7 +5438,7 @@
     </row>
     <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A11" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
@@ -5288,7 +5468,7 @@
       <c r="K11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L11" s="14" t="e">
+      <c r="L11" s="15" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -5310,7 +5490,7 @@
       <c r="R11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="S11" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T11" s="4" t="s">
@@ -5325,7 +5505,7 @@
     </row>
     <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A12" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>14</v>
@@ -5355,7 +5535,7 @@
       <c r="K12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="13" t="e">
+      <c r="L12" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -5377,7 +5557,7 @@
       <c r="R12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T12" s="2" t="s">
@@ -5392,7 +5572,7 @@
     </row>
     <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A13" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>14</v>
@@ -5422,7 +5602,7 @@
       <c r="K13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L13" s="14" t="e">
+      <c r="L13" s="15" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -5444,7 +5624,7 @@
       <c r="R13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S13" s="14" t="s">
+      <c r="S13" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T13" s="4" t="s">
@@ -5459,7 +5639,7 @@
     </row>
     <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A14" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
@@ -5480,18 +5660,18 @@
       <c r="H14" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="10"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="11"/>
       <c r="U14" s="4" t="s">
         <v>295</v>
       </c>
@@ -5499,7 +5679,7 @@
     </row>
     <row r="15" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A15" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>14</v>
@@ -5529,7 +5709,7 @@
       <c r="K15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L15" s="12" t="e">
+      <c r="L15" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -5551,7 +5731,7 @@
       <c r="R15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S15" s="12" t="s">
+      <c r="S15" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T15" s="9" t="s">
@@ -5566,7 +5746,7 @@
     </row>
     <row r="16" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A16" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>14</v>
@@ -5596,7 +5776,7 @@
       <c r="K16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L16" s="12" t="e">
+      <c r="L16" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -5618,7 +5798,7 @@
       <c r="R16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S16" s="12" t="s">
+      <c r="S16" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T16" s="9" t="s">
@@ -5633,7 +5813,7 @@
     </row>
     <row r="17" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A17" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>14</v>
@@ -5663,7 +5843,7 @@
       <c r="K17" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L17" s="12" t="e">
+      <c r="L17" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -5685,7 +5865,7 @@
       <c r="R17" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S17" s="12" t="s">
+      <c r="S17" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T17" s="9" t="s">
@@ -5700,7 +5880,7 @@
     </row>
     <row r="18" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A18" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>14</v>
@@ -5730,7 +5910,7 @@
       <c r="K18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L18" s="12" t="e">
+      <c r="L18" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -5752,7 +5932,7 @@
       <c r="R18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S18" s="12" t="s">
+      <c r="S18" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T18" s="9" t="s">
@@ -5767,7 +5947,7 @@
     </row>
     <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A19" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4" t="s">
@@ -5788,18 +5968,18 @@
       <c r="H19" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="10"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="11"/>
       <c r="U19" s="4" t="s">
         <v>295</v>
       </c>
@@ -5807,7 +5987,7 @@
     </row>
     <row r="20" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A20" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>14</v>
@@ -5837,7 +6017,7 @@
       <c r="K20" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L20" s="12" t="e">
+      <c r="L20" s="13" t="e">
         <f t="shared" ref="L20:L23" si="1">IF(I20&gt;0,K20/I20,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -5859,7 +6039,7 @@
       <c r="R20" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S20" s="12" t="s">
+      <c r="S20" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T20" s="9" t="s">
@@ -5874,7 +6054,7 @@
     </row>
     <row r="21" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A21" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>14</v>
@@ -5904,7 +6084,7 @@
       <c r="K21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L21" s="12" t="e">
+      <c r="L21" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -5926,7 +6106,7 @@
       <c r="R21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S21" s="12" t="s">
+      <c r="S21" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T21" s="9" t="s">
@@ -5941,7 +6121,7 @@
     </row>
     <row r="22" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A22" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>14</v>
@@ -5971,7 +6151,7 @@
       <c r="K22" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L22" s="12" t="e">
+      <c r="L22" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -5993,7 +6173,7 @@
       <c r="R22" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S22" s="12" t="s">
+      <c r="S22" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T22" s="9" t="s">
@@ -6008,7 +6188,7 @@
     </row>
     <row r="23" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A23" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>14</v>
@@ -6038,7 +6218,7 @@
       <c r="K23" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L23" s="12" t="e">
+      <c r="L23" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -6060,7 +6240,7 @@
       <c r="R23" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S23" s="12" t="s">
+      <c r="S23" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T23" s="9" t="s">
@@ -6075,7 +6255,7 @@
     </row>
     <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A24" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
@@ -6096,18 +6276,18 @@
       <c r="H24" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="10"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="11"/>
       <c r="U24" s="4" t="s">
         <v>295</v>
       </c>
@@ -6115,7 +6295,7 @@
     </row>
     <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A25" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>14</v>
@@ -6145,7 +6325,7 @@
       <c r="K25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="13" t="e">
+      <c r="L25" s="14" t="e">
         <f t="shared" ref="L25:L28" si="2">IF(I25&gt;0,K25/I25,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -6167,7 +6347,7 @@
       <c r="R25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S25" s="13" t="s">
+      <c r="S25" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T25" s="2" t="s">
@@ -6182,7 +6362,7 @@
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A26" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>14</v>
@@ -6212,7 +6392,7 @@
       <c r="K26" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L26" s="14" t="e">
+      <c r="L26" s="15" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
@@ -6234,7 +6414,7 @@
       <c r="R26" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S26" s="14" t="s">
+      <c r="S26" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T26" s="4" t="s">
@@ -6249,7 +6429,7 @@
     </row>
     <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A27" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>14</v>
@@ -6279,7 +6459,7 @@
       <c r="K27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L27" s="13" t="e">
+      <c r="L27" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
@@ -6301,7 +6481,7 @@
       <c r="R27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S27" s="13" t="s">
+      <c r="S27" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T27" s="2" t="s">
@@ -6316,7 +6496,7 @@
     </row>
     <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A28" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
@@ -6346,7 +6526,7 @@
       <c r="K28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L28" s="14" t="e">
+      <c r="L28" s="15" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
@@ -6368,7 +6548,7 @@
       <c r="R28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S28" s="14" t="s">
+      <c r="S28" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T28" s="4" t="s">
@@ -6383,7 +6563,7 @@
     </row>
     <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A29" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
@@ -6404,18 +6584,18 @@
       <c r="H29" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="10"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="11"/>
       <c r="U29" s="4" t="s">
         <v>295</v>
       </c>
@@ -6423,7 +6603,7 @@
     </row>
     <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A30" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>14</v>
@@ -6453,7 +6633,7 @@
       <c r="K30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L30" s="13" t="e">
+      <c r="L30" s="14" t="e">
         <f t="shared" ref="L30:L33" si="3">IF(I30&gt;0,K30/I30,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -6475,7 +6655,7 @@
       <c r="R30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S30" s="13" t="s">
+      <c r="S30" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T30" s="2" t="s">
@@ -6490,7 +6670,7 @@
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A31" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>14</v>
@@ -6520,7 +6700,7 @@
       <c r="K31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L31" s="14" t="e">
+      <c r="L31" s="15" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
@@ -6542,7 +6722,7 @@
       <c r="R31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S31" s="14" t="s">
+      <c r="S31" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T31" s="4" t="s">
@@ -6557,7 +6737,7 @@
     </row>
     <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A32" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>14</v>
@@ -6587,7 +6767,7 @@
       <c r="K32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L32" s="13" t="e">
+      <c r="L32" s="14" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
@@ -6609,7 +6789,7 @@
       <c r="R32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S32" s="13" t="s">
+      <c r="S32" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T32" s="2" t="s">
@@ -6624,7 +6804,7 @@
     </row>
     <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A33" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>14</v>
@@ -6654,7 +6834,7 @@
       <c r="K33" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L33" s="14" t="e">
+      <c r="L33" s="15" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
@@ -6676,7 +6856,7 @@
       <c r="R33" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S33" s="14" t="s">
+      <c r="S33" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T33" s="4" t="s">
@@ -6691,7 +6871,7 @@
     </row>
     <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A34" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4" t="s">
@@ -6712,18 +6892,18 @@
       <c r="H34" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="11"/>
-      <c r="T34" s="10"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="11"/>
       <c r="U34" s="4" t="s">
         <v>295</v>
       </c>
@@ -6731,7 +6911,7 @@
     </row>
     <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A35" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>14</v>
@@ -6761,7 +6941,7 @@
       <c r="K35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L35" s="13" t="e">
+      <c r="L35" s="14" t="e">
         <f t="shared" ref="L35:L38" si="4">IF(I35&gt;0,K35/I35,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -6783,7 +6963,7 @@
       <c r="R35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S35" s="13" t="s">
+      <c r="S35" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T35" s="2" t="s">
@@ -6798,7 +6978,7 @@
     </row>
     <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A36" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>14</v>
@@ -6828,7 +7008,7 @@
       <c r="K36" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L36" s="14" t="e">
+      <c r="L36" s="15" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
@@ -6850,7 +7030,7 @@
       <c r="R36" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S36" s="14" t="s">
+      <c r="S36" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T36" s="4" t="s">
@@ -6865,7 +7045,7 @@
     </row>
     <row r="37" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A37" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>14</v>
@@ -6895,7 +7075,7 @@
       <c r="K37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L37" s="13" t="e">
+      <c r="L37" s="14" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
@@ -6917,7 +7097,7 @@
       <c r="R37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S37" s="13" t="s">
+      <c r="S37" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T37" s="2" t="s">
@@ -6932,7 +7112,7 @@
     </row>
     <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A38" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>14</v>
@@ -6962,7 +7142,7 @@
       <c r="K38" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L38" s="14" t="e">
+      <c r="L38" s="15" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
@@ -6984,7 +7164,7 @@
       <c r="R38" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S38" s="14" t="s">
+      <c r="S38" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T38" s="4" t="s">
@@ -6999,7 +7179,7 @@
     </row>
     <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A39" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4" t="s">
@@ -7020,18 +7200,18 @@
       <c r="H39" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="11"/>
-      <c r="T39" s="10"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="12"/>
+      <c r="T39" s="11"/>
       <c r="U39" s="4" t="s">
         <v>295</v>
       </c>
@@ -7039,7 +7219,7 @@
     </row>
     <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A40" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>14</v>
@@ -7048,7 +7228,7 @@
         <v>297</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>140</v>
@@ -7069,7 +7249,7 @@
       <c r="K40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L40" s="13" t="e">
+      <c r="L40" s="14" t="e">
         <f t="shared" ref="L40:L43" si="5">IF(I40&gt;0,K40/I40,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -7091,7 +7271,7 @@
       <c r="R40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S40" s="13" t="s">
+      <c r="S40" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T40" s="2" t="s">
@@ -7106,7 +7286,7 @@
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A41" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>14</v>
@@ -7115,7 +7295,7 @@
         <v>297</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>146</v>
@@ -7136,7 +7316,7 @@
       <c r="K41" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L41" s="14" t="e">
+      <c r="L41" s="15" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
@@ -7158,7 +7338,7 @@
       <c r="R41" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S41" s="14" t="s">
+      <c r="S41" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T41" s="4" t="s">
@@ -7173,7 +7353,7 @@
     </row>
     <row r="42" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A42" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>14</v>
@@ -7182,7 +7362,7 @@
         <v>297</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>152</v>
@@ -7203,7 +7383,7 @@
       <c r="K42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L42" s="13" t="e">
+      <c r="L42" s="14" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
@@ -7225,7 +7405,7 @@
       <c r="R42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S42" s="13" t="s">
+      <c r="S42" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T42" s="2" t="s">
@@ -7240,7 +7420,7 @@
     </row>
     <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A43" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>14</v>
@@ -7249,7 +7429,7 @@
         <v>304</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>158</v>
@@ -7270,7 +7450,7 @@
       <c r="K43" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L43" s="14" t="e">
+      <c r="L43" s="15" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
@@ -7292,7 +7472,7 @@
       <c r="R43" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S43" s="14" t="s">
+      <c r="S43" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T43" s="4" t="s">
@@ -7307,7 +7487,7 @@
     </row>
     <row r="44" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A44" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4" t="s">
@@ -7328,18 +7508,18 @@
       <c r="H44" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="10"/>
-      <c r="S44" s="11"/>
-      <c r="T44" s="10"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="12"/>
+      <c r="T44" s="11"/>
       <c r="U44" s="4" t="s">
         <v>295</v>
       </c>
@@ -7347,7 +7527,7 @@
     </row>
     <row r="45" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A45" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>14</v>
@@ -7377,7 +7557,7 @@
       <c r="K45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L45" s="13" t="e">
+      <c r="L45" s="14" t="e">
         <f t="shared" ref="L45:L48" si="6">IF(I45&gt;0,K45/I45,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -7399,7 +7579,7 @@
       <c r="R45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S45" s="13" t="s">
+      <c r="S45" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T45" s="2" t="s">
@@ -7414,7 +7594,7 @@
     </row>
     <row r="46" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A46" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>14</v>
@@ -7444,7 +7624,7 @@
       <c r="K46" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L46" s="14" t="e">
+      <c r="L46" s="15" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
@@ -7466,7 +7646,7 @@
       <c r="R46" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S46" s="14" t="s">
+      <c r="S46" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T46" s="4" t="s">
@@ -7481,7 +7661,7 @@
     </row>
     <row r="47" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A47" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>14</v>
@@ -7511,7 +7691,7 @@
       <c r="K47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L47" s="13" t="e">
+      <c r="L47" s="14" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
@@ -7533,7 +7713,7 @@
       <c r="R47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S47" s="13" t="s">
+      <c r="S47" s="14" t="s">
         <v>14</v>
       </c>
       <c r="T47" s="2" t="s">
@@ -7548,7 +7728,7 @@
     </row>
     <row r="48" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A48" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>14</v>
@@ -7578,7 +7758,7 @@
       <c r="K48" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L48" s="14" t="e">
+      <c r="L48" s="15" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
@@ -7600,7 +7780,7 @@
       <c r="R48" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S48" s="14" t="s">
+      <c r="S48" s="15" t="s">
         <v>14</v>
       </c>
       <c r="T48" s="4" t="s">
@@ -7615,7 +7795,7 @@
     </row>
     <row r="49" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A49" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
@@ -7636,18 +7816,18 @@
       <c r="H49" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="11"/>
-      <c r="T49" s="10"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="12"/>
+      <c r="T49" s="11"/>
       <c r="U49" s="4" t="s">
         <v>295</v>
       </c>
@@ -7655,7 +7835,7 @@
     </row>
     <row r="50" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A50" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>14</v>
@@ -7685,7 +7865,7 @@
       <c r="K50" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L50" s="12" t="e">
+      <c r="L50" s="13" t="e">
         <f t="shared" ref="L50:L53" si="7">IF(I50&gt;0,K50/I50,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -7707,7 +7887,7 @@
       <c r="R50" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S50" s="12" t="s">
+      <c r="S50" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T50" s="9" t="s">
@@ -7722,7 +7902,7 @@
     </row>
     <row r="51" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A51" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>14</v>
@@ -7752,7 +7932,7 @@
       <c r="K51" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="12" t="e">
+      <c r="L51" s="13" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -7774,7 +7954,7 @@
       <c r="R51" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S51" s="12" t="s">
+      <c r="S51" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T51" s="9" t="s">
@@ -7789,7 +7969,7 @@
     </row>
     <row r="52" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A52" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>14</v>
@@ -7819,7 +7999,7 @@
       <c r="K52" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L52" s="12" t="e">
+      <c r="L52" s="13" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -7841,7 +8021,7 @@
       <c r="R52" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S52" s="12" t="s">
+      <c r="S52" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T52" s="9" t="s">
@@ -7856,7 +8036,7 @@
     </row>
     <row r="53" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A53" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>14</v>
@@ -7886,7 +8066,7 @@
       <c r="K53" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L53" s="12" t="e">
+      <c r="L53" s="13" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -7908,7 +8088,7 @@
       <c r="R53" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S53" s="12" t="s">
+      <c r="S53" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T53" s="9" t="s">
@@ -7923,7 +8103,7 @@
     </row>
     <row r="54" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A54" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
@@ -7944,18 +8124,18 @@
       <c r="H54" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
-      <c r="R54" s="10"/>
-      <c r="S54" s="11"/>
-      <c r="T54" s="10"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="12"/>
+      <c r="T54" s="11"/>
       <c r="U54" s="4" t="s">
         <v>295</v>
       </c>
@@ -7963,16 +8143,16 @@
     </row>
     <row r="55" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A55" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>140</v>
@@ -7989,11 +8169,11 @@
       <c r="I55" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J55" s="15"/>
+      <c r="J55" s="16"/>
       <c r="K55" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L55" s="12" t="e">
+      <c r="L55" s="13" t="e">
         <f t="shared" ref="L55:L58" si="8">IF(I55&gt;0,K55/I55,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -8015,7 +8195,7 @@
       <c r="R55" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S55" s="12" t="s">
+      <c r="S55" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T55" s="9" t="s">
@@ -8030,14 +8210,14 @@
     </row>
     <row r="56" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A56" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B56" s="9"/>
       <c r="C56" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>146</v>
@@ -8054,11 +8234,11 @@
       <c r="I56" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="15"/>
+      <c r="J56" s="16"/>
       <c r="K56" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="12" t="e">
+      <c r="L56" s="13" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
@@ -8080,7 +8260,7 @@
       <c r="R56" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S56" s="12" t="s">
+      <c r="S56" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T56" s="9" t="s">
@@ -8095,16 +8275,16 @@
     </row>
     <row r="57" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A57" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>152</v>
@@ -8121,11 +8301,11 @@
       <c r="I57" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J57" s="15"/>
+      <c r="J57" s="16"/>
       <c r="K57" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L57" s="12" t="e">
+      <c r="L57" s="13" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
@@ -8147,7 +8327,7 @@
       <c r="R57" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S57" s="12" t="s">
+      <c r="S57" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T57" s="9" t="s">
@@ -8162,16 +8342,16 @@
     </row>
     <row r="58" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A58" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>158</v>
@@ -8188,11 +8368,11 @@
       <c r="I58" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J58" s="15"/>
+      <c r="J58" s="16"/>
       <c r="K58" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L58" s="12" t="e">
+      <c r="L58" s="13" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
@@ -8214,7 +8394,7 @@
       <c r="R58" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S58" s="12" t="s">
+      <c r="S58" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T58" s="9" t="s">
@@ -8229,7 +8409,7 @@
     </row>
     <row r="59" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A59" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4" t="s">
@@ -8250,18 +8430,18 @@
       <c r="H59" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="10"/>
-      <c r="S59" s="11"/>
-      <c r="T59" s="10"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="12"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="11"/>
+      <c r="Q59" s="11"/>
+      <c r="R59" s="11"/>
+      <c r="S59" s="12"/>
+      <c r="T59" s="11"/>
       <c r="U59" s="4" t="s">
         <v>295</v>
       </c>
@@ -8269,16 +8449,16 @@
     </row>
     <row r="60" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A60" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>140</v>
@@ -8295,11 +8475,11 @@
       <c r="I60" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J60" s="15"/>
+      <c r="J60" s="16"/>
       <c r="K60" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L60" s="12" t="e">
+      <c r="L60" s="13" t="e">
         <f t="shared" ref="L60:L63" si="9">IF(I60&gt;0,K60/I60,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -8321,7 +8501,7 @@
       <c r="R60" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S60" s="12" t="s">
+      <c r="S60" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T60" s="9" t="s">
@@ -8336,14 +8516,14 @@
     </row>
     <row r="61" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A61" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B61" s="9"/>
       <c r="C61" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>146</v>
@@ -8360,11 +8540,11 @@
       <c r="I61" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J61" s="15"/>
+      <c r="J61" s="16"/>
       <c r="K61" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="12" t="e">
+      <c r="L61" s="13" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -8386,7 +8566,7 @@
       <c r="R61" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S61" s="12" t="s">
+      <c r="S61" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T61" s="9" t="s">
@@ -8401,16 +8581,16 @@
     </row>
     <row r="62" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A62" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>152</v>
@@ -8427,11 +8607,11 @@
       <c r="I62" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J62" s="15"/>
+      <c r="J62" s="16"/>
       <c r="K62" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L62" s="12" t="e">
+      <c r="L62" s="13" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -8453,7 +8633,7 @@
       <c r="R62" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S62" s="12" t="s">
+      <c r="S62" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T62" s="9" t="s">
@@ -8468,16 +8648,16 @@
     </row>
     <row r="63" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A63" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>158</v>
@@ -8494,11 +8674,11 @@
       <c r="I63" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J63" s="15"/>
+      <c r="J63" s="16"/>
       <c r="K63" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L63" s="12" t="e">
+      <c r="L63" s="13" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -8520,7 +8700,7 @@
       <c r="R63" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S63" s="12" t="s">
+      <c r="S63" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T63" s="9" t="s">
@@ -8535,7 +8715,7 @@
     </row>
     <row r="64" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A64" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4" t="s">
@@ -8556,18 +8736,18 @@
       <c r="H64" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-      <c r="Q64" s="10"/>
-      <c r="R64" s="10"/>
-      <c r="S64" s="11"/>
-      <c r="T64" s="10"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="11"/>
+      <c r="O64" s="11"/>
+      <c r="P64" s="11"/>
+      <c r="Q64" s="11"/>
+      <c r="R64" s="11"/>
+      <c r="S64" s="12"/>
+      <c r="T64" s="11"/>
       <c r="U64" s="4" t="s">
         <v>295</v>
       </c>
@@ -8575,16 +8755,16 @@
     </row>
     <row r="65" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A65" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>140</v>
@@ -8601,11 +8781,11 @@
       <c r="I65" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J65" s="15"/>
+      <c r="J65" s="16"/>
       <c r="K65" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L65" s="12" t="e">
+      <c r="L65" s="13" t="e">
         <f t="shared" ref="L65:L68" si="10">IF(I65&gt;0,K65/I65,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -8627,7 +8807,7 @@
       <c r="R65" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S65" s="12" t="s">
+      <c r="S65" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T65" s="9" t="s">
@@ -8642,14 +8822,14 @@
     </row>
     <row r="66" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A66" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>146</v>
@@ -8666,11 +8846,11 @@
       <c r="I66" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J66" s="15"/>
+      <c r="J66" s="16"/>
       <c r="K66" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L66" s="12" t="e">
+      <c r="L66" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
@@ -8692,7 +8872,7 @@
       <c r="R66" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S66" s="12" t="s">
+      <c r="S66" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T66" s="9" t="s">
@@ -8707,16 +8887,16 @@
     </row>
     <row r="67" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A67" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>152</v>
@@ -8733,11 +8913,11 @@
       <c r="I67" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J67" s="15"/>
+      <c r="J67" s="16"/>
       <c r="K67" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L67" s="12" t="e">
+      <c r="L67" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
@@ -8759,7 +8939,7 @@
       <c r="R67" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S67" s="12" t="s">
+      <c r="S67" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T67" s="9" t="s">
@@ -8774,16 +8954,16 @@
     </row>
     <row r="68" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A68" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>158</v>
@@ -8800,11 +8980,11 @@
       <c r="I68" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J68" s="15"/>
+      <c r="J68" s="16"/>
       <c r="K68" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L68" s="12" t="e">
+      <c r="L68" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
@@ -8826,7 +9006,7 @@
       <c r="R68" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S68" s="12" t="s">
+      <c r="S68" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T68" s="9" t="s">
@@ -8841,7 +9021,7 @@
     </row>
     <row r="69" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A69" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4" t="s">
@@ -8862,18 +9042,18 @@
       <c r="H69" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
-      <c r="O69" s="10"/>
-      <c r="P69" s="10"/>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="11"/>
-      <c r="T69" s="10"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="11"/>
+      <c r="P69" s="11"/>
+      <c r="Q69" s="11"/>
+      <c r="R69" s="11"/>
+      <c r="S69" s="12"/>
+      <c r="T69" s="11"/>
       <c r="U69" s="4" t="s">
         <v>295</v>
       </c>
@@ -8881,16 +9061,16 @@
     </row>
     <row r="70" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A70" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>140</v>
@@ -8907,11 +9087,11 @@
       <c r="I70" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J70" s="15"/>
+      <c r="J70" s="16"/>
       <c r="K70" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L70" s="12" t="e">
+      <c r="L70" s="13" t="e">
         <f t="shared" ref="L70:L73" si="11">IF(I70&gt;0,K70/I70,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -8933,7 +9113,7 @@
       <c r="R70" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S70" s="12" t="s">
+      <c r="S70" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T70" s="9" t="s">
@@ -8948,14 +9128,14 @@
     </row>
     <row r="71" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A71" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B71" s="9"/>
       <c r="C71" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>146</v>
@@ -8972,11 +9152,11 @@
       <c r="I71" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J71" s="15"/>
+      <c r="J71" s="16"/>
       <c r="K71" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L71" s="12" t="e">
+      <c r="L71" s="13" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
@@ -8998,7 +9178,7 @@
       <c r="R71" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S71" s="12" t="s">
+      <c r="S71" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T71" s="9" t="s">
@@ -9013,16 +9193,16 @@
     </row>
     <row r="72" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A72" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>152</v>
@@ -9039,11 +9219,11 @@
       <c r="I72" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J72" s="15"/>
+      <c r="J72" s="16"/>
       <c r="K72" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L72" s="12" t="e">
+      <c r="L72" s="13" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
@@ -9065,7 +9245,7 @@
       <c r="R72" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S72" s="12" t="s">
+      <c r="S72" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T72" s="9" t="s">
@@ -9080,16 +9260,16 @@
     </row>
     <row r="73" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A73" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>158</v>
@@ -9106,11 +9286,11 @@
       <c r="I73" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J73" s="15"/>
+      <c r="J73" s="16"/>
       <c r="K73" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L73" s="12" t="e">
+      <c r="L73" s="13" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
@@ -9132,7 +9312,7 @@
       <c r="R73" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S73" s="12" t="s">
+      <c r="S73" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T73" s="9" t="s">
@@ -9147,7 +9327,7 @@
     </row>
     <row r="74" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A74" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4" t="s">
@@ -9168,18 +9348,18 @@
       <c r="H74" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="10"/>
-      <c r="N74" s="10"/>
-      <c r="O74" s="10"/>
-      <c r="P74" s="10"/>
-      <c r="Q74" s="10"/>
-      <c r="R74" s="10"/>
-      <c r="S74" s="11"/>
-      <c r="T74" s="10"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="11"/>
+      <c r="P74" s="11"/>
+      <c r="Q74" s="11"/>
+      <c r="R74" s="11"/>
+      <c r="S74" s="12"/>
+      <c r="T74" s="11"/>
       <c r="U74" s="4" t="s">
         <v>295</v>
       </c>
@@ -9187,16 +9367,16 @@
     </row>
     <row r="75" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A75" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>140</v>
@@ -9217,7 +9397,7 @@
       <c r="K75" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L75" s="12" t="e">
+      <c r="L75" s="13" t="e">
         <f t="shared" ref="L75:L78" si="12">IF(I75&gt;0,K75/I75,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -9239,7 +9419,7 @@
       <c r="R75" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S75" s="12" t="s">
+      <c r="S75" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T75" s="9" t="s">
@@ -9254,14 +9434,14 @@
     </row>
     <row r="76" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A76" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B76" s="9"/>
       <c r="C76" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>146</v>
@@ -9282,7 +9462,7 @@
       <c r="K76" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L76" s="12" t="e">
+      <c r="L76" s="13" t="e">
         <f t="shared" si="12"/>
         <v>#VALUE!</v>
       </c>
@@ -9304,7 +9484,7 @@
       <c r="R76" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S76" s="12" t="s">
+      <c r="S76" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T76" s="9" t="s">
@@ -9319,16 +9499,16 @@
     </row>
     <row r="77" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A77" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>152</v>
@@ -9349,7 +9529,7 @@
       <c r="K77" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L77" s="12" t="e">
+      <c r="L77" s="13" t="e">
         <f t="shared" si="12"/>
         <v>#VALUE!</v>
       </c>
@@ -9371,7 +9551,7 @@
       <c r="R77" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S77" s="12" t="s">
+      <c r="S77" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T77" s="9" t="s">
@@ -9386,16 +9566,16 @@
     </row>
     <row r="78" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A78" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>158</v>
@@ -9416,7 +9596,7 @@
       <c r="K78" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L78" s="12" t="e">
+      <c r="L78" s="13" t="e">
         <f t="shared" si="12"/>
         <v>#VALUE!</v>
       </c>
@@ -9438,7 +9618,7 @@
       <c r="R78" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S78" s="12" t="s">
+      <c r="S78" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T78" s="9" t="s">
@@ -9453,7 +9633,7 @@
     </row>
     <row r="79" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A79" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4" t="s">
@@ -9474,18 +9654,18 @@
       <c r="H79" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="10"/>
-      <c r="N79" s="10"/>
-      <c r="O79" s="10"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="11"/>
-      <c r="T79" s="10"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="12"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="11"/>
+      <c r="O79" s="11"/>
+      <c r="P79" s="11"/>
+      <c r="Q79" s="11"/>
+      <c r="R79" s="11"/>
+      <c r="S79" s="12"/>
+      <c r="T79" s="11"/>
       <c r="U79" s="4" t="s">
         <v>295</v>
       </c>
@@ -9493,16 +9673,16 @@
     </row>
     <row r="80" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A80" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>140</v>
@@ -9523,7 +9703,7 @@
       <c r="K80" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L80" s="12" t="e">
+      <c r="L80" s="13" t="e">
         <f t="shared" ref="L80:L83" si="13">IF(I80&gt;0,K80/I80,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -9545,7 +9725,7 @@
       <c r="R80" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S80" s="12" t="s">
+      <c r="S80" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T80" s="9" t="s">
@@ -9560,14 +9740,14 @@
     </row>
     <row r="81" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A81" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B81" s="9"/>
       <c r="C81" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>146</v>
@@ -9588,7 +9768,7 @@
       <c r="K81" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L81" s="12" t="e">
+      <c r="L81" s="13" t="e">
         <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
@@ -9610,7 +9790,7 @@
       <c r="R81" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S81" s="12" t="s">
+      <c r="S81" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T81" s="9" t="s">
@@ -9625,16 +9805,16 @@
     </row>
     <row r="82" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A82" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>152</v>
@@ -9655,7 +9835,7 @@
       <c r="K82" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L82" s="12" t="e">
+      <c r="L82" s="13" t="e">
         <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
@@ -9677,7 +9857,7 @@
       <c r="R82" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S82" s="12" t="s">
+      <c r="S82" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T82" s="9" t="s">
@@ -9692,16 +9872,16 @@
     </row>
     <row r="83" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A83" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>158</v>
@@ -9722,7 +9902,7 @@
       <c r="K83" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L83" s="12" t="e">
+      <c r="L83" s="13" t="e">
         <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
@@ -9744,7 +9924,7 @@
       <c r="R83" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S83" s="12" t="s">
+      <c r="S83" s="13" t="s">
         <v>14</v>
       </c>
       <c r="T83" s="9" t="s">
@@ -9769,14 +9949,14 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
-      <c r="L84" s="13"/>
+      <c r="L84" s="14"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
       <c r="R84" s="2"/>
-      <c r="S84" s="13"/>
+      <c r="S84" s="14"/>
       <c r="T84" s="2"/>
       <c r="U84" s="2"/>
       <c r="V84" s="2"/>
@@ -9793,14 +9973,14 @@
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
-      <c r="L85" s="14"/>
+      <c r="L85" s="15"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
       <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
       <c r="R85" s="4"/>
-      <c r="S85" s="14"/>
+      <c r="S85" s="15"/>
       <c r="T85" s="4"/>
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
@@ -9817,14 +9997,14 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
-      <c r="L86" s="13"/>
+      <c r="L86" s="14"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
       <c r="R86" s="2"/>
-      <c r="S86" s="13"/>
+      <c r="S86" s="14"/>
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
       <c r="V86" s="2"/>
@@ -9841,14 +10021,14 @@
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
-      <c r="L87" s="14"/>
+      <c r="L87" s="15"/>
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
       <c r="R87" s="4"/>
-      <c r="S87" s="14"/>
+      <c r="S87" s="15"/>
       <c r="T87" s="4"/>
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
@@ -9865,14 +10045,14 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
-      <c r="L88" s="13"/>
+      <c r="L88" s="14"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
       <c r="R88" s="2"/>
-      <c r="S88" s="13"/>
+      <c r="S88" s="14"/>
       <c r="T88" s="2"/>
       <c r="U88" s="2"/>
       <c r="V88" s="2"/>
@@ -9889,14 +10069,14 @@
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
-      <c r="L89" s="14"/>
+      <c r="L89" s="15"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
       <c r="R89" s="4"/>
-      <c r="S89" s="14"/>
+      <c r="S89" s="15"/>
       <c r="T89" s="4"/>
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
@@ -9913,14 +10093,14 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
-      <c r="L90" s="13"/>
+      <c r="L90" s="14"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
       <c r="Q90" s="2"/>
       <c r="R90" s="2"/>
-      <c r="S90" s="13"/>
+      <c r="S90" s="14"/>
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
       <c r="V90" s="2"/>
@@ -9937,14 +10117,14 @@
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
-      <c r="L91" s="14"/>
+      <c r="L91" s="15"/>
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
       <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
       <c r="R91" s="4"/>
-      <c r="S91" s="14"/>
+      <c r="S91" s="15"/>
       <c r="T91" s="4"/>
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
@@ -9961,14 +10141,14 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
-      <c r="L92" s="13"/>
+      <c r="L92" s="14"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
       <c r="Q92" s="2"/>
       <c r="R92" s="2"/>
-      <c r="S92" s="13"/>
+      <c r="S92" s="14"/>
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
       <c r="V92" s="2"/>
@@ -9985,14 +10165,14 @@
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
-      <c r="L93" s="14"/>
+      <c r="L93" s="15"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
       <c r="R93" s="4"/>
-      <c r="S93" s="14"/>
+      <c r="S93" s="15"/>
       <c r="T93" s="4"/>
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
@@ -10009,14 +10189,14 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
-      <c r="L94" s="13"/>
+      <c r="L94" s="14"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
       <c r="Q94" s="2"/>
       <c r="R94" s="2"/>
-      <c r="S94" s="13"/>
+      <c r="S94" s="14"/>
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
       <c r="V94" s="2"/>
@@ -10033,14 +10213,14 @@
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
-      <c r="L95" s="14"/>
+      <c r="L95" s="15"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
       <c r="R95" s="4"/>
-      <c r="S95" s="14"/>
+      <c r="S95" s="15"/>
       <c r="T95" s="4"/>
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
@@ -10057,14 +10237,14 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
-      <c r="L96" s="13"/>
+      <c r="L96" s="14"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
-      <c r="S96" s="13"/>
+      <c r="S96" s="14"/>
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
       <c r="V96" s="2"/>
@@ -10081,14 +10261,14 @@
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
-      <c r="L97" s="14"/>
+      <c r="L97" s="15"/>
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
       <c r="R97" s="4"/>
-      <c r="S97" s="14"/>
+      <c r="S97" s="15"/>
       <c r="T97" s="4"/>
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
@@ -10105,14 +10285,14 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
-      <c r="L98" s="13"/>
+      <c r="L98" s="14"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
       <c r="Q98" s="2"/>
       <c r="R98" s="2"/>
-      <c r="S98" s="13"/>
+      <c r="S98" s="14"/>
       <c r="T98" s="2"/>
       <c r="U98" s="2"/>
       <c r="V98" s="2"/>
@@ -10129,14 +10309,14 @@
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
-      <c r="L99" s="14"/>
+      <c r="L99" s="15"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
       <c r="R99" s="4"/>
-      <c r="S99" s="14"/>
+      <c r="S99" s="15"/>
       <c r="T99" s="4"/>
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
@@ -10153,14 +10333,14 @@
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
-      <c r="L100" s="13"/>
+      <c r="L100" s="14"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
       <c r="Q100" s="2"/>
       <c r="R100" s="2"/>
-      <c r="S100" s="13"/>
+      <c r="S100" s="14"/>
       <c r="T100" s="2"/>
       <c r="U100" s="2"/>
       <c r="V100" s="2"/>
@@ -10177,14 +10357,14 @@
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
-      <c r="L101" s="14"/>
+      <c r="L101" s="15"/>
       <c r="M101" s="4"/>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
       <c r="R101" s="4"/>
-      <c r="S101" s="14"/>
+      <c r="S101" s="15"/>
       <c r="T101" s="4"/>
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
@@ -10674,7 +10854,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -10694,16 +10874,16 @@
         <v>180</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>185</v>
@@ -10712,7 +10892,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -10726,19 +10906,19 @@
         <v>283</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -10755,22 +10935,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -10787,22 +10967,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -10825,16 +11005,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -10875,10 +11055,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -10894,25 +11074,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>185</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -10923,22 +11103,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -10947,7 +11127,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -10955,22 +11135,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -10987,22 +11167,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11011,7 +11191,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11019,22 +11199,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -962,8 +962,8 @@
   <si>
     <t xml:space="preserve">预热：
 master：窗口1、.\run_distributed_v2.ps1 -Mode master -WebPort 8089
-worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 0 -TotalWorkerCount 3 -TokenFile D:\ckj_locust\user_token.txt
-worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 2 -TotalWorkerCount 3 -TokenFile C:\ckj_locust\user_token.txt
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 0 -WorkerCount 2 -TotalWorkerCount 3 -TokenFile D:\ckj_locust\user_token.txt
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 2 -WorkerCount 1 -TotalWorkerCount 3 -TokenFile C:\ckj_locust\user_token.txt
 </t>
   </si>
   <si>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -960,11 +960,10 @@
     <t>单接口-冲击</t>
   </si>
   <si>
-    <t xml:space="preserve">预热：
+    <t xml:space="preserve">
 master：窗口1、.\run_distributed_v2.ps1 -Mode master -WebPort 8089
 worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 0 -WorkerCount 2 -TotalWorkerCount 3 -TokenFile D:\ckj_locust\user_token.txt
-worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 2 -WorkerCount 1 -TotalWorkerCount 3 -TokenFile C:\ckj_locust\user_token.txt
-</t>
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 2 -WorkerCount 1 -TotalWorkerCount 3 -TokenFile C:\ckj_locust\user_token.txt</t>
   </si>
   <si>
     <t>W01</t>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="439">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -957,13 +957,16 @@
     <t>R04</t>
   </si>
   <si>
-    <t>单接口-冲击</t>
+    <t>单接口-多阶段 ramp-up</t>
   </si>
   <si>
     <t xml:space="preserve">
 master：窗口1、.\run_distributed_v2.ps1 -Mode master -WebPort 8089
-worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 0 -WorkerCount 2 -TotalWorkerCount 3 -TokenFile D:\ckj_locust\user_token.txt
-worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 2 -WorkerCount 1 -TotalWorkerCount 3 -TokenFile C:\ckj_locust\user_token.txt</t>
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 0 -WorkerCount 2 -TotalWorkerCount 4 -TokenFile D:\ckj_locust\user_token.txt
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 2 -WorkerCount 2 -TotalWorkerCount 4 -TokenFile C:\ckj_locust\user_token.txt</t>
+  </si>
+  <si>
+    <t>10m==3(100)+3(300)+4(500)</t>
   </si>
   <si>
     <t>W01</t>
@@ -979,6 +982,9 @@
   </si>
   <si>
     <t>R08</t>
+  </si>
+  <si>
+    <t>单接口-冲击</t>
   </si>
   <si>
     <t>W03</t>
@@ -5284,7 +5290,7 @@
         <v>500</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>145</v>
+        <v>306</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>14</v>
@@ -5330,7 +5336,7 @@
     </row>
     <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A9" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
@@ -5370,7 +5376,7 @@
     </row>
     <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A10" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -5437,7 +5443,7 @@
     </row>
     <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A11" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
@@ -5504,7 +5510,7 @@
     </row>
     <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A12" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>14</v>
@@ -5571,13 +5577,13 @@
     </row>
     <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A13" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>72</v>
@@ -5638,7 +5644,7 @@
     </row>
     <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A14" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
@@ -5678,7 +5684,7 @@
     </row>
     <row r="15" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A15" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>14</v>
@@ -5745,7 +5751,7 @@
     </row>
     <row r="16" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A16" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>14</v>
@@ -5812,7 +5818,7 @@
     </row>
     <row r="17" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A17" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>14</v>
@@ -5879,13 +5885,13 @@
     </row>
     <row r="18" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A18" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>77</v>
@@ -5946,7 +5952,7 @@
     </row>
     <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A19" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4" t="s">
@@ -5986,7 +5992,7 @@
     </row>
     <row r="20" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A20" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>14</v>
@@ -6053,7 +6059,7 @@
     </row>
     <row r="21" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A21" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>14</v>
@@ -6120,7 +6126,7 @@
     </row>
     <row r="22" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A22" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>14</v>
@@ -6187,13 +6193,13 @@
     </row>
     <row r="23" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A23" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>82</v>
@@ -6254,7 +6260,7 @@
     </row>
     <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A24" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
@@ -6294,7 +6300,7 @@
     </row>
     <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A25" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>14</v>
@@ -6361,7 +6367,7 @@
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A26" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>14</v>
@@ -6428,7 +6434,7 @@
     </row>
     <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A27" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>14</v>
@@ -6495,13 +6501,13 @@
     </row>
     <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A28" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>85</v>
@@ -6562,7 +6568,7 @@
     </row>
     <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A29" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
@@ -6602,7 +6608,7 @@
     </row>
     <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A30" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>14</v>
@@ -6669,7 +6675,7 @@
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A31" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>14</v>
@@ -6736,7 +6742,7 @@
     </row>
     <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A32" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>14</v>
@@ -6803,13 +6809,13 @@
     </row>
     <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A33" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>88</v>
@@ -6870,7 +6876,7 @@
     </row>
     <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A34" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4" t="s">
@@ -6910,7 +6916,7 @@
     </row>
     <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A35" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>14</v>
@@ -6977,7 +6983,7 @@
     </row>
     <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A36" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>14</v>
@@ -7044,7 +7050,7 @@
     </row>
     <row r="37" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A37" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>14</v>
@@ -7111,13 +7117,13 @@
     </row>
     <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A38" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>91</v>
@@ -7178,7 +7184,7 @@
     </row>
     <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A39" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4" t="s">
@@ -7218,7 +7224,7 @@
     </row>
     <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A40" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>14</v>
@@ -7227,7 +7233,7 @@
         <v>297</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>140</v>
@@ -7285,7 +7291,7 @@
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A41" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>14</v>
@@ -7294,7 +7300,7 @@
         <v>297</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>146</v>
@@ -7352,7 +7358,7 @@
     </row>
     <row r="42" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A42" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>14</v>
@@ -7361,7 +7367,7 @@
         <v>297</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>152</v>
@@ -7419,16 +7425,16 @@
     </row>
     <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A43" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>158</v>
@@ -7486,7 +7492,7 @@
     </row>
     <row r="44" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A44" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4" t="s">
@@ -7526,7 +7532,7 @@
     </row>
     <row r="45" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A45" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>14</v>
@@ -7593,7 +7599,7 @@
     </row>
     <row r="46" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A46" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>14</v>
@@ -7660,7 +7666,7 @@
     </row>
     <row r="47" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A47" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>14</v>
@@ -7727,13 +7733,13 @@
     </row>
     <row r="48" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A48" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>98</v>
@@ -7794,7 +7800,7 @@
     </row>
     <row r="49" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A49" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
@@ -7834,7 +7840,7 @@
     </row>
     <row r="50" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A50" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>14</v>
@@ -7901,7 +7907,7 @@
     </row>
     <row r="51" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A51" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>14</v>
@@ -7968,7 +7974,7 @@
     </row>
     <row r="52" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A52" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>14</v>
@@ -8035,13 +8041,13 @@
     </row>
     <row r="53" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A53" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>101</v>
@@ -8102,7 +8108,7 @@
     </row>
     <row r="54" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A54" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
@@ -8142,16 +8148,16 @@
     </row>
     <row r="55" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A55" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>140</v>
@@ -8209,14 +8215,14 @@
     </row>
     <row r="56" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A56" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B56" s="9"/>
       <c r="C56" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>146</v>
@@ -8274,16 +8280,16 @@
     </row>
     <row r="57" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A57" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>152</v>
@@ -8341,16 +8347,16 @@
     </row>
     <row r="58" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A58" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>158</v>
@@ -8408,7 +8414,7 @@
     </row>
     <row r="59" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A59" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4" t="s">
@@ -8448,16 +8454,16 @@
     </row>
     <row r="60" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A60" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>140</v>
@@ -8515,14 +8521,14 @@
     </row>
     <row r="61" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A61" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B61" s="9"/>
       <c r="C61" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>146</v>
@@ -8580,16 +8586,16 @@
     </row>
     <row r="62" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A62" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>364</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>362</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>152</v>
@@ -8647,16 +8653,16 @@
     </row>
     <row r="63" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A63" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>158</v>
@@ -8714,7 +8720,7 @@
     </row>
     <row r="64" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A64" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4" t="s">
@@ -8754,16 +8760,16 @@
     </row>
     <row r="65" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A65" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>140</v>
@@ -8821,14 +8827,14 @@
     </row>
     <row r="66" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A66" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>146</v>
@@ -8886,16 +8892,16 @@
     </row>
     <row r="67" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A67" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>370</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>368</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>152</v>
@@ -8953,16 +8959,16 @@
     </row>
     <row r="68" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A68" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>158</v>
@@ -9020,7 +9026,7 @@
     </row>
     <row r="69" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A69" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4" t="s">
@@ -9060,16 +9066,16 @@
     </row>
     <row r="70" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A70" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>140</v>
@@ -9127,14 +9133,14 @@
     </row>
     <row r="71" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A71" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B71" s="9"/>
       <c r="C71" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>146</v>
@@ -9192,16 +9198,16 @@
     </row>
     <row r="72" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A72" s="9" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>152</v>
@@ -9259,16 +9265,16 @@
     </row>
     <row r="73" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A73" s="9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>158</v>
@@ -9326,7 +9332,7 @@
     </row>
     <row r="74" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A74" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4" t="s">
@@ -9366,16 +9372,16 @@
     </row>
     <row r="75" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A75" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>140</v>
@@ -9433,14 +9439,14 @@
     </row>
     <row r="76" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A76" s="9" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B76" s="9"/>
       <c r="C76" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>146</v>
@@ -9498,16 +9504,16 @@
     </row>
     <row r="77" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A77" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>381</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>379</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>152</v>
@@ -9565,16 +9571,16 @@
     </row>
     <row r="78" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A78" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>158</v>
@@ -9632,7 +9638,7 @@
     </row>
     <row r="79" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A79" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4" t="s">
@@ -9672,16 +9678,16 @@
     </row>
     <row r="80" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A80" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>140</v>
@@ -9739,14 +9745,14 @@
     </row>
     <row r="81" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A81" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B81" s="9"/>
       <c r="C81" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>146</v>
@@ -9804,16 +9810,16 @@
     </row>
     <row r="82" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A82" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>387</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>385</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>152</v>
@@ -9871,16 +9877,16 @@
     </row>
     <row r="83" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A83" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>158</v>
@@ -10853,7 +10859,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -10873,16 +10879,16 @@
         <v>180</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>185</v>
@@ -10891,7 +10897,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -10905,19 +10911,19 @@
         <v>283</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -10934,22 +10940,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -10966,22 +10972,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11004,16 +11010,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11054,10 +11060,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11073,25 +11079,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>185</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11102,22 +11108,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -11126,7 +11132,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11134,22 +11140,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11166,22 +11172,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11190,7 +11196,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11198,22 +11204,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="440">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -962,11 +962,14 @@
   <si>
     <t xml:space="preserve">
 master：窗口1、.\run_distributed_v2.ps1 -Mode master -WebPort 8089
-worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 0 -WorkerCount 2 -TotalWorkerCount 4 -TokenFile D:\ckj_locust\user_token.txt
-worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 2 -WorkerCount 2 -TotalWorkerCount 4 -TokenFile C:\ckj_locust\user_token.txt</t>
-  </si>
-  <si>
-    <t>10m==3(100)+3(300)+4(500)</t>
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 0 -WorkerCount 3 -TotalWorkerCount 5 -TokenFile D:\ckj_locust\user_token.txt
+worker1：.\run_distributed_v2.ps1 -Mode worker -Headless -MasterHost 20.1.2.240 -WorkerIndexOffset 3 -WorkerCount 2 -TotalWorkerCount 5 -TokenFile C:\ckj_locust\user_token.txt</t>
+  </si>
+  <si>
+    <t>100&gt;300&gt;500</t>
+  </si>
+  <si>
+    <t>15m==5(100)+5(300)+5(500)，逐渐升高</t>
   </si>
   <si>
     <t>W01</t>
@@ -5283,14 +5286,14 @@
       <c r="E8" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F8" s="9">
-        <v>500</v>
+      <c r="F8" s="9" t="s">
+        <v>306</v>
       </c>
       <c r="G8" s="9">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>14</v>
@@ -5336,7 +5339,7 @@
     </row>
     <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A9" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
@@ -5376,7 +5379,7 @@
     </row>
     <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A10" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -5443,7 +5446,7 @@
     </row>
     <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A11" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
@@ -5510,7 +5513,7 @@
     </row>
     <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A12" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>14</v>
@@ -5577,13 +5580,13 @@
     </row>
     <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A13" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>72</v>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A14" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
@@ -5684,7 +5687,7 @@
     </row>
     <row r="15" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A15" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>14</v>
@@ -5751,7 +5754,7 @@
     </row>
     <row r="16" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A16" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>14</v>
@@ -5818,7 +5821,7 @@
     </row>
     <row r="17" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A17" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>14</v>
@@ -5885,13 +5888,13 @@
     </row>
     <row r="18" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A18" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>77</v>
@@ -5952,7 +5955,7 @@
     </row>
     <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A19" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4" t="s">
@@ -5992,7 +5995,7 @@
     </row>
     <row r="20" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A20" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>14</v>
@@ -6059,7 +6062,7 @@
     </row>
     <row r="21" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A21" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>14</v>
@@ -6126,7 +6129,7 @@
     </row>
     <row r="22" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A22" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>14</v>
@@ -6193,13 +6196,13 @@
     </row>
     <row r="23" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A23" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>82</v>
@@ -6260,7 +6263,7 @@
     </row>
     <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A24" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
@@ -6300,7 +6303,7 @@
     </row>
     <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A25" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>14</v>
@@ -6367,7 +6370,7 @@
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A26" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>14</v>
@@ -6434,7 +6437,7 @@
     </row>
     <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A27" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>14</v>
@@ -6501,13 +6504,13 @@
     </row>
     <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A28" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>85</v>
@@ -6568,7 +6571,7 @@
     </row>
     <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A29" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
@@ -6608,7 +6611,7 @@
     </row>
     <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A30" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>14</v>
@@ -6675,7 +6678,7 @@
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A31" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>14</v>
@@ -6742,7 +6745,7 @@
     </row>
     <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A32" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>14</v>
@@ -6809,13 +6812,13 @@
     </row>
     <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A33" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>88</v>
@@ -6876,7 +6879,7 @@
     </row>
     <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A34" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4" t="s">
@@ -6916,7 +6919,7 @@
     </row>
     <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A35" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>14</v>
@@ -6983,7 +6986,7 @@
     </row>
     <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A36" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>14</v>
@@ -7050,7 +7053,7 @@
     </row>
     <row r="37" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A37" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>14</v>
@@ -7117,13 +7120,13 @@
     </row>
     <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A38" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>91</v>
@@ -7184,7 +7187,7 @@
     </row>
     <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A39" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4" t="s">
@@ -7224,7 +7227,7 @@
     </row>
     <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A40" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>14</v>
@@ -7233,7 +7236,7 @@
         <v>297</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>140</v>
@@ -7291,7 +7294,7 @@
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A41" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>14</v>
@@ -7300,7 +7303,7 @@
         <v>297</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>146</v>
@@ -7358,7 +7361,7 @@
     </row>
     <row r="42" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A42" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>14</v>
@@ -7367,7 +7370,7 @@
         <v>297</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>152</v>
@@ -7425,16 +7428,16 @@
     </row>
     <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A43" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>158</v>
@@ -7492,7 +7495,7 @@
     </row>
     <row r="44" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A44" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4" t="s">
@@ -7532,7 +7535,7 @@
     </row>
     <row r="45" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A45" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>14</v>
@@ -7599,7 +7602,7 @@
     </row>
     <row r="46" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A46" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>14</v>
@@ -7666,7 +7669,7 @@
     </row>
     <row r="47" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A47" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>14</v>
@@ -7733,13 +7736,13 @@
     </row>
     <row r="48" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A48" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>98</v>
@@ -7800,7 +7803,7 @@
     </row>
     <row r="49" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A49" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
@@ -7840,7 +7843,7 @@
     </row>
     <row r="50" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A50" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>14</v>
@@ -7907,7 +7910,7 @@
     </row>
     <row r="51" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A51" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>14</v>
@@ -7974,7 +7977,7 @@
     </row>
     <row r="52" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A52" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>14</v>
@@ -8041,13 +8044,13 @@
     </row>
     <row r="53" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A53" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>101</v>
@@ -8108,7 +8111,7 @@
     </row>
     <row r="54" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A54" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
@@ -8148,16 +8151,16 @@
     </row>
     <row r="55" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A55" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>140</v>
@@ -8215,14 +8218,14 @@
     </row>
     <row r="56" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A56" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B56" s="9"/>
       <c r="C56" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>146</v>
@@ -8280,16 +8283,16 @@
     </row>
     <row r="57" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A57" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>152</v>
@@ -8347,16 +8350,16 @@
     </row>
     <row r="58" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A58" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>158</v>
@@ -8414,7 +8417,7 @@
     </row>
     <row r="59" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A59" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4" t="s">
@@ -8454,16 +8457,16 @@
     </row>
     <row r="60" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A60" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>140</v>
@@ -8521,14 +8524,14 @@
     </row>
     <row r="61" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A61" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B61" s="9"/>
       <c r="C61" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>146</v>
@@ -8586,16 +8589,16 @@
     </row>
     <row r="62" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A62" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>152</v>
@@ -8653,16 +8656,16 @@
     </row>
     <row r="63" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A63" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>158</v>
@@ -8720,7 +8723,7 @@
     </row>
     <row r="64" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A64" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4" t="s">
@@ -8760,16 +8763,16 @@
     </row>
     <row r="65" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A65" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>140</v>
@@ -8827,14 +8830,14 @@
     </row>
     <row r="66" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A66" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>146</v>
@@ -8892,16 +8895,16 @@
     </row>
     <row r="67" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A67" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>152</v>
@@ -8959,16 +8962,16 @@
     </row>
     <row r="68" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A68" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>158</v>
@@ -9026,7 +9029,7 @@
     </row>
     <row r="69" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A69" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4" t="s">
@@ -9066,16 +9069,16 @@
     </row>
     <row r="70" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A70" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>140</v>
@@ -9133,14 +9136,14 @@
     </row>
     <row r="71" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A71" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B71" s="9"/>
       <c r="C71" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>146</v>
@@ -9198,16 +9201,16 @@
     </row>
     <row r="72" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A72" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>152</v>
@@ -9265,16 +9268,16 @@
     </row>
     <row r="73" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A73" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>158</v>
@@ -9332,7 +9335,7 @@
     </row>
     <row r="74" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A74" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4" t="s">
@@ -9372,16 +9375,16 @@
     </row>
     <row r="75" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A75" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>140</v>
@@ -9439,14 +9442,14 @@
     </row>
     <row r="76" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A76" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B76" s="9"/>
       <c r="C76" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>146</v>
@@ -9504,16 +9507,16 @@
     </row>
     <row r="77" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A77" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>152</v>
@@ -9571,16 +9574,16 @@
     </row>
     <row r="78" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A78" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>158</v>
@@ -9638,7 +9641,7 @@
     </row>
     <row r="79" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A79" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4" t="s">
@@ -9678,16 +9681,16 @@
     </row>
     <row r="80" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A80" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>140</v>
@@ -9745,14 +9748,14 @@
     </row>
     <row r="81" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A81" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B81" s="9"/>
       <c r="C81" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>146</v>
@@ -9810,16 +9813,16 @@
     </row>
     <row r="82" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A82" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>152</v>
@@ -9877,16 +9880,16 @@
     </row>
     <row r="83" s="8" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A83" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>158</v>
@@ -10859,7 +10862,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -10879,16 +10882,16 @@
         <v>180</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>185</v>
@@ -10897,7 +10900,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -10911,19 +10914,19 @@
         <v>283</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -10940,22 +10943,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -10972,22 +10975,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11010,16 +11013,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11060,10 +11063,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11079,25 +11082,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>185</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11108,22 +11111,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -11132,7 +11135,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11140,22 +11143,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11172,22 +11175,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11196,7 +11199,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11204,22 +11207,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="439">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -290,15 +290,6 @@
     <t>/gacha/pay/result</t>
   </si>
   <si>
-    <t>I05</t>
-  </si>
-  <si>
-    <t>支付订单列表</t>
-  </si>
-  <si>
-    <t>/gacha/order/list?cursor=0&amp;status=-1</t>
-  </si>
-  <si>
     <t>I06</t>
   </si>
   <si>
@@ -901,6 +892,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>成功 QPS</t>
     </r>
     <r>
@@ -1040,6 +1038,9 @@
   </si>
   <si>
     <t>R17</t>
+  </si>
+  <si>
+    <t>支付订单列表</t>
   </si>
   <si>
     <t>R18</t>
@@ -3821,7 +3822,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3992,7 +3993,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:9">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -4008,9 +4009,11 @@
         <v>67</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="G8" s="2">
+        <v>500</v>
+      </c>
       <c r="H8" s="4" t="s">
         <v>69</v>
       </c>
@@ -4019,29 +4022,29 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="4">
         <v>500</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>80</v>
@@ -4049,28 +4052,28 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:9">
       <c r="A10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2">
+        <v>500</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="4">
-        <v>500</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>80</v>
@@ -4080,69 +4083,69 @@
       <c r="A11" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="4">
         <v>500</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:9">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="2">
         <v>500</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:9">
-      <c r="A13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>100</v>
       </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:9">
+      <c r="A13" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>66</v>
@@ -4157,7 +4160,7 @@
         <v>500</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>103</v>
@@ -4171,7 +4174,7 @@
         <v>105</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>66</v>
@@ -4186,21 +4189,21 @@
         <v>500</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:9">
       <c r="A15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>66</v>
@@ -4215,21 +4218,21 @@
         <v>500</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:9">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>66</v>
@@ -4244,21 +4247,21 @@
         <v>500</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:9">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>66</v>
@@ -4273,39 +4276,10 @@
         <v>500</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1" spans="1:9">
-      <c r="A18" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="2">
-        <v>500</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4313,10 +4287,10 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E4:E102">
+    <dataValidation type="list" allowBlank="1" sqref="E4:E7 E8:E101">
       <formula1>"是,否,待确认"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F4:F102">
+    <dataValidation type="list" allowBlank="1" sqref="F4:F7 F8:F101">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4344,7 +4318,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:12">
@@ -4363,37 +4337,37 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:12">
       <c r="A3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>8</v>
@@ -4401,13 +4375,13 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:12">
       <c r="A4" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D4" s="4">
         <v>50</v>
@@ -4416,34 +4390,34 @@
         <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D5" s="2">
         <v>100</v>
@@ -4452,34 +4426,34 @@
         <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>67</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D6" s="4">
         <v>300</v>
@@ -4488,34 +4462,34 @@
         <v>10</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>148</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>67</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D7" s="2">
         <v>500</v>
@@ -4524,34 +4498,34 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>67</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D8" s="4">
         <v>500</v>
@@ -4560,34 +4534,34 @@
         <v>500</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>67</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D9" s="2">
         <v>500</v>
@@ -4596,34 +4570,34 @@
         <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:12">
       <c r="A10" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D10" s="4">
         <v>500</v>
@@ -4632,23 +4606,23 @@
         <v>10</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>176</v>
-      </c>
       <c r="J10" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4680,7 +4654,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
@@ -4695,25 +4669,25 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
       <c r="A3" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>8</v>
@@ -4721,184 +4695,184 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8">
       <c r="A4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8">
       <c r="A5" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8">
       <c r="A6" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8">
       <c r="A7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8">
       <c r="A8" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8">
       <c r="A9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8">
       <c r="A10" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4928,7 +4902,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:9">
@@ -4944,28 +4918,28 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:9">
       <c r="A3" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>242</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>245</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I3" s="19" t="s">
         <v>8</v>
@@ -4973,7 +4947,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:9">
       <c r="A4" s="20" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B4" s="20">
         <v>500</v>
@@ -4982,19 +4956,19 @@
         <v>500</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I4" s="20" t="s">
         <v>14</v>
@@ -5002,28 +4976,28 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:9">
       <c r="A5" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" s="21" t="s">
         <v>252</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>255</v>
       </c>
       <c r="G5" s="21" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I5" s="21" t="s">
         <v>14</v>
@@ -5031,28 +5005,28 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:9">
       <c r="A6" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="G6" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="H6" s="20" t="s">
         <v>259</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>262</v>
       </c>
       <c r="I6" s="20" t="s">
         <v>14</v>
@@ -5060,60 +5034,60 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:9">
       <c r="A7" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="E7" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="G7" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="I7" s="21" t="s">
         <v>266</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:9">
       <c r="A8" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="E8" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="G8" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="I8" s="20" t="s">
         <v>273</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -5152,7 +5126,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:25">
@@ -5184,94 +5158,94 @@
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:25">
       <c r="A3" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="K3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>286</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="X3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:25">
       <c r="A4" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F4" s="4">
         <v>50</v>
@@ -5280,7 +5254,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>14</v>
@@ -5320,26 +5294,26 @@
         <v>14</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
     <row r="5" s="8" customFormat="1" ht="207" customHeight="1" spans="1:25">
       <c r="A5" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>64</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F5" s="9">
         <v>100</v>
@@ -5348,7 +5322,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I5" s="9">
         <v>14324</v>
@@ -5381,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="U5" s="14">
         <v>0.0166</v>
@@ -5397,19 +5371,19 @@
     </row>
     <row r="6" s="8" customFormat="1" ht="153" customHeight="1" spans="1:25">
       <c r="A6" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>64</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F6" s="9">
         <v>300</v>
@@ -5418,7 +5392,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I6" s="9">
         <v>24431</v>
@@ -5451,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="U6" s="14">
         <v>0.0209</v>
@@ -5467,19 +5441,19 @@
     </row>
     <row r="7" s="8" customFormat="1" ht="182" customHeight="1" spans="1:25">
       <c r="A7" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>64</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F7" s="9">
         <v>500</v>
@@ -5488,7 +5462,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I7" s="9">
         <v>36167</v>
@@ -5521,7 +5495,7 @@
         <v>14</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="U7" s="14">
         <v>0.0214</v>
@@ -5539,28 +5513,28 @@
     </row>
     <row r="8" s="8" customFormat="1" ht="287" customHeight="1" spans="1:25">
       <c r="A8" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>64</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G8" s="9">
         <v>10</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I8" s="9">
         <v>142276</v>
@@ -5589,7 +5563,7 @@
         <v>43.9</v>
       </c>
       <c r="R8" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="S8" s="9">
         <v>0</v>
@@ -5607,23 +5581,23 @@
         <v>15</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Y8" s="9"/>
     </row>
     <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A9" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F9" s="4">
         <v>50</v>
@@ -5632,7 +5606,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
@@ -5649,35 +5623,35 @@
       <c r="U9" s="13"/>
       <c r="V9" s="12"/>
       <c r="W9" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
     </row>
     <row r="10" customFormat="1" ht="310" customHeight="1" spans="1:25">
       <c r="A10" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G10" s="2">
         <v>10</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>14</v>
@@ -5726,19 +5700,19 @@
     </row>
     <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A11" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>72</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F11" s="4">
         <v>500</v>
@@ -5747,7 +5721,7 @@
         <v>500</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>14</v>
@@ -5796,17 +5770,17 @@
     </row>
     <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A12" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F12" s="4">
         <v>50</v>
@@ -5815,7 +5789,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
@@ -5832,26 +5806,26 @@
       <c r="U12" s="13"/>
       <c r="V12" s="12"/>
       <c r="W12" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
     </row>
     <row r="13" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A13" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>77</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F13" s="9">
         <v>100</v>
@@ -5860,7 +5834,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>14</v>
@@ -5909,19 +5883,19 @@
     </row>
     <row r="14" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A14" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>77</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F14" s="9">
         <v>300</v>
@@ -5930,7 +5904,7 @@
         <v>10</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>14</v>
@@ -5979,19 +5953,19 @@
     </row>
     <row r="15" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A15" s="9" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>77</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F15" s="9">
         <v>500</v>
@@ -6000,7 +5974,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>14</v>
@@ -6049,19 +6023,19 @@
     </row>
     <row r="16" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A16" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>77</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F16" s="9">
         <v>500</v>
@@ -6070,7 +6044,7 @@
         <v>500</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>14</v>
@@ -6119,17 +6093,17 @@
     </row>
     <row r="17" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A17" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F17" s="4">
         <v>50</v>
@@ -6138,7 +6112,7 @@
         <v>10</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
@@ -6155,26 +6129,26 @@
       <c r="U17" s="13"/>
       <c r="V17" s="12"/>
       <c r="W17" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
     </row>
     <row r="18" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A18" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>82</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F18" s="9">
         <v>100</v>
@@ -6183,7 +6157,7 @@
         <v>10</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>14</v>
@@ -6232,19 +6206,19 @@
     </row>
     <row r="19" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A19" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>82</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F19" s="9">
         <v>300</v>
@@ -6253,7 +6227,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>14</v>
@@ -6302,19 +6276,19 @@
     </row>
     <row r="20" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A20" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>82</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F20" s="9">
         <v>500</v>
@@ -6323,7 +6297,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>14</v>
@@ -6372,19 +6346,19 @@
     </row>
     <row r="21" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A21" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>82</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F21" s="9">
         <v>500</v>
@@ -6393,7 +6367,7 @@
         <v>500</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>14</v>
@@ -6442,17 +6416,17 @@
     </row>
     <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A22" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F22" s="4">
         <v>50</v>
@@ -6461,7 +6435,7 @@
         <v>10</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
@@ -6478,26 +6452,26 @@
       <c r="U22" s="13"/>
       <c r="V22" s="12"/>
       <c r="W22" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
     </row>
     <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A23" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>324</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F23" s="2">
         <v>100</v>
@@ -6506,7 +6480,7 @@
         <v>10</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>14</v>
@@ -6555,19 +6529,19 @@
     </row>
     <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A24" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>85</v>
+        <v>324</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F24" s="4">
         <v>300</v>
@@ -6576,7 +6550,7 @@
         <v>10</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>14</v>
@@ -6625,19 +6599,19 @@
     </row>
     <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A25" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>85</v>
+        <v>324</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F25" s="2">
         <v>500</v>
@@ -6646,7 +6620,7 @@
         <v>10</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>14</v>
@@ -6695,19 +6669,19 @@
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A26" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>85</v>
+        <v>324</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F26" s="4">
         <v>500</v>
@@ -6716,7 +6690,7 @@
         <v>500</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>14</v>
@@ -6765,17 +6739,17 @@
     </row>
     <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A27" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F27" s="4">
         <v>50</v>
@@ -6784,7 +6758,7 @@
         <v>10</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
@@ -6801,26 +6775,26 @@
       <c r="U27" s="13"/>
       <c r="V27" s="12"/>
       <c r="W27" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
     </row>
     <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A28" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F28" s="2">
         <v>100</v>
@@ -6829,7 +6803,7 @@
         <v>10</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>14</v>
@@ -6878,19 +6852,19 @@
     </row>
     <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F29" s="4">
         <v>300</v>
@@ -6899,7 +6873,7 @@
         <v>10</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>14</v>
@@ -6948,19 +6922,19 @@
     </row>
     <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A30" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F30" s="2">
         <v>500</v>
@@ -6969,7 +6943,7 @@
         <v>10</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>14</v>
@@ -7018,19 +6992,19 @@
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F31" s="4">
         <v>500</v>
@@ -7039,7 +7013,7 @@
         <v>500</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>14</v>
@@ -7088,17 +7062,17 @@
     </row>
     <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F32" s="4">
         <v>50</v>
@@ -7107,7 +7081,7 @@
         <v>10</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
@@ -7124,26 +7098,26 @@
       <c r="U32" s="13"/>
       <c r="V32" s="12"/>
       <c r="W32" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
     </row>
     <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A33" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F33" s="2">
         <v>100</v>
@@ -7152,7 +7126,7 @@
         <v>10</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>14</v>
@@ -7201,19 +7175,19 @@
     </row>
     <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F34" s="4">
         <v>300</v>
@@ -7222,7 +7196,7 @@
         <v>10</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>14</v>
@@ -7271,19 +7245,19 @@
     </row>
     <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A35" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F35" s="2">
         <v>500</v>
@@ -7292,7 +7266,7 @@
         <v>10</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>14</v>
@@ -7341,19 +7315,19 @@
     </row>
     <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F36" s="4">
         <v>500</v>
@@ -7362,7 +7336,7 @@
         <v>500</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>14</v>
@@ -7411,17 +7385,17 @@
     </row>
     <row r="37" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F37" s="4">
         <v>50</v>
@@ -7430,7 +7404,7 @@
         <v>10</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
@@ -7447,26 +7421,26 @@
       <c r="U37" s="13"/>
       <c r="V37" s="12"/>
       <c r="W37" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
     </row>
     <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A38" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F38" s="2">
         <v>100</v>
@@ -7475,7 +7449,7 @@
         <v>10</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>14</v>
@@ -7524,19 +7498,19 @@
     </row>
     <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F39" s="4">
         <v>300</v>
@@ -7545,7 +7519,7 @@
         <v>10</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>14</v>
@@ -7594,19 +7568,19 @@
     </row>
     <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A40" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F40" s="2">
         <v>500</v>
@@ -7615,7 +7589,7 @@
         <v>10</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>14</v>
@@ -7664,19 +7638,19 @@
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F41" s="4">
         <v>500</v>
@@ -7685,7 +7659,7 @@
         <v>500</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>14</v>
@@ -7734,17 +7708,17 @@
     </row>
     <row r="42" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F42" s="4">
         <v>50</v>
@@ -7753,7 +7727,7 @@
         <v>10</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12"/>
@@ -7770,26 +7744,26 @@
       <c r="U42" s="13"/>
       <c r="V42" s="12"/>
       <c r="W42" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X42" s="4"/>
       <c r="Y42" s="4"/>
     </row>
     <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A43" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F43" s="2">
         <v>100</v>
@@ -7798,7 +7772,7 @@
         <v>10</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>14</v>
@@ -7847,19 +7821,19 @@
     </row>
     <row r="44" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F44" s="4">
         <v>300</v>
@@ -7868,7 +7842,7 @@
         <v>10</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>14</v>
@@ -7917,19 +7891,19 @@
     </row>
     <row r="45" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A45" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F45" s="2">
         <v>500</v>
@@ -7938,7 +7912,7 @@
         <v>10</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>14</v>
@@ -7987,19 +7961,19 @@
     </row>
     <row r="46" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F46" s="4">
         <v>500</v>
@@ -8008,7 +7982,7 @@
         <v>500</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>14</v>
@@ -8057,17 +8031,17 @@
     </row>
     <row r="47" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F47" s="4">
         <v>50</v>
@@ -8076,7 +8050,7 @@
         <v>10</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12"/>
@@ -8093,26 +8067,26 @@
       <c r="U47" s="13"/>
       <c r="V47" s="12"/>
       <c r="W47" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X47" s="4"/>
       <c r="Y47" s="4"/>
     </row>
     <row r="48" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A48" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F48" s="9">
         <v>100</v>
@@ -8121,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>14</v>
@@ -8170,19 +8144,19 @@
     </row>
     <row r="49" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A49" s="9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F49" s="9">
         <v>300</v>
@@ -8191,7 +8165,7 @@
         <v>10</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>14</v>
@@ -8240,19 +8214,19 @@
     </row>
     <row r="50" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A50" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F50" s="9">
         <v>500</v>
@@ -8261,7 +8235,7 @@
         <v>10</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>14</v>
@@ -8310,19 +8284,19 @@
     </row>
     <row r="51" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A51" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F51" s="9">
         <v>500</v>
@@ -8331,7 +8305,7 @@
         <v>500</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I51" s="9" t="s">
         <v>14</v>
@@ -8380,17 +8354,17 @@
     </row>
     <row r="52" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A52" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F52" s="4">
         <v>50</v>
@@ -8399,7 +8373,7 @@
         <v>10</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
@@ -8416,26 +8390,26 @@
       <c r="U52" s="13"/>
       <c r="V52" s="12"/>
       <c r="W52" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X52" s="4"/>
       <c r="Y52" s="4"/>
     </row>
     <row r="53" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A53" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="E53" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F53" s="9">
         <v>100</v>
@@ -8444,7 +8418,7 @@
         <v>10</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>14</v>
@@ -8493,17 +8467,17 @@
     </row>
     <row r="54" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A54" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B54" s="9"/>
       <c r="C54" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F54" s="9">
         <v>300</v>
@@ -8512,7 +8486,7 @@
         <v>10</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>14</v>
@@ -8561,19 +8535,19 @@
     </row>
     <row r="55" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A55" s="9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F55" s="9">
         <v>500</v>
@@ -8582,7 +8556,7 @@
         <v>10</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I55" s="9" t="s">
         <v>14</v>
@@ -8631,19 +8605,19 @@
     </row>
     <row r="56" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A56" s="9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F56" s="9">
         <v>500</v>
@@ -8652,7 +8626,7 @@
         <v>500</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>14</v>
@@ -8701,17 +8675,17 @@
     </row>
     <row r="57" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F57" s="4">
         <v>50</v>
@@ -8720,7 +8694,7 @@
         <v>10</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I57" s="12"/>
       <c r="J57" s="12"/>
@@ -8737,26 +8711,26 @@
       <c r="U57" s="13"/>
       <c r="V57" s="12"/>
       <c r="W57" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X57" s="4"/>
       <c r="Y57" s="4"/>
     </row>
     <row r="58" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A58" s="9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F58" s="9">
         <v>100</v>
@@ -8765,7 +8739,7 @@
         <v>10</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I58" s="9" t="s">
         <v>14</v>
@@ -8814,17 +8788,17 @@
     </row>
     <row r="59" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A59" s="9" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B59" s="9"/>
       <c r="C59" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F59" s="9">
         <v>300</v>
@@ -8833,7 +8807,7 @@
         <v>10</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I59" s="9" t="s">
         <v>14</v>
@@ -8882,19 +8856,19 @@
     </row>
     <row r="60" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A60" s="9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F60" s="9">
         <v>500</v>
@@ -8903,7 +8877,7 @@
         <v>10</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I60" s="9" t="s">
         <v>14</v>
@@ -8952,19 +8926,19 @@
     </row>
     <row r="61" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A61" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F61" s="9">
         <v>500</v>
@@ -8973,7 +8947,7 @@
         <v>500</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I61" s="9" t="s">
         <v>14</v>
@@ -9022,17 +8996,17 @@
     </row>
     <row r="62" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F62" s="4">
         <v>50</v>
@@ -9041,7 +9015,7 @@
         <v>10</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I62" s="12"/>
       <c r="J62" s="12"/>
@@ -9058,26 +9032,26 @@
       <c r="U62" s="13"/>
       <c r="V62" s="12"/>
       <c r="W62" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X62" s="4"/>
       <c r="Y62" s="4"/>
     </row>
     <row r="63" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A63" s="9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F63" s="9">
         <v>100</v>
@@ -9086,7 +9060,7 @@
         <v>10</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I63" s="9" t="s">
         <v>14</v>
@@ -9135,17 +9109,17 @@
     </row>
     <row r="64" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A64" s="9" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B64" s="9"/>
       <c r="C64" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F64" s="9">
         <v>300</v>
@@ -9154,7 +9128,7 @@
         <v>10</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I64" s="9" t="s">
         <v>14</v>
@@ -9203,19 +9177,19 @@
     </row>
     <row r="65" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A65" s="9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F65" s="9">
         <v>500</v>
@@ -9224,7 +9198,7 @@
         <v>10</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>14</v>
@@ -9273,19 +9247,19 @@
     </row>
     <row r="66" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A66" s="9" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F66" s="9">
         <v>500</v>
@@ -9294,7 +9268,7 @@
         <v>500</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>14</v>
@@ -9343,17 +9317,17 @@
     </row>
     <row r="67" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E67" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F67" s="4">
         <v>50</v>
@@ -9362,7 +9336,7 @@
         <v>10</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
@@ -9379,26 +9353,26 @@
       <c r="U67" s="13"/>
       <c r="V67" s="12"/>
       <c r="W67" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X67" s="4"/>
       <c r="Y67" s="4"/>
     </row>
     <row r="68" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A68" s="9" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F68" s="9">
         <v>100</v>
@@ -9407,7 +9381,7 @@
         <v>10</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I68" s="9" t="s">
         <v>14</v>
@@ -9456,17 +9430,17 @@
     </row>
     <row r="69" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A69" s="9" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B69" s="9"/>
       <c r="C69" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F69" s="9">
         <v>300</v>
@@ -9475,7 +9449,7 @@
         <v>10</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I69" s="9" t="s">
         <v>14</v>
@@ -9524,19 +9498,19 @@
     </row>
     <row r="70" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A70" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F70" s="9">
         <v>500</v>
@@ -9545,7 +9519,7 @@
         <v>10</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I70" s="9" t="s">
         <v>14</v>
@@ -9594,19 +9568,19 @@
     </row>
     <row r="71" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A71" s="9" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F71" s="9">
         <v>500</v>
@@ -9615,7 +9589,7 @@
         <v>500</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I71" s="9" t="s">
         <v>14</v>
@@ -9664,17 +9638,17 @@
     </row>
     <row r="72" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A72" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F72" s="4">
         <v>50</v>
@@ -9683,7 +9657,7 @@
         <v>10</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I72" s="12"/>
       <c r="J72" s="12"/>
@@ -9700,26 +9674,26 @@
       <c r="U72" s="13"/>
       <c r="V72" s="12"/>
       <c r="W72" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X72" s="4"/>
       <c r="Y72" s="4"/>
     </row>
     <row r="73" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A73" s="9" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F73" s="9">
         <v>100</v>
@@ -9728,7 +9702,7 @@
         <v>10</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>14</v>
@@ -9777,17 +9751,17 @@
     </row>
     <row r="74" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A74" s="9" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F74" s="9">
         <v>300</v>
@@ -9796,7 +9770,7 @@
         <v>10</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I74" s="9" t="s">
         <v>14</v>
@@ -9845,19 +9819,19 @@
     </row>
     <row r="75" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A75" s="9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F75" s="9">
         <v>500</v>
@@ -9866,7 +9840,7 @@
         <v>10</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I75" s="9" t="s">
         <v>14</v>
@@ -9915,19 +9889,19 @@
     </row>
     <row r="76" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A76" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F76" s="9">
         <v>500</v>
@@ -9936,7 +9910,7 @@
         <v>500</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I76" s="9" t="s">
         <v>14</v>
@@ -9985,17 +9959,17 @@
     </row>
     <row r="77" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A77" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F77" s="4">
         <v>50</v>
@@ -10004,7 +9978,7 @@
         <v>10</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I77" s="12"/>
       <c r="J77" s="12"/>
@@ -10021,26 +9995,26 @@
       <c r="U77" s="13"/>
       <c r="V77" s="12"/>
       <c r="W77" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="X77" s="4"/>
       <c r="Y77" s="4"/>
     </row>
     <row r="78" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A78" s="9" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F78" s="9">
         <v>100</v>
@@ -10049,7 +10023,7 @@
         <v>10</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I78" s="9" t="s">
         <v>14</v>
@@ -10098,17 +10072,17 @@
     </row>
     <row r="79" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A79" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B79" s="9"/>
       <c r="C79" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F79" s="9">
         <v>300</v>
@@ -10117,7 +10091,7 @@
         <v>10</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I79" s="9" t="s">
         <v>14</v>
@@ -10166,19 +10140,19 @@
     </row>
     <row r="80" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A80" s="9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F80" s="9">
         <v>500</v>
@@ -10187,7 +10161,7 @@
         <v>10</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>14</v>
@@ -10236,19 +10210,19 @@
     </row>
     <row r="81" s="8" customFormat="1" ht="24" customHeight="1" spans="1:25">
       <c r="A81" s="9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F81" s="9">
         <v>500</v>
@@ -10257,7 +10231,7 @@
         <v>500</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I81" s="9" t="s">
         <v>14</v>
@@ -11245,7 +11219,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="W4:W9 W10:W99">
+    <dataValidation type="list" allowBlank="1" sqref="W4:W99">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11275,7 +11249,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -11292,28 +11266,28 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>397</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -11324,22 +11298,22 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -11356,22 +11330,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -11388,22 +11362,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11426,16 +11400,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11476,10 +11450,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11495,25 +11469,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="F11" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>418</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>420</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11524,31 +11498,31 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="G12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11556,23 +11530,23 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
       </c>
@@ -11580,7 +11554,7 @@
         <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>14</v>
@@ -11588,23 +11562,23 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>436</v>
-      </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
       </c>
@@ -11612,7 +11586,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11620,22 +11594,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>
@@ -11644,7 +11618,7 @@
         <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="437">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1001,11 +1001,15 @@
     <t>只读节点最高达14%，读写节点最高达4%</t>
   </si>
   <si>
-    <t>1.在长达 15 分钟的测试中，系统平均每秒处理了 53个请求，不具有报错。
+    <t>1.在长达 15 分钟的压力测试中，系统平均每秒处理了 53个请求，不具有报错。
 2.小程序有明显白屏卡顿延迟，但未有大面积接口崩溃情况。</t>
   </si>
   <si>
     <t>R12</t>
+  </si>
+  <si>
+    <t>1.在长达 10 分钟的压力测试中，系统平均每秒处理了 48个请求，不具有报错。
+2.小程序未有卡顿等情况</t>
   </si>
   <si>
     <t>W04</t>
@@ -1578,7 +1582,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1636,6 +1640,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2008,7 +2018,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2032,16 +2042,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2050,89 +2060,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2188,6 +2198,9 @@
     <xf numFmtId="10" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2195,6 +2208,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3372,6 +3391,258 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>417195</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1186815</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="图片 26"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27247215" y="16304895"/>
+          <a:ext cx="981075" cy="640080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>262890</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1548130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1421765</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2326640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="图片 27"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27304365" y="17435830"/>
+          <a:ext cx="1158875" cy="778510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>242570</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2700655</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1336675</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3331845</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="图片 28"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27284045" y="18588355"/>
+          <a:ext cx="1094105" cy="631190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1619885</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>537845</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2459990</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1184275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="图片 29"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28661360" y="16425545"/>
+          <a:ext cx="840105" cy="646430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1652905</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1671320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>29210</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2346325</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="图片 30"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28694380" y="17559020"/>
+          <a:ext cx="1119505" cy="675005"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1872615</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2836545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2727960</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3350895</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="图片 31"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28914090" y="18724245"/>
+          <a:ext cx="855345" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3663,237 +3934,237 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18" style="27" customWidth="1"/>
-    <col min="2" max="2" width="34" style="27" customWidth="1"/>
-    <col min="3" max="3" width="42" style="27" customWidth="1"/>
-    <col min="4" max="4" width="14" style="27" customWidth="1"/>
-    <col min="5" max="5" width="22.75" style="27" customWidth="1"/>
-    <col min="6" max="6" width="25.25" style="27" customWidth="1"/>
-    <col min="7" max="7" width="14" style="27" customWidth="1"/>
-    <col min="8" max="8" width="30" style="27" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="27"/>
+    <col min="1" max="1" width="18" style="30" customWidth="1"/>
+    <col min="2" max="2" width="34" style="30" customWidth="1"/>
+    <col min="3" max="3" width="42" style="30" customWidth="1"/>
+    <col min="4" max="4" width="14" style="30" customWidth="1"/>
+    <col min="5" max="5" width="22.75" style="30" customWidth="1"/>
+    <col min="6" max="6" width="25.25" style="30" customWidth="1"/>
+    <col min="7" max="7" width="14" style="30" customWidth="1"/>
+    <col min="8" max="8" width="30" style="30" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="32" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="30" t="s">
+      <c r="F4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="33" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:8">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="33" t="s">
+      <c r="D5" s="37"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="30" t="s">
+      <c r="D6" s="37"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="33" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="36">
         <v>500</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="33" t="s">
+      <c r="D7" s="37"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="D8" s="37"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="33" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="33" t="s">
+      <c r="D9" s="39"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8">
       <c r="A14" s="7" t="s">
@@ -5141,176 +5412,176 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:9">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="27" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:9">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="28">
         <v>500</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="28">
         <v>500</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:9">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="29" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:9">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:9">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="G7" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="26" t="s">
+      <c r="G7" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="I7" s="26" t="s">
+      <c r="I7" s="29" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:9">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="G8" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="25" t="s">
+      <c r="G8" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="I8" s="25" t="s">
+      <c r="I8" s="28" t="s">
         <v>273</v>
       </c>
     </row>
@@ -5794,7 +6065,7 @@
       <c r="U8" s="12">
         <v>433</v>
       </c>
-      <c r="V8" s="12" t="s">
+      <c r="V8" s="25" t="s">
         <v>15</v>
       </c>
       <c r="W8" s="12" t="s">
@@ -5867,8 +6138,8 @@
       <c r="U9" s="2">
         <v>520</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>29</v>
+      <c r="V9" s="25" t="s">
+        <v>15</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>311</v>
@@ -5902,46 +6173,52 @@
       <c r="H10" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="I10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="21" t="e">
+      <c r="I10" s="14">
+        <v>28868</v>
+      </c>
+      <c r="J10" s="21">
+        <v>28779</v>
+      </c>
+      <c r="K10" s="14">
+        <v>89</v>
+      </c>
+      <c r="L10" s="22">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="R10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="S10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="T10" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="U10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="V10" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="W10" s="14"/>
+        <v>0.00308299847582098</v>
+      </c>
+      <c r="M10" s="14">
+        <v>60.55</v>
+      </c>
+      <c r="N10" s="14">
+        <v>82</v>
+      </c>
+      <c r="O10" s="14">
+        <v>47.965</v>
+      </c>
+      <c r="P10" s="14">
+        <v>16</v>
+      </c>
+      <c r="Q10" s="14">
+        <v>285</v>
+      </c>
+      <c r="R10" s="14">
+        <v>577</v>
+      </c>
+      <c r="S10" s="14">
+        <v>0</v>
+      </c>
+      <c r="T10" s="22">
+        <v>0.0285</v>
+      </c>
+      <c r="U10" s="14">
+        <v>141</v>
+      </c>
+      <c r="V10" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="W10" s="14" t="s">
+        <v>313</v>
+      </c>
       <c r="X10" s="14" t="s">
         <v>14</v>
       </c>
@@ -5978,7 +6255,7 @@
       <c r="K11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="L11" s="21" t="e">
+      <c r="L11" s="22" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -6001,7 +6278,7 @@
       <c r="S11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T11" s="21" t="s">
+      <c r="T11" s="22" t="s">
         <v>14</v>
       </c>
       <c r="U11" s="14" t="s">
@@ -6047,8 +6324,8 @@
       <c r="K12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="21" t="e">
-        <f>IF(I12&gt;0,K12/I12,0)</f>
+      <c r="L12" s="22" t="e">
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="M12" s="14" t="s">
@@ -6070,7 +6347,7 @@
       <c r="S12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T12" s="21" t="s">
+      <c r="T12" s="22" t="s">
         <v>14</v>
       </c>
       <c r="U12" s="14" t="s">
@@ -6086,7 +6363,7 @@
     </row>
     <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A13" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
@@ -6128,7 +6405,7 @@
     </row>
     <row r="14" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A14" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>14</v>
@@ -6197,7 +6474,7 @@
     </row>
     <row r="15" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A15" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>14</v>
@@ -6266,7 +6543,7 @@
     </row>
     <row r="16" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A16" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>14</v>
@@ -6335,13 +6612,13 @@
     </row>
     <row r="17" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A17" s="12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>82</v>
@@ -6404,7 +6681,7 @@
     </row>
     <row r="18" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A18" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
@@ -6446,7 +6723,7 @@
     </row>
     <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A19" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
@@ -6455,7 +6732,7 @@
         <v>295</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>137</v>
@@ -6515,7 +6792,7 @@
     </row>
     <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A20" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>14</v>
@@ -6524,7 +6801,7 @@
         <v>295</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>143</v>
@@ -6545,7 +6822,7 @@
       <c r="K20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L20" s="22" t="e">
+      <c r="L20" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
@@ -6568,7 +6845,7 @@
       <c r="S20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T20" s="22" t="s">
+      <c r="T20" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U20" s="4" t="s">
@@ -6584,7 +6861,7 @@
     </row>
     <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A21" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>14</v>
@@ -6593,7 +6870,7 @@
         <v>295</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>149</v>
@@ -6653,16 +6930,16 @@
     </row>
     <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A22" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>155</v>
@@ -6683,7 +6960,7 @@
       <c r="K22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L22" s="22" t="e">
+      <c r="L22" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
@@ -6706,7 +6983,7 @@
       <c r="S22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T22" s="22" t="s">
+      <c r="T22" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U22" s="4" t="s">
@@ -6722,7 +6999,7 @@
     </row>
     <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A23" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
@@ -6764,7 +7041,7 @@
     </row>
     <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A24" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>14</v>
@@ -6833,7 +7110,7 @@
     </row>
     <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A25" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>14</v>
@@ -6863,7 +7140,7 @@
       <c r="K25" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="22" t="e">
+      <c r="L25" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
@@ -6886,7 +7163,7 @@
       <c r="S25" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T25" s="22" t="s">
+      <c r="T25" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U25" s="4" t="s">
@@ -6902,7 +7179,7 @@
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A26" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>14</v>
@@ -6971,13 +7248,13 @@
     </row>
     <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A27" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>85</v>
@@ -7001,7 +7278,7 @@
       <c r="K27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L27" s="22" t="e">
+      <c r="L27" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
@@ -7024,7 +7301,7 @@
       <c r="S27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T27" s="22" t="s">
+      <c r="T27" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U27" s="4" t="s">
@@ -7040,7 +7317,7 @@
     </row>
     <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A28" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
@@ -7082,7 +7359,7 @@
     </row>
     <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A29" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>14</v>
@@ -7151,7 +7428,7 @@
     </row>
     <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A30" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>14</v>
@@ -7181,7 +7458,7 @@
       <c r="K30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L30" s="22" t="e">
+      <c r="L30" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
@@ -7204,7 +7481,7 @@
       <c r="S30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T30" s="22" t="s">
+      <c r="T30" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U30" s="4" t="s">
@@ -7220,7 +7497,7 @@
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A31" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>14</v>
@@ -7289,13 +7566,13 @@
     </row>
     <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A32" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>88</v>
@@ -7319,7 +7596,7 @@
       <c r="K32" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L32" s="22" t="e">
+      <c r="L32" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
@@ -7342,7 +7619,7 @@
       <c r="S32" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T32" s="22" t="s">
+      <c r="T32" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U32" s="4" t="s">
@@ -7358,7 +7635,7 @@
     </row>
     <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A33" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4" t="s">
@@ -7400,7 +7677,7 @@
     </row>
     <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A34" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>14</v>
@@ -7409,7 +7686,7 @@
         <v>295</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>137</v>
@@ -7469,7 +7746,7 @@
     </row>
     <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A35" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>14</v>
@@ -7478,7 +7755,7 @@
         <v>295</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>143</v>
@@ -7499,7 +7776,7 @@
       <c r="K35" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L35" s="22" t="e">
+      <c r="L35" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
@@ -7522,7 +7799,7 @@
       <c r="S35" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T35" s="22" t="s">
+      <c r="T35" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U35" s="4" t="s">
@@ -7538,7 +7815,7 @@
     </row>
     <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A36" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>14</v>
@@ -7547,7 +7824,7 @@
         <v>295</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>149</v>
@@ -7607,16 +7884,16 @@
     </row>
     <row r="37" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A37" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>155</v>
@@ -7637,7 +7914,7 @@
       <c r="K37" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L37" s="22" t="e">
+      <c r="L37" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
@@ -7660,7 +7937,7 @@
       <c r="S37" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T37" s="22" t="s">
+      <c r="T37" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U37" s="4" t="s">
@@ -7676,7 +7953,7 @@
     </row>
     <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A38" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4" t="s">
@@ -7718,7 +7995,7 @@
     </row>
     <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A39" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>14</v>
@@ -7787,7 +8064,7 @@
     </row>
     <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A40" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>14</v>
@@ -7817,7 +8094,7 @@
       <c r="K40" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L40" s="22" t="e">
+      <c r="L40" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
@@ -7840,7 +8117,7 @@
       <c r="S40" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T40" s="22" t="s">
+      <c r="T40" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U40" s="4" t="s">
@@ -7856,7 +8133,7 @@
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A41" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>14</v>
@@ -7925,13 +8202,13 @@
     </row>
     <row r="42" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A42" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>95</v>
@@ -7955,7 +8232,7 @@
       <c r="K42" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L42" s="22" t="e">
+      <c r="L42" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
@@ -7978,7 +8255,7 @@
       <c r="S42" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T42" s="22" t="s">
+      <c r="T42" s="23" t="s">
         <v>14</v>
       </c>
       <c r="U42" s="4" t="s">
@@ -7994,7 +8271,7 @@
     </row>
     <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A43" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
@@ -8036,7 +8313,7 @@
     </row>
     <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A44" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>14</v>
@@ -8105,7 +8382,7 @@
     </row>
     <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A45" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>14</v>
@@ -8174,7 +8451,7 @@
     </row>
     <row r="46" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A46" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>14</v>
@@ -8243,13 +8520,13 @@
     </row>
     <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A47" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>98</v>
@@ -8312,7 +8589,7 @@
     </row>
     <row r="48" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A48" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4" t="s">
@@ -8354,16 +8631,16 @@
     </row>
     <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A49" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>137</v>
@@ -8380,7 +8657,7 @@
       <c r="I49" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J49" s="23"/>
+      <c r="J49" s="24"/>
       <c r="K49" s="12" t="s">
         <v>14</v>
       </c>
@@ -8423,14 +8700,14 @@
     </row>
     <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A50" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>143</v>
@@ -8447,7 +8724,7 @@
       <c r="I50" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J50" s="23"/>
+      <c r="J50" s="24"/>
       <c r="K50" s="12" t="s">
         <v>14</v>
       </c>
@@ -8490,16 +8767,16 @@
     </row>
     <row r="51" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A51" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>149</v>
@@ -8516,7 +8793,7 @@
       <c r="I51" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="23"/>
+      <c r="J51" s="24"/>
       <c r="K51" s="12" t="s">
         <v>14</v>
       </c>
@@ -8559,16 +8836,16 @@
     </row>
     <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A52" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>155</v>
@@ -8585,7 +8862,7 @@
       <c r="I52" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J52" s="23"/>
+      <c r="J52" s="24"/>
       <c r="K52" s="12" t="s">
         <v>14</v>
       </c>
@@ -8628,7 +8905,7 @@
     </row>
     <row r="53" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A53" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4" t="s">
@@ -8670,16 +8947,16 @@
     </row>
     <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A54" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>137</v>
@@ -8696,7 +8973,7 @@
       <c r="I54" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J54" s="23"/>
+      <c r="J54" s="24"/>
       <c r="K54" s="12" t="s">
         <v>14</v>
       </c>
@@ -8739,14 +9016,14 @@
     </row>
     <row r="55" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A55" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>143</v>
@@ -8763,7 +9040,7 @@
       <c r="I55" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J55" s="23"/>
+      <c r="J55" s="24"/>
       <c r="K55" s="12" t="s">
         <v>14</v>
       </c>
@@ -8806,16 +9083,16 @@
     </row>
     <row r="56" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A56" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>149</v>
@@ -8832,7 +9109,7 @@
       <c r="I56" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="23"/>
+      <c r="J56" s="24"/>
       <c r="K56" s="12" t="s">
         <v>14</v>
       </c>
@@ -8875,16 +9152,16 @@
     </row>
     <row r="57" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A57" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>155</v>
@@ -8901,7 +9178,7 @@
       <c r="I57" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J57" s="23"/>
+      <c r="J57" s="24"/>
       <c r="K57" s="12" t="s">
         <v>14</v>
       </c>
@@ -8944,7 +9221,7 @@
     </row>
     <row r="58" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A58" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4" t="s">
@@ -8986,16 +9263,16 @@
     </row>
     <row r="59" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A59" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>137</v>
@@ -9012,7 +9289,7 @@
       <c r="I59" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J59" s="23"/>
+      <c r="J59" s="24"/>
       <c r="K59" s="12" t="s">
         <v>14</v>
       </c>
@@ -9055,14 +9332,14 @@
     </row>
     <row r="60" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A60" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>143</v>
@@ -9079,7 +9356,7 @@
       <c r="I60" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J60" s="23"/>
+      <c r="J60" s="24"/>
       <c r="K60" s="12" t="s">
         <v>14</v>
       </c>
@@ -9122,16 +9399,16 @@
     </row>
     <row r="61" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A61" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>149</v>
@@ -9148,7 +9425,7 @@
       <c r="I61" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J61" s="23"/>
+      <c r="J61" s="24"/>
       <c r="K61" s="12" t="s">
         <v>14</v>
       </c>
@@ -9191,16 +9468,16 @@
     </row>
     <row r="62" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A62" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>155</v>
@@ -9217,7 +9494,7 @@
       <c r="I62" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J62" s="23"/>
+      <c r="J62" s="24"/>
       <c r="K62" s="12" t="s">
         <v>14</v>
       </c>
@@ -9260,7 +9537,7 @@
     </row>
     <row r="63" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A63" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4" t="s">
@@ -9302,16 +9579,16 @@
     </row>
     <row r="64" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A64" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>137</v>
@@ -9328,7 +9605,7 @@
       <c r="I64" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J64" s="23"/>
+      <c r="J64" s="24"/>
       <c r="K64" s="12" t="s">
         <v>14</v>
       </c>
@@ -9371,14 +9648,14 @@
     </row>
     <row r="65" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A65" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E65" s="12" t="s">
         <v>143</v>
@@ -9395,7 +9672,7 @@
       <c r="I65" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J65" s="23"/>
+      <c r="J65" s="24"/>
       <c r="K65" s="12" t="s">
         <v>14</v>
       </c>
@@ -9438,16 +9715,16 @@
     </row>
     <row r="66" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A66" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>149</v>
@@ -9464,7 +9741,7 @@
       <c r="I66" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J66" s="23"/>
+      <c r="J66" s="24"/>
       <c r="K66" s="12" t="s">
         <v>14</v>
       </c>
@@ -9507,16 +9784,16 @@
     </row>
     <row r="67" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A67" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>155</v>
@@ -9533,7 +9810,7 @@
       <c r="I67" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J67" s="23"/>
+      <c r="J67" s="24"/>
       <c r="K67" s="12" t="s">
         <v>14</v>
       </c>
@@ -9576,7 +9853,7 @@
     </row>
     <row r="68" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A68" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
@@ -9618,16 +9895,16 @@
     </row>
     <row r="69" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A69" s="12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>137</v>
@@ -9687,14 +9964,14 @@
     </row>
     <row r="70" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A70" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B70" s="12"/>
       <c r="C70" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>143</v>
@@ -9754,16 +10031,16 @@
     </row>
     <row r="71" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A71" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>149</v>
@@ -9823,16 +10100,16 @@
     </row>
     <row r="72" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A72" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>155</v>
@@ -9892,7 +10169,7 @@
     </row>
     <row r="73" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A73" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4" t="s">
@@ -9934,16 +10211,16 @@
     </row>
     <row r="74" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A74" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>137</v>
@@ -10003,14 +10280,14 @@
     </row>
     <row r="75" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A75" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B75" s="12"/>
       <c r="C75" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E75" s="12" t="s">
         <v>143</v>
@@ -10070,16 +10347,16 @@
     </row>
     <row r="76" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A76" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>149</v>
@@ -10139,16 +10416,16 @@
     </row>
     <row r="77" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A77" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E77" s="12" t="s">
         <v>155</v>
@@ -10244,7 +10521,7 @@
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
-      <c r="L79" s="22"/>
+      <c r="L79" s="23"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
@@ -10252,7 +10529,7 @@
       <c r="Q79" s="4"/>
       <c r="R79" s="4"/>
       <c r="S79" s="4"/>
-      <c r="T79" s="22"/>
+      <c r="T79" s="23"/>
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
       <c r="W79" s="4"/>
@@ -10296,7 +10573,7 @@
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
-      <c r="L81" s="22"/>
+      <c r="L81" s="23"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
@@ -10304,7 +10581,7 @@
       <c r="Q81" s="4"/>
       <c r="R81" s="4"/>
       <c r="S81" s="4"/>
-      <c r="T81" s="22"/>
+      <c r="T81" s="23"/>
       <c r="U81" s="4"/>
       <c r="V81" s="4"/>
       <c r="W81" s="4"/>
@@ -10348,7 +10625,7 @@
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
-      <c r="L83" s="22"/>
+      <c r="L83" s="23"/>
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
@@ -10356,7 +10633,7 @@
       <c r="Q83" s="4"/>
       <c r="R83" s="4"/>
       <c r="S83" s="4"/>
-      <c r="T83" s="22"/>
+      <c r="T83" s="23"/>
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
       <c r="W83" s="4"/>
@@ -10400,7 +10677,7 @@
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
-      <c r="L85" s="22"/>
+      <c r="L85" s="23"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
@@ -10408,7 +10685,7 @@
       <c r="Q85" s="4"/>
       <c r="R85" s="4"/>
       <c r="S85" s="4"/>
-      <c r="T85" s="22"/>
+      <c r="T85" s="23"/>
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
       <c r="W85" s="4"/>
@@ -10452,7 +10729,7 @@
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
-      <c r="L87" s="22"/>
+      <c r="L87" s="23"/>
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
@@ -10460,7 +10737,7 @@
       <c r="Q87" s="4"/>
       <c r="R87" s="4"/>
       <c r="S87" s="4"/>
-      <c r="T87" s="22"/>
+      <c r="T87" s="23"/>
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
       <c r="W87" s="4"/>
@@ -10504,7 +10781,7 @@
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
-      <c r="L89" s="22"/>
+      <c r="L89" s="23"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
@@ -10512,7 +10789,7 @@
       <c r="Q89" s="4"/>
       <c r="R89" s="4"/>
       <c r="S89" s="4"/>
-      <c r="T89" s="22"/>
+      <c r="T89" s="23"/>
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
@@ -10556,7 +10833,7 @@
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
-      <c r="L91" s="22"/>
+      <c r="L91" s="23"/>
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
@@ -10564,7 +10841,7 @@
       <c r="Q91" s="4"/>
       <c r="R91" s="4"/>
       <c r="S91" s="4"/>
-      <c r="T91" s="22"/>
+      <c r="T91" s="23"/>
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
       <c r="W91" s="4"/>
@@ -10608,7 +10885,7 @@
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
-      <c r="L93" s="22"/>
+      <c r="L93" s="23"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
@@ -10616,7 +10893,7 @@
       <c r="Q93" s="4"/>
       <c r="R93" s="4"/>
       <c r="S93" s="4"/>
-      <c r="T93" s="22"/>
+      <c r="T93" s="23"/>
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
       <c r="W93" s="4"/>
@@ -10660,7 +10937,7 @@
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
-      <c r="L95" s="22"/>
+      <c r="L95" s="23"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
@@ -10668,7 +10945,7 @@
       <c r="Q95" s="4"/>
       <c r="R95" s="4"/>
       <c r="S95" s="4"/>
-      <c r="T95" s="22"/>
+      <c r="T95" s="23"/>
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
       <c r="W95" s="4"/>
@@ -11144,7 +11421,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="V9 V10 V11 V4:V8 V12:V95">
+    <dataValidation type="list" allowBlank="1" sqref="V4:V95">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11174,7 +11451,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -11194,16 +11471,16 @@
         <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>182</v>
@@ -11212,7 +11489,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -11226,19 +11503,19 @@
         <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -11255,22 +11532,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -11287,22 +11564,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11325,16 +11602,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11375,10 +11652,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11394,25 +11671,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11423,22 +11700,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -11447,7 +11724,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11455,22 +11732,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11487,22 +11764,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11511,7 +11788,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11519,22 +11796,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="438">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1010,6 +1010,11 @@
   <si>
     <t>1.在长达 10 分钟的压力测试中，系统平均每秒处理了 48个请求，不具有报错。
 2.小程序未有卡顿等情况</t>
+  </si>
+  <si>
+    <t>1.在长达 10 分钟的压力测试中，系统平均每秒处理了 140个请求，不具有报错。
+2.小程序未有卡顿等情况
+3.实际插入order表的数据为78462条</t>
   </si>
   <si>
     <t>W04</t>
@@ -3643,6 +3648,216 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>337185</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>998220</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>960755</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="图片 33"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27216735" y="20149185"/>
+          <a:ext cx="822960" cy="623570"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1415415</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>324485</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2290445</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>977265</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="图片 34"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28456890" y="20136485"/>
+          <a:ext cx="875030" cy="652780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1334135</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1057910</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>2117090</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="图片 35"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27285315" y="21146135"/>
+          <a:ext cx="814070" cy="782955"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1367155</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2606675</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>2406650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="图片 36"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28270200" y="21179155"/>
+          <a:ext cx="1377950" cy="1039495"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>494665</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>2912745</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1176020</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3588385</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="图片 37"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27536140" y="22724745"/>
+          <a:ext cx="681355" cy="675640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6248,46 +6463,50 @@
       <c r="H11" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="22" t="e">
+      <c r="I11" s="14">
+        <v>84405</v>
+      </c>
+      <c r="J11" s="21">
+        <v>84022</v>
+      </c>
+      <c r="K11" s="14">
+        <v>383</v>
+      </c>
+      <c r="L11" s="22">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="R11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="S11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="T11" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="U11" s="14" t="s">
-        <v>14</v>
-      </c>
+        <v>0.00453764587405959</v>
+      </c>
+      <c r="M11" s="14">
+        <v>68.56</v>
+      </c>
+      <c r="N11" s="14">
+        <v>100</v>
+      </c>
+      <c r="O11" s="14">
+        <v>140</v>
+      </c>
+      <c r="P11" s="14">
+        <v>49.4</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>1000</v>
+      </c>
+      <c r="R11" s="14">
+        <v>1000</v>
+      </c>
+      <c r="S11" s="14">
+        <v>1</v>
+      </c>
+      <c r="T11" s="22">
+        <v>0.04</v>
+      </c>
+      <c r="U11" s="14"/>
       <c r="V11" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="W11" s="14"/>
+        <v>15</v>
+      </c>
+      <c r="W11" s="14" t="s">
+        <v>314</v>
+      </c>
       <c r="X11" s="14" t="s">
         <v>14</v>
       </c>
@@ -6363,7 +6582,7 @@
     </row>
     <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A13" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
@@ -6405,7 +6624,7 @@
     </row>
     <row r="14" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A14" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>14</v>
@@ -6474,7 +6693,7 @@
     </row>
     <row r="15" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A15" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>14</v>
@@ -6543,7 +6762,7 @@
     </row>
     <row r="16" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A16" s="12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>14</v>
@@ -6612,13 +6831,13 @@
     </row>
     <row r="17" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A17" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>82</v>
@@ -6681,7 +6900,7 @@
     </row>
     <row r="18" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A18" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
@@ -6723,7 +6942,7 @@
     </row>
     <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A19" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
@@ -6732,7 +6951,7 @@
         <v>295</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>137</v>
@@ -6792,7 +7011,7 @@
     </row>
     <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A20" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>14</v>
@@ -6801,7 +7020,7 @@
         <v>295</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>143</v>
@@ -6861,7 +7080,7 @@
     </row>
     <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A21" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>14</v>
@@ -6870,7 +7089,7 @@
         <v>295</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>149</v>
@@ -6930,16 +7149,16 @@
     </row>
     <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A22" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>155</v>
@@ -6999,7 +7218,7 @@
     </row>
     <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A23" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
@@ -7041,7 +7260,7 @@
     </row>
     <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A24" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>14</v>
@@ -7110,7 +7329,7 @@
     </row>
     <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A25" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>14</v>
@@ -7179,7 +7398,7 @@
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A26" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>14</v>
@@ -7248,13 +7467,13 @@
     </row>
     <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A27" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>85</v>
@@ -7317,7 +7536,7 @@
     </row>
     <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A28" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
@@ -7359,7 +7578,7 @@
     </row>
     <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A29" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>14</v>
@@ -7428,7 +7647,7 @@
     </row>
     <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A30" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>14</v>
@@ -7497,7 +7716,7 @@
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A31" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>14</v>
@@ -7566,13 +7785,13 @@
     </row>
     <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A32" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>88</v>
@@ -7635,7 +7854,7 @@
     </row>
     <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A33" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4" t="s">
@@ -7677,7 +7896,7 @@
     </row>
     <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A34" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>14</v>
@@ -7686,7 +7905,7 @@
         <v>295</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>137</v>
@@ -7746,7 +7965,7 @@
     </row>
     <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A35" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>14</v>
@@ -7755,7 +7974,7 @@
         <v>295</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>143</v>
@@ -7815,7 +8034,7 @@
     </row>
     <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A36" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>14</v>
@@ -7824,7 +8043,7 @@
         <v>295</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>149</v>
@@ -7884,16 +8103,16 @@
     </row>
     <row r="37" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A37" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>155</v>
@@ -7953,7 +8172,7 @@
     </row>
     <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A38" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4" t="s">
@@ -7995,7 +8214,7 @@
     </row>
     <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A39" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>14</v>
@@ -8064,7 +8283,7 @@
     </row>
     <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A40" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>14</v>
@@ -8133,7 +8352,7 @@
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A41" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>14</v>
@@ -8202,13 +8421,13 @@
     </row>
     <row r="42" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A42" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>95</v>
@@ -8271,7 +8490,7 @@
     </row>
     <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A43" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
@@ -8313,7 +8532,7 @@
     </row>
     <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A44" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>14</v>
@@ -8382,7 +8601,7 @@
     </row>
     <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A45" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>14</v>
@@ -8451,7 +8670,7 @@
     </row>
     <row r="46" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A46" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>14</v>
@@ -8520,13 +8739,13 @@
     </row>
     <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A47" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>98</v>
@@ -8589,7 +8808,7 @@
     </row>
     <row r="48" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A48" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4" t="s">
@@ -8631,16 +8850,16 @@
     </row>
     <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A49" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>137</v>
@@ -8700,14 +8919,14 @@
     </row>
     <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A50" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>143</v>
@@ -8767,16 +8986,16 @@
     </row>
     <row r="51" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A51" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>149</v>
@@ -8836,16 +9055,16 @@
     </row>
     <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A52" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>155</v>
@@ -8905,7 +9124,7 @@
     </row>
     <row r="53" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A53" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4" t="s">
@@ -8947,16 +9166,16 @@
     </row>
     <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A54" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>137</v>
@@ -9016,14 +9235,14 @@
     </row>
     <row r="55" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A55" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>143</v>
@@ -9083,16 +9302,16 @@
     </row>
     <row r="56" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A56" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>149</v>
@@ -9152,16 +9371,16 @@
     </row>
     <row r="57" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A57" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>155</v>
@@ -9221,7 +9440,7 @@
     </row>
     <row r="58" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A58" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4" t="s">
@@ -9263,16 +9482,16 @@
     </row>
     <row r="59" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A59" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>137</v>
@@ -9332,14 +9551,14 @@
     </row>
     <row r="60" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A60" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>143</v>
@@ -9399,16 +9618,16 @@
     </row>
     <row r="61" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A61" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>149</v>
@@ -9468,16 +9687,16 @@
     </row>
     <row r="62" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A62" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>155</v>
@@ -9537,7 +9756,7 @@
     </row>
     <row r="63" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A63" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4" t="s">
@@ -9579,16 +9798,16 @@
     </row>
     <row r="64" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A64" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>137</v>
@@ -9648,14 +9867,14 @@
     </row>
     <row r="65" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A65" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E65" s="12" t="s">
         <v>143</v>
@@ -9715,16 +9934,16 @@
     </row>
     <row r="66" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A66" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>149</v>
@@ -9784,16 +10003,16 @@
     </row>
     <row r="67" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A67" s="12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>155</v>
@@ -9853,7 +10072,7 @@
     </row>
     <row r="68" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A68" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
@@ -9895,16 +10114,16 @@
     </row>
     <row r="69" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A69" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>137</v>
@@ -9964,14 +10183,14 @@
     </row>
     <row r="70" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A70" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B70" s="12"/>
       <c r="C70" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>143</v>
@@ -10031,16 +10250,16 @@
     </row>
     <row r="71" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A71" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>149</v>
@@ -10100,16 +10319,16 @@
     </row>
     <row r="72" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A72" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>155</v>
@@ -10169,7 +10388,7 @@
     </row>
     <row r="73" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A73" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4" t="s">
@@ -10211,16 +10430,16 @@
     </row>
     <row r="74" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A74" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>137</v>
@@ -10280,14 +10499,14 @@
     </row>
     <row r="75" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A75" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B75" s="12"/>
       <c r="C75" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E75" s="12" t="s">
         <v>143</v>
@@ -10347,16 +10566,16 @@
     </row>
     <row r="76" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A76" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>149</v>
@@ -10416,16 +10635,16 @@
     </row>
     <row r="77" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A77" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E77" s="12" t="s">
         <v>155</v>
@@ -11451,7 +11670,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -11471,16 +11690,16 @@
         <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>182</v>
@@ -11489,7 +11708,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -11503,19 +11722,19 @@
         <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -11532,22 +11751,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -11564,22 +11783,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11602,16 +11821,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11652,10 +11871,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11671,25 +11890,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11700,22 +11919,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -11724,7 +11943,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11732,22 +11951,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11764,22 +11983,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11788,7 +12007,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11796,22 +12015,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="437">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1015,9 +1015,6 @@
     <t>1.在长达 10 分钟的压力测试中，系统平均每秒处理了 140个请求，不具有报错。
 2.小程序未有卡顿等情况
 3.实际插入order表的数据为78462条</t>
-  </si>
-  <si>
-    <t>W04</t>
   </si>
   <si>
     <t>R13</t>
@@ -2374,7 +2371,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27162760" y="1590040"/>
+          <a:off x="29912310" y="1590040"/>
           <a:ext cx="1051560" cy="707390"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2416,7 +2413,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28589605" y="2411730"/>
+          <a:off x="31339155" y="2411730"/>
           <a:ext cx="1077595" cy="966470"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2458,7 +2455,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27231975" y="2432050"/>
+          <a:off x="29981525" y="2432050"/>
           <a:ext cx="1134110" cy="640715"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2500,7 +2497,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27159585" y="3249930"/>
+          <a:off x="29909135" y="3249930"/>
           <a:ext cx="1158875" cy="630555"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2542,7 +2539,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28413710" y="1619250"/>
+          <a:off x="31163260" y="1619250"/>
           <a:ext cx="1009650" cy="670560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2584,7 +2581,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27424380" y="4308475"/>
+          <a:off x="30173930" y="4308475"/>
           <a:ext cx="836295" cy="449580"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2626,7 +2623,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28533725" y="4060825"/>
+          <a:off x="31283275" y="4060825"/>
           <a:ext cx="879475" cy="506730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2668,7 +2665,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27495500" y="4946650"/>
+          <a:off x="30245050" y="4946650"/>
           <a:ext cx="660400" cy="370840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2710,7 +2707,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28482290" y="4832350"/>
+          <a:off x="31231840" y="4832350"/>
           <a:ext cx="654685" cy="401320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2752,7 +2749,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28578175" y="5461000"/>
+          <a:off x="31327725" y="5461000"/>
           <a:ext cx="596900" cy="403860"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2794,7 +2791,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27485340" y="5394325"/>
+          <a:off x="30234890" y="5394325"/>
           <a:ext cx="680085" cy="391160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2836,7 +2833,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27170380" y="6127750"/>
+          <a:off x="29919930" y="6127750"/>
           <a:ext cx="1090295" cy="536575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2878,7 +2875,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28554045" y="6146800"/>
+          <a:off x="31303595" y="6146800"/>
           <a:ext cx="611505" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2920,7 +2917,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27492325" y="6819900"/>
+          <a:off x="30241875" y="6819900"/>
           <a:ext cx="730250" cy="508635"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2962,7 +2959,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28379420" y="6962140"/>
+          <a:off x="31128970" y="6962140"/>
           <a:ext cx="1122045" cy="571500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3004,7 +3001,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27753945" y="8442960"/>
+          <a:off x="30503495" y="8442960"/>
           <a:ext cx="962025" cy="556895"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3046,7 +3043,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28818205" y="8499475"/>
+          <a:off x="31567755" y="8499475"/>
           <a:ext cx="829945" cy="539750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3088,7 +3085,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27133550" y="9394825"/>
+          <a:off x="29883100" y="9394825"/>
           <a:ext cx="1036955" cy="250190"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3130,7 +3127,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28610560" y="9306560"/>
+          <a:off x="31360110" y="9306560"/>
           <a:ext cx="737235" cy="556260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3172,7 +3169,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28091130" y="10348595"/>
+          <a:off x="30840680" y="10348595"/>
           <a:ext cx="882650" cy="622935"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3214,7 +3211,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27485340" y="12278360"/>
+          <a:off x="30234890" y="12278360"/>
           <a:ext cx="1044575" cy="671830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3256,7 +3253,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27129105" y="13241020"/>
+          <a:off x="29878655" y="13241020"/>
           <a:ext cx="758190" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3298,7 +3295,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28416250" y="13117830"/>
+          <a:off x="31165800" y="13117830"/>
           <a:ext cx="879475" cy="707390"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3340,7 +3337,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27305635" y="14194155"/>
+          <a:off x="30055185" y="14194155"/>
           <a:ext cx="1013460" cy="603250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3382,7 +3379,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27597100" y="15056485"/>
+          <a:off x="30346650" y="15056485"/>
           <a:ext cx="1379855" cy="614680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3424,7 +3421,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27247215" y="16304895"/>
+          <a:off x="29996765" y="16304895"/>
           <a:ext cx="981075" cy="640080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3466,7 +3463,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27304365" y="17435830"/>
+          <a:off x="30053915" y="17435830"/>
           <a:ext cx="1158875" cy="778510"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3508,7 +3505,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27284045" y="18588355"/>
+          <a:off x="30033595" y="18588355"/>
           <a:ext cx="1094105" cy="631190"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3550,7 +3547,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28661360" y="16425545"/>
+          <a:off x="31410910" y="16425545"/>
           <a:ext cx="840105" cy="646430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3592,7 +3589,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28694380" y="17559020"/>
+          <a:off x="31443930" y="17559020"/>
           <a:ext cx="1119505" cy="675005"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3634,7 +3631,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28914090" y="18724245"/>
+          <a:off x="31663640" y="18724245"/>
           <a:ext cx="855345" cy="514350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3676,7 +3673,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27216735" y="20149185"/>
+          <a:off x="29966285" y="20149185"/>
           <a:ext cx="822960" cy="623570"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3718,7 +3715,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28456890" y="20136485"/>
+          <a:off x="31206440" y="20136485"/>
           <a:ext cx="875030" cy="652780"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3760,7 +3757,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27285315" y="21146135"/>
+          <a:off x="30034865" y="21146135"/>
           <a:ext cx="814070" cy="782955"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3802,7 +3799,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28270200" y="21179155"/>
+          <a:off x="31019750" y="21179155"/>
           <a:ext cx="1377950" cy="1039495"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3844,7 +3841,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27536140" y="22724745"/>
+          <a:off x="30285690" y="22724745"/>
           <a:ext cx="681355" cy="675640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5817,14 +5814,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X95"/>
+  <dimension ref="A1:X94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="21.9083333333333" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="48.5" customWidth="1"/>
+    <col min="5" max="5" width="78.675" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="24.375" customWidth="1"/>
@@ -6580,47 +6577,74 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A13" s="2" t="s">
+    <row r="13" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A13" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F13" s="4">
-        <v>50</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="B13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="12">
+        <v>100</v>
+      </c>
+      <c r="G13" s="12">
         <v>10</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
+      <c r="H13" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" s="19" t="e">
+        <f t="shared" ref="L13:L16" si="1">IF(I13&gt;0,K13/I13,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A14" s="12" t="s">
@@ -6636,16 +6660,16 @@
         <v>82</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F14" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G14" s="12">
         <v>10</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>14</v>
@@ -6655,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="L14" s="19" t="e">
-        <f t="shared" ref="L14:L17" si="1">IF(I14&gt;0,K14/I14,0)</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="M14" s="12" t="s">
@@ -6705,16 +6729,16 @@
         <v>82</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F15" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G15" s="12">
         <v>10</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>14</v>
@@ -6768,22 +6792,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F16" s="12">
         <v>500</v>
       </c>
       <c r="G16" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>14</v>
@@ -6829,321 +6853,321 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A17" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="12" t="s">
+    <row r="17" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A17" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F17" s="12">
-        <v>500</v>
-      </c>
-      <c r="G17" s="12">
-        <v>500</v>
-      </c>
-      <c r="H17" s="12" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="4">
+        <v>50</v>
+      </c>
+      <c r="G17" s="4">
+        <v>10</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+    </row>
+    <row r="18" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A18" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="2">
+        <v>100</v>
+      </c>
+      <c r="G18" s="2">
+        <v>10</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18" s="20" t="e">
+        <f t="shared" ref="L18:L21" si="2">IF(I18&gt;0,K18/I18,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T18" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A19" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" s="4">
+        <v>300</v>
+      </c>
+      <c r="G19" s="4">
+        <v>10</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T17" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V17" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A18" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F18" s="4">
-        <v>50</v>
-      </c>
-      <c r="G18" s="4">
-        <v>10</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-    </row>
-    <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A19" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F19" s="2">
-        <v>100</v>
-      </c>
-      <c r="G19" s="2">
-        <v>10</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="20" t="e">
-        <f t="shared" ref="L19:L22" si="2">IF(I19&gt;0,K19/I19,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T19" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A20" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F20" s="4">
-        <v>300</v>
-      </c>
-      <c r="G20" s="4">
-        <v>10</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L20" s="23" t="e">
+      <c r="I19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L19" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T20" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V20" s="4" t="s">
+      <c r="M19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T19" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A21" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="W19" s="4"/>
+      <c r="X19" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A20" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F20" s="2">
         <v>500</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G20" s="2">
         <v>10</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" s="20" t="e">
+      <c r="I20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L20" s="20" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T21" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V21" s="2" t="s">
+      <c r="M20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2" t="s">
+      <c r="W20" s="2"/>
+      <c r="X20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A21" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21" s="4">
+        <v>500</v>
+      </c>
+      <c r="G21" s="4">
+        <v>500</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21" s="23" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T21" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7151,317 +7175,317 @@
       <c r="A22" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="B22" s="4"/>
       <c r="C22" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>323</v>
+        <v>125</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="F22" s="4">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G22" s="4">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L22" s="23" t="e">
-        <f t="shared" si="2"/>
+        <v>127</v>
+      </c>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="15"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+    </row>
+    <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A23" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="2">
+        <v>100</v>
+      </c>
+      <c r="G23" s="2">
+        <v>10</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="20" t="e">
+        <f t="shared" ref="L23:L26" si="3">IF(I23&gt;0,K23/I23,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T22" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V22" s="4" t="s">
+      <c r="M23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T23" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A23" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="4">
-        <v>50</v>
-      </c>
-      <c r="G23" s="4">
-        <v>10</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>295</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F24" s="2">
-        <v>100</v>
-      </c>
-      <c r="G24" s="2">
+      <c r="E24" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F24" s="4">
+        <v>300</v>
+      </c>
+      <c r="G24" s="4">
         <v>10</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="20" t="e">
-        <f t="shared" ref="L24:L27" si="3">IF(I24&gt;0,K24/I24,0)</f>
+      <c r="H24" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24" s="23" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T24" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V24" s="2" t="s">
+      <c r="M24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T24" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V24" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2" t="s">
+      <c r="W24" s="4"/>
+      <c r="X24" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>295</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" s="4">
-        <v>300</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="E25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" s="2">
+        <v>500</v>
+      </c>
+      <c r="G25" s="2">
         <v>10</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" s="23" t="e">
+      <c r="H25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" s="20" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T25" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" s="4" t="s">
+      <c r="M25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T25" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4" t="s">
+      <c r="W25" s="2"/>
+      <c r="X25" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>295</v>
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="E26" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="4">
         <v>500</v>
       </c>
-      <c r="G26" s="2">
-        <v>10</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L26" s="20" t="e">
+      <c r="G26" s="4">
+        <v>500</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T26" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V26" s="2" t="s">
+      <c r="M26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T26" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2" t="s">
+      <c r="W26" s="4"/>
+      <c r="X26" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7469,317 +7493,317 @@
       <c r="A27" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>125</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="F27" s="4">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G27" s="4">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="23" t="e">
-        <f t="shared" si="3"/>
+        <v>127</v>
+      </c>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A28" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="2">
+        <v>100</v>
+      </c>
+      <c r="G28" s="2">
+        <v>10</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="20" t="e">
+        <f t="shared" ref="L28:L31" si="4">IF(I28&gt;0,K28/I28,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T27" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V27" s="4" t="s">
+      <c r="M28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T28" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A28" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F28" s="4">
-        <v>50</v>
-      </c>
-      <c r="G28" s="4">
-        <v>10</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>295</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F29" s="2">
-        <v>100</v>
-      </c>
-      <c r="G29" s="2">
+      <c r="E29" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" s="4">
+        <v>300</v>
+      </c>
+      <c r="G29" s="4">
         <v>10</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="20" t="e">
-        <f t="shared" ref="L29:L32" si="4">IF(I29&gt;0,K29/I29,0)</f>
+      <c r="H29" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="23" t="e">
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T29" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V29" s="2" t="s">
+      <c r="M29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T29" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2" t="s">
+      <c r="W29" s="4"/>
+      <c r="X29" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="B30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>295</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="4">
-        <v>300</v>
-      </c>
-      <c r="G30" s="4">
+      <c r="E30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" s="2">
+        <v>500</v>
+      </c>
+      <c r="G30" s="2">
         <v>10</v>
       </c>
-      <c r="H30" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L30" s="23" t="e">
+      <c r="H30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30" s="20" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T30" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V30" s="4" t="s">
+      <c r="M30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T30" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4" t="s">
+      <c r="W30" s="2"/>
+      <c r="X30" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>295</v>
+      <c r="B31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F31" s="2">
+      <c r="E31" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F31" s="4">
         <v>500</v>
       </c>
-      <c r="G31" s="2">
-        <v>10</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="20" t="e">
+      <c r="G31" s="4">
+        <v>500</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T31" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V31" s="2" t="s">
+      <c r="M31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T31" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V31" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2" t="s">
+      <c r="W31" s="4"/>
+      <c r="X31" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7787,317 +7811,317 @@
       <c r="A32" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="B32" s="4"/>
       <c r="C32" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="F32" s="4">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G32" s="4">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H32" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+    </row>
+    <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A33" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33" s="2">
+        <v>100</v>
+      </c>
+      <c r="G33" s="2">
+        <v>10</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="20" t="e">
+        <f t="shared" ref="L33:L36" si="5">IF(I33&gt;0,K33/I33,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T33" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A34" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F34" s="4">
+        <v>300</v>
+      </c>
+      <c r="G34" s="4">
+        <v>10</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L32" s="23" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T32" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V32" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A33" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F33" s="4">
-        <v>50</v>
-      </c>
-      <c r="G33" s="4">
-        <v>10</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-    </row>
-    <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A34" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F34" s="2">
-        <v>100</v>
-      </c>
-      <c r="G34" s="2">
-        <v>10</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L34" s="20" t="e">
-        <f t="shared" ref="L34:L37" si="5">IF(I34&gt;0,K34/I34,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T34" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="W34" s="2"/>
-      <c r="X34" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A35" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F35" s="4">
-        <v>300</v>
-      </c>
-      <c r="G35" s="4">
-        <v>10</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L35" s="23" t="e">
+      <c r="I34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34" s="23" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T35" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V35" s="4" t="s">
+      <c r="M34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T34" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A36" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="W34" s="4"/>
+      <c r="X34" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A35" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F35" s="2">
         <v>500</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G35" s="2">
         <v>10</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L36" s="20" t="e">
+      <c r="I35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="20" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T36" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V36" s="2" t="s">
+      <c r="M35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T35" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V35" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W36" s="2"/>
-      <c r="X36" s="2" t="s">
+      <c r="W35" s="2"/>
+      <c r="X35" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A36" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F36" s="4">
+        <v>500</v>
+      </c>
+      <c r="G36" s="4">
+        <v>500</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="23" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T36" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W36" s="4"/>
+      <c r="X36" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8105,317 +8129,317 @@
       <c r="A37" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>339</v>
+        <v>125</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="F37" s="4">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G37" s="4">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L37" s="23" t="e">
-        <f t="shared" si="5"/>
+        <v>127</v>
+      </c>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+    </row>
+    <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A38" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" s="2">
+        <v>100</v>
+      </c>
+      <c r="G38" s="2">
+        <v>10</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L38" s="20" t="e">
+        <f t="shared" ref="L38:L41" si="6">IF(I38&gt;0,K38/I38,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T37" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V37" s="4" t="s">
+      <c r="M38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T38" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V38" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A38" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" s="4">
-        <v>50</v>
-      </c>
-      <c r="G38" s="4">
-        <v>10</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>295</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F39" s="2">
-        <v>100</v>
-      </c>
-      <c r="G39" s="2">
+      <c r="E39" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="4">
+        <v>300</v>
+      </c>
+      <c r="G39" s="4">
         <v>10</v>
       </c>
-      <c r="H39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L39" s="20" t="e">
-        <f t="shared" ref="L39:L42" si="6">IF(I39&gt;0,K39/I39,0)</f>
+      <c r="H39" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39" s="23" t="e">
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T39" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V39" s="2" t="s">
+      <c r="M39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T39" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V39" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W39" s="2"/>
-      <c r="X39" s="2" t="s">
+      <c r="W39" s="4"/>
+      <c r="X39" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="4" t="s">
+      <c r="B40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>295</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F40" s="4">
-        <v>300</v>
-      </c>
-      <c r="G40" s="4">
+      <c r="E40" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F40" s="2">
+        <v>500</v>
+      </c>
+      <c r="G40" s="2">
         <v>10</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L40" s="23" t="e">
+      <c r="H40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" s="20" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T40" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V40" s="4" t="s">
+      <c r="M40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T40" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V40" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4" t="s">
+      <c r="W40" s="2"/>
+      <c r="X40" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>295</v>
+      <c r="B41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F41" s="2">
+      <c r="E41" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="4">
         <v>500</v>
       </c>
-      <c r="G41" s="2">
-        <v>10</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L41" s="20" t="e">
+      <c r="G41" s="4">
+        <v>500</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="23" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T41" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V41" s="2" t="s">
+      <c r="M41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T41" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V41" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W41" s="2"/>
-      <c r="X41" s="2" t="s">
+      <c r="W41" s="4"/>
+      <c r="X41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8423,112 +8447,112 @@
       <c r="A42" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="B42" s="4"/>
       <c r="C42" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>95</v>
+        <v>125</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="F42" s="4">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G42" s="4">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L42" s="23" t="e">
-        <f t="shared" si="6"/>
+        <v>127</v>
+      </c>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="15"/>
+      <c r="T42" s="16"/>
+      <c r="U42" s="15"/>
+      <c r="V42" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+    </row>
+    <row r="43" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A43" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F43" s="12">
+        <v>100</v>
+      </c>
+      <c r="G43" s="12">
+        <v>10</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="19" t="e">
+        <f t="shared" ref="L43:L46" si="7">IF(I43&gt;0,K43/I43,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T42" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V42" s="4" t="s">
+      <c r="M43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O43" s="12"/>
+      <c r="P43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T43" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V43" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A43" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F43" s="4">
-        <v>50</v>
-      </c>
-      <c r="G43" s="4">
-        <v>10</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="15"/>
-      <c r="R43" s="15"/>
-      <c r="S43" s="15"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="15"/>
-      <c r="V43" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
+      <c r="W43" s="12"/>
+      <c r="X43" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A44" s="12" t="s">
@@ -8544,16 +8568,16 @@
         <v>98</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F44" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G44" s="12">
         <v>10</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>14</v>
@@ -8563,7 +8587,7 @@
         <v>14</v>
       </c>
       <c r="L44" s="19" t="e">
-        <f t="shared" ref="L44:L47" si="7">IF(I44&gt;0,K44/I44,0)</f>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="M44" s="12" t="s">
@@ -8613,16 +8637,16 @@
         <v>98</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F45" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G45" s="12">
         <v>10</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I45" s="12" t="s">
         <v>14</v>
@@ -8676,22 +8700,22 @@
         <v>14</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>98</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F46" s="12">
         <v>500</v>
       </c>
       <c r="G46" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I46" s="12" t="s">
         <v>14</v>
@@ -8737,141 +8761,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A47" s="12" t="s">
+    <row r="47" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A47" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F47" s="12">
-        <v>500</v>
-      </c>
-      <c r="G47" s="12">
-        <v>500</v>
-      </c>
-      <c r="H47" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L47" s="19" t="e">
-        <f t="shared" si="7"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="4">
+        <v>50</v>
+      </c>
+      <c r="G47" s="4">
+        <v>10</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15"/>
+      <c r="R47" s="15"/>
+      <c r="S47" s="15"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="15"/>
+      <c r="V47" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W47" s="4"/>
+      <c r="X47" s="4"/>
+    </row>
+    <row r="48" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A48" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" s="12">
+        <v>100</v>
+      </c>
+      <c r="G48" s="12">
+        <v>10</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" s="24"/>
+      <c r="K48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L48" s="19" t="e">
+        <f t="shared" ref="L48:L51" si="8">IF(I48&gt;0,K48/I48,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O47" s="12"/>
-      <c r="P47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T47" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V47" s="12" t="s">
+      <c r="M48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O48" s="12"/>
+      <c r="P48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T48" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V48" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W47" s="12"/>
-      <c r="X47" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A48" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F48" s="4">
-        <v>50</v>
-      </c>
-      <c r="G48" s="4">
-        <v>10</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15"/>
-      <c r="R48" s="15"/>
-      <c r="S48" s="15"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="15"/>
-      <c r="V48" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
+      <c r="W48" s="12"/>
+      <c r="X48" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A49" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="12" t="s">
+      <c r="D49" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>356</v>
-      </c>
       <c r="E49" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F49" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G49" s="12">
         <v>10</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>14</v>
@@ -8881,7 +8903,7 @@
         <v>14</v>
       </c>
       <c r="L49" s="19" t="e">
-        <f t="shared" ref="L49:L52" si="8">IF(I49&gt;0,K49/I49,0)</f>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="M49" s="12" t="s">
@@ -8921,24 +8943,26 @@
       <c r="A50" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="B50" s="12"/>
+      <c r="B50" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C50" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>356</v>
-      </c>
       <c r="E50" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F50" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G50" s="12">
         <v>10</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I50" s="12" t="s">
         <v>14</v>
@@ -8992,22 +9016,22 @@
         <v>14</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="D51" s="12" t="s">
-        <v>356</v>
-      </c>
       <c r="E51" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F51" s="12">
         <v>500</v>
       </c>
       <c r="G51" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>14</v>
@@ -9053,141 +9077,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A52" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C52" s="12" t="s">
+    <row r="52" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A52" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F52" s="12">
-        <v>500</v>
-      </c>
-      <c r="G52" s="12">
-        <v>500</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J52" s="24"/>
-      <c r="K52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L52" s="19" t="e">
-        <f t="shared" si="8"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="4">
+        <v>50</v>
+      </c>
+      <c r="G52" s="4">
+        <v>10</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="15"/>
+      <c r="P52" s="15"/>
+      <c r="Q52" s="15"/>
+      <c r="R52" s="15"/>
+      <c r="S52" s="15"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="15"/>
+      <c r="V52" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+    </row>
+    <row r="53" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A53" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F53" s="12">
+        <v>100</v>
+      </c>
+      <c r="G53" s="12">
+        <v>10</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" s="24"/>
+      <c r="K53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" s="19" t="e">
+        <f t="shared" ref="L53:L56" si="9">IF(I53&gt;0,K53/I53,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O52" s="12"/>
-      <c r="P52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T52" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V52" s="12" t="s">
+      <c r="M53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O53" s="12"/>
+      <c r="P53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T53" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V53" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W52" s="12"/>
-      <c r="X52" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A53" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F53" s="4">
-        <v>50</v>
-      </c>
-      <c r="G53" s="4">
-        <v>10</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="15"/>
-      <c r="N53" s="15"/>
-      <c r="O53" s="15"/>
-      <c r="P53" s="15"/>
-      <c r="Q53" s="15"/>
-      <c r="R53" s="15"/>
-      <c r="S53" s="15"/>
-      <c r="T53" s="16"/>
-      <c r="U53" s="15"/>
-      <c r="V53" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
+      <c r="W53" s="12"/>
+      <c r="X53" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A54" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>363</v>
-      </c>
       <c r="E54" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F54" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G54" s="12">
         <v>10</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>14</v>
@@ -9197,7 +9219,7 @@
         <v>14</v>
       </c>
       <c r="L54" s="19" t="e">
-        <f t="shared" ref="L54:L57" si="9">IF(I54&gt;0,K54/I54,0)</f>
+        <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
       <c r="M54" s="12" t="s">
@@ -9237,24 +9259,26 @@
       <c r="A55" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="B55" s="12"/>
+      <c r="B55" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C55" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F55" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G55" s="12">
         <v>10</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I55" s="12" t="s">
         <v>14</v>
@@ -9308,22 +9332,22 @@
         <v>14</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F56" s="12">
         <v>500</v>
       </c>
       <c r="G56" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>14</v>
@@ -9369,141 +9393,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A57" s="12" t="s">
+    <row r="57" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A57" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F57" s="12">
-        <v>500</v>
-      </c>
-      <c r="G57" s="12">
-        <v>500</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J57" s="24"/>
-      <c r="K57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L57" s="19" t="e">
-        <f t="shared" si="9"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57" s="4">
+        <v>50</v>
+      </c>
+      <c r="G57" s="4">
+        <v>10</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="R57" s="15"/>
+      <c r="S57" s="15"/>
+      <c r="T57" s="16"/>
+      <c r="U57" s="15"/>
+      <c r="V57" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+    </row>
+    <row r="58" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A58" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F58" s="12">
+        <v>100</v>
+      </c>
+      <c r="G58" s="12">
+        <v>10</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" s="24"/>
+      <c r="K58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L58" s="19" t="e">
+        <f t="shared" ref="L58:L61" si="10">IF(I58&gt;0,K58/I58,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T57" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V57" s="12" t="s">
+      <c r="M58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O58" s="12"/>
+      <c r="P58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T58" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V58" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W57" s="12"/>
-      <c r="X57" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A58" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F58" s="4">
-        <v>50</v>
-      </c>
-      <c r="G58" s="4">
-        <v>10</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="15"/>
-      <c r="N58" s="15"/>
-      <c r="O58" s="15"/>
-      <c r="P58" s="15"/>
-      <c r="Q58" s="15"/>
-      <c r="R58" s="15"/>
-      <c r="S58" s="15"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="15"/>
-      <c r="V58" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W58" s="4"/>
-      <c r="X58" s="4"/>
+      <c r="W58" s="12"/>
+      <c r="X58" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="59" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A59" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="B59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>369</v>
-      </c>
       <c r="E59" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F59" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G59" s="12">
         <v>10</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>14</v>
@@ -9513,7 +9535,7 @@
         <v>14</v>
       </c>
       <c r="L59" s="19" t="e">
-        <f t="shared" ref="L59:L62" si="10">IF(I59&gt;0,K59/I59,0)</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="M59" s="12" t="s">
@@ -9553,24 +9575,26 @@
       <c r="A60" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="B60" s="12"/>
+      <c r="B60" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C60" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F60" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G60" s="12">
         <v>10</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I60" s="12" t="s">
         <v>14</v>
@@ -9624,22 +9648,22 @@
         <v>14</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F61" s="12">
         <v>500</v>
       </c>
       <c r="G61" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>14</v>
@@ -9685,141 +9709,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A62" s="12" t="s">
+    <row r="62" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A62" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F62" s="12">
-        <v>500</v>
-      </c>
-      <c r="G62" s="12">
-        <v>500</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J62" s="24"/>
-      <c r="K62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L62" s="19" t="e">
-        <f t="shared" si="10"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F62" s="4">
+        <v>50</v>
+      </c>
+      <c r="G62" s="4">
+        <v>10</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
+      <c r="P62" s="15"/>
+      <c r="Q62" s="15"/>
+      <c r="R62" s="15"/>
+      <c r="S62" s="15"/>
+      <c r="T62" s="16"/>
+      <c r="U62" s="15"/>
+      <c r="V62" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+    </row>
+    <row r="63" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A63" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F63" s="12">
+        <v>100</v>
+      </c>
+      <c r="G63" s="12">
+        <v>10</v>
+      </c>
+      <c r="H63" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J63" s="24"/>
+      <c r="K63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L63" s="19" t="e">
+        <f t="shared" ref="L63:L66" si="11">IF(I63&gt;0,K63/I63,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O62" s="12"/>
-      <c r="P62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T62" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V62" s="12" t="s">
+      <c r="M63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O63" s="12"/>
+      <c r="P63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T63" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V63" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W62" s="12"/>
-      <c r="X62" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A63" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F63" s="4">
-        <v>50</v>
-      </c>
-      <c r="G63" s="4">
-        <v>10</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="15"/>
-      <c r="O63" s="15"/>
-      <c r="P63" s="15"/>
-      <c r="Q63" s="15"/>
-      <c r="R63" s="15"/>
-      <c r="S63" s="15"/>
-      <c r="T63" s="16"/>
-      <c r="U63" s="15"/>
-      <c r="V63" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
+      <c r="W63" s="12"/>
+      <c r="X63" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="64" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A64" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="B64" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="B64" s="12"/>
       <c r="C64" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F64" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G64" s="12">
         <v>10</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>14</v>
@@ -9829,7 +9851,7 @@
         <v>14</v>
       </c>
       <c r="L64" s="19" t="e">
-        <f t="shared" ref="L64:L67" si="11">IF(I64&gt;0,K64/I64,0)</f>
+        <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
       <c r="M64" s="12" t="s">
@@ -9869,24 +9891,26 @@
       <c r="A65" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="B65" s="12"/>
+      <c r="B65" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C65" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F65" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G65" s="12">
         <v>10</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>14</v>
@@ -9940,22 +9964,22 @@
         <v>14</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F66" s="12">
         <v>500</v>
       </c>
       <c r="G66" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>14</v>
@@ -10001,141 +10025,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A67" s="12" t="s">
+    <row r="67" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A67" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F67" s="12">
-        <v>500</v>
-      </c>
-      <c r="G67" s="12">
-        <v>500</v>
-      </c>
-      <c r="H67" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J67" s="24"/>
-      <c r="K67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L67" s="19" t="e">
-        <f t="shared" si="11"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" s="4">
+        <v>50</v>
+      </c>
+      <c r="G67" s="4">
+        <v>10</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+      <c r="P67" s="15"/>
+      <c r="Q67" s="15"/>
+      <c r="R67" s="15"/>
+      <c r="S67" s="15"/>
+      <c r="T67" s="16"/>
+      <c r="U67" s="15"/>
+      <c r="V67" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+    </row>
+    <row r="68" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A68" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F68" s="12">
+        <v>100</v>
+      </c>
+      <c r="G68" s="12">
+        <v>10</v>
+      </c>
+      <c r="H68" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L68" s="19" t="e">
+        <f t="shared" ref="L68:L71" si="12">IF(I68&gt;0,K68/I68,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O67" s="12"/>
-      <c r="P67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T67" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V67" s="12" t="s">
+      <c r="M68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O68" s="12"/>
+      <c r="P68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T68" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V68" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W67" s="12"/>
-      <c r="X67" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A68" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F68" s="4">
-        <v>50</v>
-      </c>
-      <c r="G68" s="4">
-        <v>10</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="15"/>
-      <c r="N68" s="15"/>
-      <c r="O68" s="15"/>
-      <c r="P68" s="15"/>
-      <c r="Q68" s="15"/>
-      <c r="R68" s="15"/>
-      <c r="S68" s="15"/>
-      <c r="T68" s="16"/>
-      <c r="U68" s="15"/>
-      <c r="V68" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
+      <c r="W68" s="12"/>
+      <c r="X68" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="69" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A69" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="B69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>380</v>
-      </c>
       <c r="E69" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F69" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G69" s="12">
         <v>10</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I69" s="12" t="s">
         <v>14</v>
@@ -10145,7 +10167,7 @@
         <v>14</v>
       </c>
       <c r="L69" s="19" t="e">
-        <f t="shared" ref="L69:L72" si="12">IF(I69&gt;0,K69/I69,0)</f>
+        <f t="shared" si="12"/>
         <v>#VALUE!</v>
       </c>
       <c r="M69" s="12" t="s">
@@ -10185,24 +10207,26 @@
       <c r="A70" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="B70" s="12"/>
+      <c r="B70" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C70" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F70" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G70" s="12">
         <v>10</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I70" s="12" t="s">
         <v>14</v>
@@ -10256,22 +10280,22 @@
         <v>14</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F71" s="12">
         <v>500</v>
       </c>
       <c r="G71" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>14</v>
@@ -10317,141 +10341,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A72" s="12" t="s">
+    <row r="72" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A72" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F72" s="12">
-        <v>500</v>
-      </c>
-      <c r="G72" s="12">
-        <v>500</v>
-      </c>
-      <c r="H72" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J72" s="12"/>
-      <c r="K72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L72" s="19" t="e">
-        <f t="shared" si="12"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F72" s="4">
+        <v>50</v>
+      </c>
+      <c r="G72" s="4">
+        <v>10</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="15"/>
+      <c r="N72" s="15"/>
+      <c r="O72" s="15"/>
+      <c r="P72" s="15"/>
+      <c r="Q72" s="15"/>
+      <c r="R72" s="15"/>
+      <c r="S72" s="15"/>
+      <c r="T72" s="16"/>
+      <c r="U72" s="15"/>
+      <c r="V72" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+    </row>
+    <row r="73" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A73" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F73" s="12">
+        <v>100</v>
+      </c>
+      <c r="G73" s="12">
+        <v>10</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J73" s="12"/>
+      <c r="K73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L73" s="19" t="e">
+        <f t="shared" ref="L73:L76" si="13">IF(I73&gt;0,K73/I73,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O72" s="12"/>
-      <c r="P72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T72" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V72" s="12" t="s">
+      <c r="M73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O73" s="12"/>
+      <c r="P73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T73" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V73" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W72" s="12"/>
-      <c r="X72" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A73" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F73" s="4">
-        <v>50</v>
-      </c>
-      <c r="G73" s="4">
-        <v>10</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="15"/>
-      <c r="N73" s="15"/>
-      <c r="O73" s="15"/>
-      <c r="P73" s="15"/>
-      <c r="Q73" s="15"/>
-      <c r="R73" s="15"/>
-      <c r="S73" s="15"/>
-      <c r="T73" s="16"/>
-      <c r="U73" s="15"/>
-      <c r="V73" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W73" s="4"/>
-      <c r="X73" s="4"/>
+      <c r="W73" s="12"/>
+      <c r="X73" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="74" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A74" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>386</v>
-      </c>
       <c r="E74" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F74" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G74" s="12">
         <v>10</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I74" s="12" t="s">
         <v>14</v>
@@ -10461,7 +10483,7 @@
         <v>14</v>
       </c>
       <c r="L74" s="19" t="e">
-        <f t="shared" ref="L74:L77" si="13">IF(I74&gt;0,K74/I74,0)</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="M74" s="12" t="s">
@@ -10501,24 +10523,26 @@
       <c r="A75" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="B75" s="12"/>
+      <c r="B75" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C75" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F75" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G75" s="12">
         <v>10</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I75" s="12" t="s">
         <v>14</v>
@@ -10572,22 +10596,22 @@
         <v>14</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F76" s="12">
         <v>500</v>
       </c>
       <c r="G76" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I76" s="12" t="s">
         <v>14</v>
@@ -10633,542 +10657,473 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A77" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F77" s="12">
-        <v>500</v>
-      </c>
-      <c r="G77" s="12">
-        <v>500</v>
-      </c>
-      <c r="H77" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J77" s="12"/>
-      <c r="K77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L77" s="19" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O77" s="12"/>
-      <c r="P77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T77" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U77" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V77" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W77" s="12"/>
-      <c r="X77" s="12" t="s">
-        <v>14</v>
-      </c>
+    <row r="77" ht="24" customHeight="1" spans="1:24">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="20"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="2"/>
+      <c r="T77" s="20"/>
+      <c r="U77" s="2"/>
+      <c r="V77" s="2"/>
+      <c r="W77" s="2"/>
+      <c r="X77" s="2"/>
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:24">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="20"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="20"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
-      <c r="X78" s="2"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="23"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="23"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:24">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="23"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="23"/>
-      <c r="U79" s="4"/>
-      <c r="V79" s="4"/>
-      <c r="W79" s="4"/>
-      <c r="X79" s="4"/>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="20"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="2"/>
+      <c r="T79" s="20"/>
+      <c r="U79" s="2"/>
+      <c r="V79" s="2"/>
+      <c r="W79" s="2"/>
+      <c r="X79" s="2"/>
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:24">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="20"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
-      <c r="T80" s="20"/>
-      <c r="U80" s="2"/>
-      <c r="V80" s="2"/>
-      <c r="W80" s="2"/>
-      <c r="X80" s="2"/>
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="23"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4"/>
+      <c r="S80" s="4"/>
+      <c r="T80" s="23"/>
+      <c r="U80" s="4"/>
+      <c r="V80" s="4"/>
+      <c r="W80" s="4"/>
+      <c r="X80" s="4"/>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:24">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="23"/>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
-      <c r="O81" s="4"/>
-      <c r="P81" s="4"/>
-      <c r="Q81" s="4"/>
-      <c r="R81" s="4"/>
-      <c r="S81" s="4"/>
-      <c r="T81" s="23"/>
-      <c r="U81" s="4"/>
-      <c r="V81" s="4"/>
-      <c r="W81" s="4"/>
-      <c r="X81" s="4"/>
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="20"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+      <c r="R81" s="2"/>
+      <c r="S81" s="2"/>
+      <c r="T81" s="20"/>
+      <c r="U81" s="2"/>
+      <c r="V81" s="2"/>
+      <c r="W81" s="2"/>
+      <c r="X81" s="2"/>
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:24">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="20"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" s="2"/>
-      <c r="Q82" s="2"/>
-      <c r="R82" s="2"/>
-      <c r="S82" s="2"/>
-      <c r="T82" s="20"/>
-      <c r="U82" s="2"/>
-      <c r="V82" s="2"/>
-      <c r="W82" s="2"/>
-      <c r="X82" s="2"/>
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="23"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4"/>
+      <c r="R82" s="4"/>
+      <c r="S82" s="4"/>
+      <c r="T82" s="23"/>
+      <c r="U82" s="4"/>
+      <c r="V82" s="4"/>
+      <c r="W82" s="4"/>
+      <c r="X82" s="4"/>
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:24">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="23"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
-      <c r="Q83" s="4"/>
-      <c r="R83" s="4"/>
-      <c r="S83" s="4"/>
-      <c r="T83" s="23"/>
-      <c r="U83" s="4"/>
-      <c r="V83" s="4"/>
-      <c r="W83" s="4"/>
-      <c r="X83" s="4"/>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="20"/>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="2"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="2"/>
+      <c r="T83" s="20"/>
+      <c r="U83" s="2"/>
+      <c r="V83" s="2"/>
+      <c r="W83" s="2"/>
+      <c r="X83" s="2"/>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:24">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="20"/>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
-      <c r="Q84" s="2"/>
-      <c r="R84" s="2"/>
-      <c r="S84" s="2"/>
-      <c r="T84" s="20"/>
-      <c r="U84" s="2"/>
-      <c r="V84" s="2"/>
-      <c r="W84" s="2"/>
-      <c r="X84" s="2"/>
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="23"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4"/>
+      <c r="R84" s="4"/>
+      <c r="S84" s="4"/>
+      <c r="T84" s="23"/>
+      <c r="U84" s="4"/>
+      <c r="V84" s="4"/>
+      <c r="W84" s="4"/>
+      <c r="X84" s="4"/>
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:24">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="23"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="4"/>
-      <c r="Q85" s="4"/>
-      <c r="R85" s="4"/>
-      <c r="S85" s="4"/>
-      <c r="T85" s="23"/>
-      <c r="U85" s="4"/>
-      <c r="V85" s="4"/>
-      <c r="W85" s="4"/>
-      <c r="X85" s="4"/>
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="20"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="2"/>
+      <c r="T85" s="20"/>
+      <c r="U85" s="2"/>
+      <c r="V85" s="2"/>
+      <c r="W85" s="2"/>
+      <c r="X85" s="2"/>
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:24">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-      <c r="L86" s="20"/>
-      <c r="M86" s="2"/>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" s="2"/>
-      <c r="Q86" s="2"/>
-      <c r="R86" s="2"/>
-      <c r="S86" s="2"/>
-      <c r="T86" s="20"/>
-      <c r="U86" s="2"/>
-      <c r="V86" s="2"/>
-      <c r="W86" s="2"/>
-      <c r="X86" s="2"/>
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="23"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="4"/>
+      <c r="R86" s="4"/>
+      <c r="S86" s="4"/>
+      <c r="T86" s="23"/>
+      <c r="U86" s="4"/>
+      <c r="V86" s="4"/>
+      <c r="W86" s="4"/>
+      <c r="X86" s="4"/>
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:24">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="23"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="23"/>
-      <c r="U87" s="4"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="4"/>
-      <c r="X87" s="4"/>
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="20"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="2"/>
+      <c r="R87" s="2"/>
+      <c r="S87" s="2"/>
+      <c r="T87" s="20"/>
+      <c r="U87" s="2"/>
+      <c r="V87" s="2"/>
+      <c r="W87" s="2"/>
+      <c r="X87" s="2"/>
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:24">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="20"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2"/>
-      <c r="Q88" s="2"/>
-      <c r="R88" s="2"/>
-      <c r="S88" s="2"/>
-      <c r="T88" s="20"/>
-      <c r="U88" s="2"/>
-      <c r="V88" s="2"/>
-      <c r="W88" s="2"/>
-      <c r="X88" s="2"/>
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="23"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="4"/>
+      <c r="S88" s="4"/>
+      <c r="T88" s="23"/>
+      <c r="U88" s="4"/>
+      <c r="V88" s="4"/>
+      <c r="W88" s="4"/>
+      <c r="X88" s="4"/>
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:24">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="23"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="23"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
-      <c r="X89" s="4"/>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="20"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" s="2"/>
+      <c r="R89" s="2"/>
+      <c r="S89" s="2"/>
+      <c r="T89" s="20"/>
+      <c r="U89" s="2"/>
+      <c r="V89" s="2"/>
+      <c r="W89" s="2"/>
+      <c r="X89" s="2"/>
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:24">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="20"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-      <c r="R90" s="2"/>
-      <c r="S90" s="2"/>
-      <c r="T90" s="20"/>
-      <c r="U90" s="2"/>
-      <c r="V90" s="2"/>
-      <c r="W90" s="2"/>
-      <c r="X90" s="2"/>
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="23"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="4"/>
+      <c r="R90" s="4"/>
+      <c r="S90" s="4"/>
+      <c r="T90" s="23"/>
+      <c r="U90" s="4"/>
+      <c r="V90" s="4"/>
+      <c r="W90" s="4"/>
+      <c r="X90" s="4"/>
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:24">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="23"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="23"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
-      <c r="X91" s="4"/>
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="20"/>
+      <c r="M91" s="2"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" s="2"/>
+      <c r="Q91" s="2"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="2"/>
+      <c r="T91" s="20"/>
+      <c r="U91" s="2"/>
+      <c r="V91" s="2"/>
+      <c r="W91" s="2"/>
+      <c r="X91" s="2"/>
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:24">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="20"/>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" s="2"/>
-      <c r="Q92" s="2"/>
-      <c r="R92" s="2"/>
-      <c r="S92" s="2"/>
-      <c r="T92" s="20"/>
-      <c r="U92" s="2"/>
-      <c r="V92" s="2"/>
-      <c r="W92" s="2"/>
-      <c r="X92" s="2"/>
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="23"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="4"/>
+      <c r="S92" s="4"/>
+      <c r="T92" s="23"/>
+      <c r="U92" s="4"/>
+      <c r="V92" s="4"/>
+      <c r="W92" s="4"/>
+      <c r="X92" s="4"/>
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:24">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="23"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="23"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
-      <c r="X93" s="4"/>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="20"/>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" s="2"/>
+      <c r="R93" s="2"/>
+      <c r="S93" s="2"/>
+      <c r="T93" s="20"/>
+      <c r="U93" s="2"/>
+      <c r="V93" s="2"/>
+      <c r="W93" s="2"/>
+      <c r="X93" s="2"/>
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:24">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
-      <c r="L94" s="20"/>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" s="2"/>
-      <c r="Q94" s="2"/>
-      <c r="R94" s="2"/>
-      <c r="S94" s="2"/>
-      <c r="T94" s="20"/>
-      <c r="U94" s="2"/>
-      <c r="V94" s="2"/>
-      <c r="W94" s="2"/>
-      <c r="X94" s="2"/>
-    </row>
-    <row r="95" ht="24" customHeight="1" spans="1:24">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="23"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="23"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
-      <c r="X95" s="4"/>
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="23"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="4"/>
+      <c r="R94" s="4"/>
+      <c r="S94" s="4"/>
+      <c r="T94" s="23"/>
+      <c r="U94" s="4"/>
+      <c r="V94" s="4"/>
+      <c r="W94" s="4"/>
+      <c r="X94" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11234,413 +11189,398 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L13">
-    <cfRule type="cellIs" dxfId="0" priority="85" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:O13">
-    <cfRule type="cellIs" dxfId="1" priority="86" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T13">
-    <cfRule type="cellIs" dxfId="1" priority="87" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L18">
+  <conditionalFormatting sqref="L17">
     <cfRule type="cellIs" dxfId="0" priority="79" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18:O18">
+  <conditionalFormatting sqref="N17:O17">
     <cfRule type="cellIs" dxfId="1" priority="80" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T18">
+  <conditionalFormatting sqref="T17">
     <cfRule type="cellIs" dxfId="1" priority="81" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L23">
+  <conditionalFormatting sqref="L22">
     <cfRule type="cellIs" dxfId="0" priority="73" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N23:O23">
+  <conditionalFormatting sqref="N22:O22">
     <cfRule type="cellIs" dxfId="1" priority="74" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T23">
+  <conditionalFormatting sqref="T22">
     <cfRule type="cellIs" dxfId="1" priority="75" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L28">
+  <conditionalFormatting sqref="L27">
     <cfRule type="cellIs" dxfId="0" priority="67" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N28:O28">
+  <conditionalFormatting sqref="N27:O27">
     <cfRule type="cellIs" dxfId="1" priority="68" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T28">
+  <conditionalFormatting sqref="T27">
     <cfRule type="cellIs" dxfId="1" priority="69" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L33">
+  <conditionalFormatting sqref="L32">
     <cfRule type="cellIs" dxfId="0" priority="61" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N33:O33">
+  <conditionalFormatting sqref="N32:O32">
     <cfRule type="cellIs" dxfId="1" priority="62" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T33">
+  <conditionalFormatting sqref="T32">
     <cfRule type="cellIs" dxfId="1" priority="63" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L38">
+  <conditionalFormatting sqref="L37">
     <cfRule type="cellIs" dxfId="0" priority="55" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N38:O38">
+  <conditionalFormatting sqref="N37:O37">
     <cfRule type="cellIs" dxfId="1" priority="56" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T38">
+  <conditionalFormatting sqref="T37">
     <cfRule type="cellIs" dxfId="1" priority="57" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L43">
+  <conditionalFormatting sqref="L42">
     <cfRule type="cellIs" dxfId="0" priority="49" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N43:O43">
+  <conditionalFormatting sqref="N42:O42">
     <cfRule type="cellIs" dxfId="1" priority="50" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T43">
+  <conditionalFormatting sqref="T42">
     <cfRule type="cellIs" dxfId="1" priority="51" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L48">
+  <conditionalFormatting sqref="L47">
     <cfRule type="cellIs" dxfId="0" priority="43" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N48:O48">
+  <conditionalFormatting sqref="N47:O47">
     <cfRule type="cellIs" dxfId="1" priority="44" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T48">
+  <conditionalFormatting sqref="T47">
     <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L53">
+  <conditionalFormatting sqref="L52">
     <cfRule type="cellIs" dxfId="0" priority="37" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N53:O53">
+  <conditionalFormatting sqref="N52:O52">
     <cfRule type="cellIs" dxfId="1" priority="38" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T53">
+  <conditionalFormatting sqref="T52">
     <cfRule type="cellIs" dxfId="1" priority="39" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L58">
+  <conditionalFormatting sqref="L57">
     <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N58:O58">
+  <conditionalFormatting sqref="N57:O57">
     <cfRule type="cellIs" dxfId="1" priority="32" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T58">
+  <conditionalFormatting sqref="T57">
     <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L63">
+  <conditionalFormatting sqref="L62">
     <cfRule type="cellIs" dxfId="0" priority="25" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N63:O63">
+  <conditionalFormatting sqref="N62:O62">
     <cfRule type="cellIs" dxfId="1" priority="26" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T63">
+  <conditionalFormatting sqref="T62">
     <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L68">
+  <conditionalFormatting sqref="L67">
     <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N68:O68">
+  <conditionalFormatting sqref="N67:O67">
     <cfRule type="cellIs" dxfId="1" priority="20" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T68">
+  <conditionalFormatting sqref="T67">
     <cfRule type="cellIs" dxfId="1" priority="21" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L73">
+  <conditionalFormatting sqref="L72">
     <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N73:O73">
+  <conditionalFormatting sqref="N72:O72">
     <cfRule type="cellIs" dxfId="1" priority="14" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T73">
+  <conditionalFormatting sqref="T72">
     <cfRule type="cellIs" dxfId="1" priority="15" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L14:L17">
+  <conditionalFormatting sqref="L13:L16">
     <cfRule type="cellIs" dxfId="0" priority="82" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19:L22">
+  <conditionalFormatting sqref="L18:L21">
     <cfRule type="cellIs" dxfId="0" priority="76" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L24:L27">
+  <conditionalFormatting sqref="L23:L26">
     <cfRule type="cellIs" dxfId="0" priority="70" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L29:L32">
+  <conditionalFormatting sqref="L28:L31">
     <cfRule type="cellIs" dxfId="0" priority="64" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L34:L37">
+  <conditionalFormatting sqref="L33:L36">
     <cfRule type="cellIs" dxfId="0" priority="58" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L39:L42">
+  <conditionalFormatting sqref="L38:L41">
     <cfRule type="cellIs" dxfId="0" priority="52" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L44:L47">
+  <conditionalFormatting sqref="L43:L46">
     <cfRule type="cellIs" dxfId="0" priority="46" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L49:L52">
+  <conditionalFormatting sqref="L48:L51">
     <cfRule type="cellIs" dxfId="0" priority="40" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L54:L57">
+  <conditionalFormatting sqref="L53:L56">
     <cfRule type="cellIs" dxfId="0" priority="34" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L59:L62">
+  <conditionalFormatting sqref="L58:L61">
     <cfRule type="cellIs" dxfId="0" priority="28" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L64:L67">
+  <conditionalFormatting sqref="L63:L66">
     <cfRule type="cellIs" dxfId="0" priority="22" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L69:L72">
+  <conditionalFormatting sqref="L68:L71">
     <cfRule type="cellIs" dxfId="0" priority="16" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L74:L77">
+  <conditionalFormatting sqref="L73:L76">
     <cfRule type="cellIs" dxfId="0" priority="10" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T14:T17">
+  <conditionalFormatting sqref="T13:T16">
     <cfRule type="cellIs" dxfId="1" priority="84" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T19:T22">
+  <conditionalFormatting sqref="T18:T21">
     <cfRule type="cellIs" dxfId="1" priority="78" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T24:T27">
+  <conditionalFormatting sqref="T23:T26">
     <cfRule type="cellIs" dxfId="1" priority="72" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T29:T32">
+  <conditionalFormatting sqref="T28:T31">
     <cfRule type="cellIs" dxfId="1" priority="66" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T34:T37">
+  <conditionalFormatting sqref="T33:T36">
     <cfRule type="cellIs" dxfId="1" priority="60" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T39:T42">
+  <conditionalFormatting sqref="T38:T41">
     <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T44:T47">
+  <conditionalFormatting sqref="T43:T46">
     <cfRule type="cellIs" dxfId="1" priority="48" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T49:T52">
+  <conditionalFormatting sqref="T48:T51">
     <cfRule type="cellIs" dxfId="1" priority="42" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T54:T57">
+  <conditionalFormatting sqref="T53:T56">
     <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T59:T62">
+  <conditionalFormatting sqref="T58:T61">
     <cfRule type="cellIs" dxfId="1" priority="30" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T64:T67">
+  <conditionalFormatting sqref="T63:T66">
     <cfRule type="cellIs" dxfId="1" priority="24" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T69:T72">
+  <conditionalFormatting sqref="T68:T71">
     <cfRule type="cellIs" dxfId="1" priority="18" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T74:T77">
+  <conditionalFormatting sqref="T73:T76">
     <cfRule type="cellIs" dxfId="1" priority="12" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L8 L78:L95">
+  <conditionalFormatting sqref="L4:L8 L77:L94">
     <cfRule type="cellIs" dxfId="0" priority="97" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O8 N78:O95">
+  <conditionalFormatting sqref="N4:O8 N77:O94">
     <cfRule type="cellIs" dxfId="1" priority="98" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T4:T8 T78:T95">
+  <conditionalFormatting sqref="T4:T8 T77:T94">
     <cfRule type="cellIs" dxfId="1" priority="99" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N14:O17">
+  <conditionalFormatting sqref="N13:O16">
     <cfRule type="cellIs" dxfId="1" priority="83" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N19:O22">
+  <conditionalFormatting sqref="N18:O21">
     <cfRule type="cellIs" dxfId="1" priority="77" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N24:O27">
+  <conditionalFormatting sqref="N23:O26">
     <cfRule type="cellIs" dxfId="1" priority="71" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N29:O32">
+  <conditionalFormatting sqref="N28:O31">
     <cfRule type="cellIs" dxfId="1" priority="65" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N34:O37">
+  <conditionalFormatting sqref="N33:O36">
     <cfRule type="cellIs" dxfId="1" priority="59" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N39:O42">
+  <conditionalFormatting sqref="N38:O41">
     <cfRule type="cellIs" dxfId="1" priority="53" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N44:O47">
+  <conditionalFormatting sqref="N43:O46">
     <cfRule type="cellIs" dxfId="1" priority="47" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N49:O52">
+  <conditionalFormatting sqref="N48:O51">
     <cfRule type="cellIs" dxfId="1" priority="41" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N54:O57">
+  <conditionalFormatting sqref="N53:O56">
     <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N59:O62">
+  <conditionalFormatting sqref="N58:O61">
     <cfRule type="cellIs" dxfId="1" priority="29" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N64:O67">
+  <conditionalFormatting sqref="N63:O66">
     <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N69:O72">
+  <conditionalFormatting sqref="N68:O71">
     <cfRule type="cellIs" dxfId="1" priority="17" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N74:O77">
+  <conditionalFormatting sqref="N73:O76">
     <cfRule type="cellIs" dxfId="1" priority="11" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="V4:V95">
+    <dataValidation type="list" allowBlank="1" sqref="V4:V12 V13:V94">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11670,7 +11610,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -11690,16 +11630,16 @@
         <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>182</v>
@@ -11708,7 +11648,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -11722,19 +11662,19 @@
         <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -11751,22 +11691,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -11783,22 +11723,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>407</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11821,16 +11761,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11871,10 +11811,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>410</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>411</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11890,25 +11830,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>415</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>417</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11919,31 +11859,31 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>423</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11951,22 +11891,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>425</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11983,23 +11923,23 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>433</v>
-      </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
       </c>
@@ -12007,7 +11947,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -12015,22 +11955,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="429">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1017,6 +1017,12 @@
 3.实际插入order表的数据为78462条</t>
   </si>
   <si>
+    <t>200&gt;400&gt;600</t>
+  </si>
+  <si>
+    <t>13m==3(200)+5(400)+5(600)，逐渐升高</t>
+  </si>
+  <si>
     <t>R13</t>
   </si>
   <si>
@@ -1030,36 +1036,6 @@
   </si>
   <si>
     <t>单接口-冲击</t>
-  </si>
-  <si>
-    <t>W05</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>支付订单列表</t>
-  </si>
-  <si>
-    <t>R18</t>
-  </si>
-  <si>
-    <t>R19</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>W06</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>R22</t>
-  </si>
-  <si>
-    <t>R23</t>
   </si>
   <si>
     <t>R24</t>
@@ -5814,7 +5790,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X94"/>
+  <dimension ref="A1:X85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6525,13 +6501,13 @@
         <v>303</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="G12" s="12">
         <v>10</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>14</v>
@@ -6579,7 +6555,7 @@
     </row>
     <row r="13" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A13" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>14</v>
@@ -6648,7 +6624,7 @@
     </row>
     <row r="14" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A14" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>14</v>
@@ -6717,7 +6693,7 @@
     </row>
     <row r="15" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A15" s="12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>14</v>
@@ -6786,13 +6762,13 @@
     </row>
     <row r="16" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A16" s="12" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>82</v>
@@ -6853,1741 +6829,1739 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="24" customHeight="1" spans="1:24">
+    <row r="17" customFormat="1" ht="202" customHeight="1" spans="1:24">
       <c r="A17" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B17" s="4"/>
+        <v>322</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="C17" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>292</v>
+        <v>302</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F17" s="4">
-        <v>50</v>
+        <v>303</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>315</v>
       </c>
       <c r="G17" s="4">
         <v>10</v>
       </c>
       <c r="H17" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L17" s="23" t="e">
+        <f>IF(I17&gt;0,K17/I17,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T17" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A18" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" s="4">
+        <v>50</v>
+      </c>
+      <c r="G18" s="4">
+        <v>10</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="4" t="s">
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-    </row>
-    <row r="18" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A18" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+    </row>
+    <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A19" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F19" s="2">
         <v>100</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G19" s="2">
         <v>10</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" s="20" t="e">
-        <f t="shared" ref="L18:L21" si="2">IF(I18&gt;0,K18/I18,0)</f>
+      <c r="I19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L19" s="20" t="e">
+        <f t="shared" ref="L19:L22" si="2">IF(I19&gt;0,K19/I19,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T18" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V18" s="2" t="s">
+      <c r="M19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T19" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A19" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="W19" s="2"/>
+      <c r="X19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A20" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="D20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F20" s="4">
         <v>300</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G20" s="4">
         <v>10</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="23" t="e">
+      <c r="I20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L20" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T19" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V19" s="4" t="s">
+      <c r="M20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T20" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A20" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="W20" s="4"/>
+      <c r="X20" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A21" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F21" s="2">
         <v>500</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G21" s="2">
         <v>10</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L20" s="20" t="e">
+      <c r="I21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21" s="20" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T20" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V20" s="2" t="s">
+      <c r="M21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T21" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A21" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="W21" s="2"/>
+      <c r="X21" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A22" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F22" s="4">
         <v>500</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G22" s="4">
         <v>500</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" s="23" t="e">
+      <c r="I22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L22" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T21" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V21" s="4" t="s">
+      <c r="M22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T22" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A22" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4" t="s">
+      <c r="W22" s="4"/>
+      <c r="X22" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A23" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F23" s="4">
         <v>50</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G23" s="4">
         <v>10</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="15"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="4" t="s">
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-    </row>
-    <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A23" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A24" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F24" s="2">
         <v>100</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G24" s="2">
         <v>10</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L23" s="20" t="e">
-        <f t="shared" ref="L23:L26" si="3">IF(I23&gt;0,K23/I23,0)</f>
+      <c r="I24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24" s="20" t="e">
+        <f t="shared" ref="L24:L27" si="3">IF(I24&gt;0,K24/I24,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T23" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V23" s="2" t="s">
+      <c r="M24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T24" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A24" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="W24" s="2"/>
+      <c r="X24" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A25" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="D25" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F25" s="4">
         <v>300</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G25" s="4">
         <v>10</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="23" t="e">
+      <c r="I25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T24" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V24" s="4" t="s">
+      <c r="M25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T25" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W24" s="4"/>
-      <c r="X24" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A25" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="W25" s="4"/>
+      <c r="X25" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A26" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F26" s="2">
         <v>500</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G26" s="2">
         <v>10</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" s="20" t="e">
+      <c r="I26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26" s="20" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T25" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" s="2" t="s">
+      <c r="M26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T26" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A26" s="2" t="s">
+      <c r="W26" s="2"/>
+      <c r="X26" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A27" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F27" s="4">
         <v>500</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G27" s="4">
         <v>500</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L26" s="23" t="e">
+      <c r="I27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="23" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T26" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V26" s="4" t="s">
+      <c r="M27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T27" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A27" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4" t="s">
+      <c r="W27" s="4"/>
+      <c r="X27" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A28" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F28" s="4">
         <v>50</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G28" s="4">
         <v>10</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="4" t="s">
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
-    </row>
-    <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A28" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+    </row>
+    <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A29" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F29" s="2">
         <v>100</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G29" s="2">
         <v>10</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L28" s="20" t="e">
-        <f t="shared" ref="L28:L31" si="4">IF(I28&gt;0,K28/I28,0)</f>
+      <c r="I29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="20" t="e">
+        <f t="shared" ref="L29:L32" si="4">IF(I29&gt;0,K29/I29,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T28" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V28" s="2" t="s">
+      <c r="M29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T29" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A29" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="W29" s="2"/>
+      <c r="X29" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A30" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="D30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F30" s="4">
         <v>300</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G30" s="4">
         <v>10</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H30" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="23" t="e">
+      <c r="I30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T29" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V29" s="4" t="s">
+      <c r="M30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T30" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A30" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="W30" s="4"/>
+      <c r="X30" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A31" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F31" s="2">
         <v>500</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G31" s="2">
         <v>10</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L30" s="20" t="e">
+      <c r="I31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="20" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T30" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V30" s="2" t="s">
+      <c r="M31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T31" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V31" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A31" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="W31" s="2"/>
+      <c r="X31" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A32" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F32" s="4">
         <v>500</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G32" s="4">
         <v>500</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H32" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="23" t="e">
+      <c r="I32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32" s="23" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T31" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V31" s="4" t="s">
+      <c r="M32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T32" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A32" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4" t="s">
+      <c r="W32" s="4"/>
+      <c r="X32" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F33" s="4">
         <v>50</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G33" s="4">
         <v>10</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H33" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="15"/>
-      <c r="V32" s="4" t="s">
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-    </row>
-    <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A33" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+    </row>
+    <row r="34" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A34" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="D34" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F34" s="12">
         <v>100</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G34" s="12">
         <v>10</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H34" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L33" s="20" t="e">
-        <f t="shared" ref="L33:L36" si="5">IF(I33&gt;0,K33/I33,0)</f>
+      <c r="I34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34" s="19" t="e">
+        <f t="shared" ref="L34:L37" si="5">IF(I34&gt;0,K34/I34,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T33" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V33" s="2" t="s">
+      <c r="M34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O34" s="12"/>
+      <c r="P34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T34" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V34" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W33" s="2"/>
-      <c r="X33" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A34" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="W34" s="12"/>
+      <c r="X34" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A35" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="D35" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F35" s="12">
         <v>300</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G35" s="12">
         <v>10</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H35" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L34" s="23" t="e">
+      <c r="I35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T34" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V34" s="4" t="s">
+      <c r="M35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T35" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V35" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A35" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="W35" s="12"/>
+      <c r="X35" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A36" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="D36" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F36" s="12">
         <v>500</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G36" s="12">
         <v>10</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H36" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L35" s="20" t="e">
+      <c r="I36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T35" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V35" s="2" t="s">
+      <c r="M36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O36" s="12"/>
+      <c r="P36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T36" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V36" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W35" s="2"/>
-      <c r="X35" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A36" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="W36" s="12"/>
+      <c r="X36" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A37" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F37" s="12">
         <v>500</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G37" s="12">
         <v>500</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H37" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L36" s="23" t="e">
+      <c r="I37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T36" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V36" s="4" t="s">
+      <c r="M37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O37" s="12"/>
+      <c r="P37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T37" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V37" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A37" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4" t="s">
+      <c r="W37" s="12"/>
+      <c r="X37" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A38" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E37" s="4" t="s">
+      <c r="D38" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F38" s="4">
         <v>50</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G38" s="4">
         <v>10</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="16"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="4" t="s">
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-    </row>
-    <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A38" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+    </row>
+    <row r="39" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A39" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E39" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F39" s="12">
         <v>100</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G39" s="12">
         <v>10</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H39" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L38" s="20" t="e">
-        <f t="shared" ref="L38:L41" si="6">IF(I38&gt;0,K38/I38,0)</f>
+      <c r="I39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="24"/>
+      <c r="K39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39" s="19" t="e">
+        <f t="shared" ref="L39:L42" si="6">IF(I39&gt;0,K39/I39,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T38" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V38" s="2" t="s">
+      <c r="M39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O39" s="12"/>
+      <c r="P39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T39" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V39" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W38" s="2"/>
-      <c r="X38" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A39" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E39" s="4" t="s">
+      <c r="W39" s="12"/>
+      <c r="X39" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A40" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E40" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F40" s="12">
         <v>300</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G40" s="12">
         <v>10</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H40" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L39" s="23" t="e">
+      <c r="I40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="24"/>
+      <c r="K40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" s="19" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T39" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V39" s="4" t="s">
+      <c r="M40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T40" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V40" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A40" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="W40" s="12"/>
+      <c r="X40" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A41" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E41" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F41" s="12">
         <v>500</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G41" s="12">
         <v>10</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H41" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L40" s="20" t="e">
+      <c r="I41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="24"/>
+      <c r="K41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="19" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O40" s="2"/>
-      <c r="P40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T40" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V40" s="2" t="s">
+      <c r="M41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O41" s="12"/>
+      <c r="P41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T41" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V41" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W40" s="2"/>
-      <c r="X40" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A41" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="4" t="s">
+      <c r="W41" s="12"/>
+      <c r="X41" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A42" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F42" s="12">
         <v>500</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G42" s="12">
         <v>500</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H42" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L41" s="23" t="e">
+      <c r="I42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="24"/>
+      <c r="K42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42" s="19" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T41" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V41" s="4" t="s">
+      <c r="M42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O42" s="12"/>
+      <c r="P42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T42" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V42" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A42" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4" t="s">
+      <c r="W42" s="12"/>
+      <c r="X42" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A43" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E42" s="4" t="s">
+      <c r="D43" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F43" s="4">
         <v>50</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G43" s="4">
         <v>10</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="15"/>
-      <c r="O42" s="15"/>
-      <c r="P42" s="15"/>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="15"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="15"/>
-      <c r="V42" s="4" t="s">
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="15"/>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="15"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="15"/>
+      <c r="T43" s="16"/>
+      <c r="U43" s="15"/>
+      <c r="V43" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-    </row>
-    <row r="43" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A43" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F43" s="12">
-        <v>100</v>
-      </c>
-      <c r="G43" s="12">
-        <v>10</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L43" s="19" t="e">
-        <f t="shared" ref="L43:L46" si="7">IF(I43&gt;0,K43/I43,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O43" s="12"/>
-      <c r="P43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T43" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V43" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W43" s="12"/>
-      <c r="X43" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
     </row>
     <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A44" s="12" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>98</v>
+        <v>354</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F44" s="12">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G44" s="12">
         <v>10</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J44" s="12"/>
+      <c r="J44" s="24"/>
       <c r="K44" s="12" t="s">
         <v>14</v>
       </c>
       <c r="L44" s="19" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="L44:L47" si="7">IF(I44&gt;0,K44/I44,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M44" s="12" t="s">
@@ -8625,33 +8599,31 @@
     </row>
     <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A45" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="B45" s="12"/>
       <c r="C45" s="12" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>98</v>
+        <v>354</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F45" s="12">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G45" s="12">
         <v>10</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I45" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J45" s="12"/>
+      <c r="J45" s="24"/>
       <c r="K45" s="12" t="s">
         <v>14</v>
       </c>
@@ -8694,33 +8666,33 @@
     </row>
     <row r="46" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A46" s="12" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>98</v>
+        <v>354</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F46" s="12">
         <v>500</v>
       </c>
       <c r="G46" s="12">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I46" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J46" s="12"/>
+      <c r="J46" s="24"/>
       <c r="K46" s="12" t="s">
         <v>14</v>
       </c>
@@ -8761,139 +8733,141 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A47" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4" t="s">
+    <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A47" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F47" s="12">
+        <v>500</v>
+      </c>
+      <c r="G47" s="12">
+        <v>500</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" s="24"/>
+      <c r="K47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L47" s="19" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O47" s="12"/>
+      <c r="P47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T47" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V47" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W47" s="12"/>
+      <c r="X47" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A48" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D48" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F48" s="4">
         <v>50</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G48" s="4">
         <v>10</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H48" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="15"/>
-      <c r="V47" s="4" t="s">
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="15"/>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="15"/>
+      <c r="R48" s="15"/>
+      <c r="S48" s="15"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="15"/>
+      <c r="V48" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W47" s="4"/>
-      <c r="X47" s="4"/>
-    </row>
-    <row r="48" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A48" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F48" s="12">
-        <v>100</v>
-      </c>
-      <c r="G48" s="12">
-        <v>10</v>
-      </c>
-      <c r="H48" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J48" s="24"/>
-      <c r="K48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L48" s="19" t="e">
-        <f t="shared" ref="L48:L51" si="8">IF(I48&gt;0,K48/I48,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O48" s="12"/>
-      <c r="P48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T48" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V48" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W48" s="12"/>
-      <c r="X48" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
     </row>
     <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A49" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="B49" s="12"/>
+        <v>359</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C49" s="12" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F49" s="12">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G49" s="12">
         <v>10</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>14</v>
@@ -8903,7 +8877,7 @@
         <v>14</v>
       </c>
       <c r="L49" s="19" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="L49:L52" si="8">IF(I49&gt;0,K49/I49,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M49" s="12" t="s">
@@ -8941,28 +8915,26 @@
     </row>
     <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A50" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="B50" s="12"/>
       <c r="C50" s="12" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F50" s="12">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G50" s="12">
         <v>10</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I50" s="12" t="s">
         <v>14</v>
@@ -9010,28 +8982,28 @@
     </row>
     <row r="51" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A51" s="12" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F51" s="12">
         <v>500</v>
       </c>
       <c r="G51" s="12">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>14</v>
@@ -9077,139 +9049,141 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A52" s="2" t="s">
+    <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A52" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4" t="s">
+      <c r="E52" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" s="12">
+        <v>500</v>
+      </c>
+      <c r="G52" s="12">
+        <v>500</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" s="24"/>
+      <c r="K52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" s="19" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O52" s="12"/>
+      <c r="P52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T52" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V52" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W52" s="12"/>
+      <c r="X52" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A53" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F53" s="4">
         <v>50</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G53" s="4">
         <v>10</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H53" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="15"/>
-      <c r="O52" s="15"/>
-      <c r="P52" s="15"/>
-      <c r="Q52" s="15"/>
-      <c r="R52" s="15"/>
-      <c r="S52" s="15"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="15"/>
-      <c r="V52" s="4" t="s">
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15"/>
+      <c r="R53" s="15"/>
+      <c r="S53" s="15"/>
+      <c r="T53" s="16"/>
+      <c r="U53" s="15"/>
+      <c r="V53" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-    </row>
-    <row r="53" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A53" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F53" s="12">
-        <v>100</v>
-      </c>
-      <c r="G53" s="12">
-        <v>10</v>
-      </c>
-      <c r="H53" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J53" s="24"/>
-      <c r="K53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L53" s="19" t="e">
-        <f t="shared" ref="L53:L56" si="9">IF(I53&gt;0,K53/I53,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O53" s="12"/>
-      <c r="P53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T53" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U53" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V53" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W53" s="12"/>
-      <c r="X53" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
     </row>
     <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A54" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="B54" s="12"/>
+        <v>365</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C54" s="12" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F54" s="12">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G54" s="12">
         <v>10</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>14</v>
@@ -9219,7 +9193,7 @@
         <v>14</v>
       </c>
       <c r="L54" s="19" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="L54:L57" si="9">IF(I54&gt;0,K54/I54,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M54" s="12" t="s">
@@ -9257,28 +9231,26 @@
     </row>
     <row r="55" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A55" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B55" s="12"/>
       <c r="C55" s="12" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F55" s="12">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G55" s="12">
         <v>10</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I55" s="12" t="s">
         <v>14</v>
@@ -9326,28 +9298,28 @@
     </row>
     <row r="56" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A56" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F56" s="12">
         <v>500</v>
       </c>
       <c r="G56" s="12">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>14</v>
@@ -9393,149 +9365,151 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A57" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4" t="s">
+    <row r="57" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A57" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F57" s="12">
+        <v>500</v>
+      </c>
+      <c r="G57" s="12">
+        <v>500</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J57" s="24"/>
+      <c r="K57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L57" s="19" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O57" s="12"/>
+      <c r="P57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T57" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V57" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W57" s="12"/>
+      <c r="X57" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A58" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E57" s="4" t="s">
+      <c r="D58" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F58" s="4">
         <v>50</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G58" s="4">
         <v>10</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="15"/>
-      <c r="N57" s="15"/>
-      <c r="O57" s="15"/>
-      <c r="P57" s="15"/>
-      <c r="Q57" s="15"/>
-      <c r="R57" s="15"/>
-      <c r="S57" s="15"/>
-      <c r="T57" s="16"/>
-      <c r="U57" s="15"/>
-      <c r="V57" s="4" t="s">
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="15"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="15"/>
+      <c r="P58" s="15"/>
+      <c r="Q58" s="15"/>
+      <c r="R58" s="15"/>
+      <c r="S58" s="15"/>
+      <c r="T58" s="16"/>
+      <c r="U58" s="15"/>
+      <c r="V58" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
-    </row>
-    <row r="58" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A58" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F58" s="12">
-        <v>100</v>
-      </c>
-      <c r="G58" s="12">
-        <v>10</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J58" s="24"/>
-      <c r="K58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L58" s="19" t="e">
-        <f t="shared" ref="L58:L61" si="10">IF(I58&gt;0,K58/I58,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O58" s="12"/>
-      <c r="P58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T58" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V58" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W58" s="12"/>
-      <c r="X58" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
     </row>
     <row r="59" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A59" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="B59" s="12"/>
+        <v>370</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C59" s="12" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F59" s="12">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G59" s="12">
         <v>10</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J59" s="24"/>
+      <c r="J59" s="12"/>
       <c r="K59" s="12" t="s">
         <v>14</v>
       </c>
       <c r="L59" s="19" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="L59:L62" si="10">IF(I59&gt;0,K59/I59,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M59" s="12" t="s">
@@ -9573,33 +9547,31 @@
     </row>
     <row r="60" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A60" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="B60" s="12"/>
       <c r="C60" s="12" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F60" s="12">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G60" s="12">
         <v>10</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I60" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J60" s="24"/>
+      <c r="J60" s="12"/>
       <c r="K60" s="12" t="s">
         <v>14</v>
       </c>
@@ -9642,33 +9614,33 @@
     </row>
     <row r="61" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A61" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>368</v>
-      </c>
       <c r="E61" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F61" s="12">
         <v>500</v>
       </c>
       <c r="G61" s="12">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J61" s="24"/>
+      <c r="J61" s="12"/>
       <c r="K61" s="12" t="s">
         <v>14</v>
       </c>
@@ -9709,149 +9681,151 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A62" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4" t="s">
+    <row r="62" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A62" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F62" s="12">
+        <v>500</v>
+      </c>
+      <c r="G62" s="12">
+        <v>500</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L62" s="19" t="e">
+        <f t="shared" si="10"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T62" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U62" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V62" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A63" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E62" s="4" t="s">
+      <c r="D63" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F63" s="4">
         <v>50</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G63" s="4">
         <v>10</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="15"/>
-      <c r="N62" s="15"/>
-      <c r="O62" s="15"/>
-      <c r="P62" s="15"/>
-      <c r="Q62" s="15"/>
-      <c r="R62" s="15"/>
-      <c r="S62" s="15"/>
-      <c r="T62" s="16"/>
-      <c r="U62" s="15"/>
-      <c r="V62" s="4" t="s">
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="15"/>
+      <c r="P63" s="15"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="15"/>
+      <c r="S63" s="15"/>
+      <c r="T63" s="16"/>
+      <c r="U63" s="15"/>
+      <c r="V63" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W62" s="4"/>
-      <c r="X62" s="4"/>
-    </row>
-    <row r="63" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A63" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F63" s="12">
-        <v>100</v>
-      </c>
-      <c r="G63" s="12">
-        <v>10</v>
-      </c>
-      <c r="H63" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J63" s="24"/>
-      <c r="K63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L63" s="19" t="e">
-        <f t="shared" ref="L63:L66" si="11">IF(I63&gt;0,K63/I63,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O63" s="12"/>
-      <c r="P63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T63" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U63" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V63" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W63" s="12"/>
-      <c r="X63" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
     </row>
     <row r="64" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A64" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="B64" s="12"/>
+        <v>376</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C64" s="12" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F64" s="12">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G64" s="12">
         <v>10</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J64" s="24"/>
+      <c r="J64" s="12"/>
       <c r="K64" s="12" t="s">
         <v>14</v>
       </c>
       <c r="L64" s="19" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="L64:L67" si="11">IF(I64&gt;0,K64/I64,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M64" s="12" t="s">
@@ -9889,33 +9863,31 @@
     </row>
     <row r="65" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A65" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="B65" s="12"/>
       <c r="C65" s="12" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F65" s="12">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G65" s="12">
         <v>10</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J65" s="24"/>
+      <c r="J65" s="12"/>
       <c r="K65" s="12" t="s">
         <v>14</v>
       </c>
@@ -9958,33 +9930,33 @@
     </row>
     <row r="66" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A66" s="12" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F66" s="12">
         <v>500</v>
       </c>
       <c r="G66" s="12">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J66" s="24"/>
+      <c r="J66" s="12"/>
       <c r="K66" s="12" t="s">
         <v>14</v>
       </c>
@@ -10025,1105 +9997,542 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A67" s="2" t="s">
+    <row r="67" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A67" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F67" s="4">
-        <v>50</v>
-      </c>
-      <c r="G67" s="4">
-        <v>10</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="15"/>
-      <c r="R67" s="15"/>
-      <c r="S67" s="15"/>
-      <c r="T67" s="16"/>
-      <c r="U67" s="15"/>
-      <c r="V67" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
-    </row>
-    <row r="68" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A68" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F68" s="12">
-        <v>100</v>
-      </c>
-      <c r="G68" s="12">
-        <v>10</v>
-      </c>
-      <c r="H68" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J68" s="12"/>
-      <c r="K68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L68" s="19" t="e">
-        <f t="shared" ref="L68:L71" si="12">IF(I68&gt;0,K68/I68,0)</f>
+      <c r="E67" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F67" s="12">
+        <v>500</v>
+      </c>
+      <c r="G67" s="12">
+        <v>500</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L67" s="19" t="e">
+        <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O68" s="12"/>
-      <c r="P68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T68" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V68" s="12" t="s">
+      <c r="M67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O67" s="12"/>
+      <c r="P67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T67" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V67" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W68" s="12"/>
-      <c r="X68" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A69" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F69" s="12">
-        <v>300</v>
-      </c>
-      <c r="G69" s="12">
-        <v>10</v>
-      </c>
-      <c r="H69" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L69" s="19" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O69" s="12"/>
-      <c r="P69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T69" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U69" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V69" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W69" s="12"/>
-      <c r="X69" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A70" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F70" s="12">
-        <v>500</v>
-      </c>
-      <c r="G70" s="12">
-        <v>10</v>
-      </c>
-      <c r="H70" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J70" s="12"/>
-      <c r="K70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L70" s="19" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O70" s="12"/>
-      <c r="P70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T70" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U70" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V70" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W70" s="12"/>
-      <c r="X70" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A71" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F71" s="12">
-        <v>500</v>
-      </c>
-      <c r="G71" s="12">
-        <v>500</v>
-      </c>
-      <c r="H71" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J71" s="12"/>
-      <c r="K71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L71" s="19" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O71" s="12"/>
-      <c r="P71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T71" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U71" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V71" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W71" s="12"/>
-      <c r="X71" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A72" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F72" s="4">
-        <v>50</v>
-      </c>
-      <c r="G72" s="4">
-        <v>10</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="15"/>
-      <c r="N72" s="15"/>
-      <c r="O72" s="15"/>
-      <c r="P72" s="15"/>
-      <c r="Q72" s="15"/>
-      <c r="R72" s="15"/>
-      <c r="S72" s="15"/>
-      <c r="T72" s="16"/>
-      <c r="U72" s="15"/>
-      <c r="V72" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W72" s="4"/>
-      <c r="X72" s="4"/>
-    </row>
-    <row r="73" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A73" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F73" s="12">
-        <v>100</v>
-      </c>
-      <c r="G73" s="12">
-        <v>10</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L73" s="19" t="e">
-        <f t="shared" ref="L73:L76" si="13">IF(I73&gt;0,K73/I73,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O73" s="12"/>
-      <c r="P73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T73" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V73" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W73" s="12"/>
-      <c r="X73" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="74" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A74" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F74" s="12">
-        <v>300</v>
-      </c>
-      <c r="G74" s="12">
-        <v>10</v>
-      </c>
-      <c r="H74" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J74" s="12"/>
-      <c r="K74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L74" s="19" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O74" s="12"/>
-      <c r="P74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T74" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U74" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V74" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W74" s="12"/>
-      <c r="X74" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A75" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F75" s="12">
-        <v>500</v>
-      </c>
-      <c r="G75" s="12">
-        <v>10</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L75" s="19" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O75" s="12"/>
-      <c r="P75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T75" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U75" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V75" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W75" s="12"/>
-      <c r="X75" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A76" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F76" s="12">
-        <v>500</v>
-      </c>
-      <c r="G76" s="12">
-        <v>500</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L76" s="19" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O76" s="12"/>
-      <c r="P76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T76" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U76" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V76" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W76" s="12"/>
-      <c r="X76" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="W67" s="12"/>
+      <c r="X67" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1" spans="1:24">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="20"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="20"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
+    </row>
+    <row r="69" ht="24" customHeight="1" spans="1:24">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="23"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="23"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+    </row>
+    <row r="70" ht="24" customHeight="1" spans="1:24">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="20"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
+    </row>
+    <row r="71" ht="24" customHeight="1" spans="1:24">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="23"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+    </row>
+    <row r="72" ht="24" customHeight="1" spans="1:24">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="20"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="20"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="2"/>
+      <c r="W72" s="2"/>
+      <c r="X72" s="2"/>
+    </row>
+    <row r="73" ht="24" customHeight="1" spans="1:24">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="23"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+      <c r="S73" s="4"/>
+      <c r="T73" s="23"/>
+      <c r="U73" s="4"/>
+      <c r="V73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+    </row>
+    <row r="74" ht="24" customHeight="1" spans="1:24">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="20"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="2"/>
+      <c r="T74" s="20"/>
+      <c r="U74" s="2"/>
+      <c r="V74" s="2"/>
+      <c r="W74" s="2"/>
+      <c r="X74" s="2"/>
+    </row>
+    <row r="75" ht="24" customHeight="1" spans="1:24">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="23"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="23"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+    </row>
+    <row r="76" ht="24" customHeight="1" spans="1:24">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="20"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="2"/>
+      <c r="T76" s="20"/>
+      <c r="U76" s="2"/>
+      <c r="V76" s="2"/>
+      <c r="W76" s="2"/>
+      <c r="X76" s="2"/>
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:24">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="20"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
-      <c r="T77" s="20"/>
-      <c r="U77" s="2"/>
-      <c r="V77" s="2"/>
-      <c r="W77" s="2"/>
-      <c r="X77" s="2"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="23"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="23"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:24">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="23"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="23"/>
-      <c r="U78" s="4"/>
-      <c r="V78" s="4"/>
-      <c r="W78" s="4"/>
-      <c r="X78" s="4"/>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="20"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="S78" s="2"/>
+      <c r="T78" s="20"/>
+      <c r="U78" s="2"/>
+      <c r="V78" s="2"/>
+      <c r="W78" s="2"/>
+      <c r="X78" s="2"/>
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:24">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="20"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
-      <c r="T79" s="20"/>
-      <c r="U79" s="2"/>
-      <c r="V79" s="2"/>
-      <c r="W79" s="2"/>
-      <c r="X79" s="2"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="23"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="23"/>
+      <c r="U79" s="4"/>
+      <c r="V79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:24">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="23"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="4"/>
-      <c r="S80" s="4"/>
-      <c r="T80" s="23"/>
-      <c r="U80" s="4"/>
-      <c r="V80" s="4"/>
-      <c r="W80" s="4"/>
-      <c r="X80" s="4"/>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="20"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
+      <c r="R80" s="2"/>
+      <c r="S80" s="2"/>
+      <c r="T80" s="20"/>
+      <c r="U80" s="2"/>
+      <c r="V80" s="2"/>
+      <c r="W80" s="2"/>
+      <c r="X80" s="2"/>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:24">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="20"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" s="2"/>
-      <c r="Q81" s="2"/>
-      <c r="R81" s="2"/>
-      <c r="S81" s="2"/>
-      <c r="T81" s="20"/>
-      <c r="U81" s="2"/>
-      <c r="V81" s="2"/>
-      <c r="W81" s="2"/>
-      <c r="X81" s="2"/>
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="23"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="4"/>
+      <c r="S81" s="4"/>
+      <c r="T81" s="23"/>
+      <c r="U81" s="4"/>
+      <c r="V81" s="4"/>
+      <c r="W81" s="4"/>
+      <c r="X81" s="4"/>
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:24">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="23"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
-      <c r="Q82" s="4"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
-      <c r="T82" s="23"/>
-      <c r="U82" s="4"/>
-      <c r="V82" s="4"/>
-      <c r="W82" s="4"/>
-      <c r="X82" s="4"/>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="20"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
+      <c r="R82" s="2"/>
+      <c r="S82" s="2"/>
+      <c r="T82" s="20"/>
+      <c r="U82" s="2"/>
+      <c r="V82" s="2"/>
+      <c r="W82" s="2"/>
+      <c r="X82" s="2"/>
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:24">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="L83" s="20"/>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" s="2"/>
-      <c r="Q83" s="2"/>
-      <c r="R83" s="2"/>
-      <c r="S83" s="2"/>
-      <c r="T83" s="20"/>
-      <c r="U83" s="2"/>
-      <c r="V83" s="2"/>
-      <c r="W83" s="2"/>
-      <c r="X83" s="2"/>
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="23"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="4"/>
+      <c r="S83" s="4"/>
+      <c r="T83" s="23"/>
+      <c r="U83" s="4"/>
+      <c r="V83" s="4"/>
+      <c r="W83" s="4"/>
+      <c r="X83" s="4"/>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:24">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="23"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
-      <c r="Q84" s="4"/>
-      <c r="R84" s="4"/>
-      <c r="S84" s="4"/>
-      <c r="T84" s="23"/>
-      <c r="U84" s="4"/>
-      <c r="V84" s="4"/>
-      <c r="W84" s="4"/>
-      <c r="X84" s="4"/>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="20"/>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="2"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="2"/>
+      <c r="T84" s="20"/>
+      <c r="U84" s="2"/>
+      <c r="V84" s="2"/>
+      <c r="W84" s="2"/>
+      <c r="X84" s="2"/>
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:24">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
-      <c r="L85" s="20"/>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" s="2"/>
-      <c r="Q85" s="2"/>
-      <c r="R85" s="2"/>
-      <c r="S85" s="2"/>
-      <c r="T85" s="20"/>
-      <c r="U85" s="2"/>
-      <c r="V85" s="2"/>
-      <c r="W85" s="2"/>
-      <c r="X85" s="2"/>
-    </row>
-    <row r="86" ht="24" customHeight="1" spans="1:24">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="23"/>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-      <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
-      <c r="Q86" s="4"/>
-      <c r="R86" s="4"/>
-      <c r="S86" s="4"/>
-      <c r="T86" s="23"/>
-      <c r="U86" s="4"/>
-      <c r="V86" s="4"/>
-      <c r="W86" s="4"/>
-      <c r="X86" s="4"/>
-    </row>
-    <row r="87" ht="24" customHeight="1" spans="1:24">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="20"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
-      <c r="T87" s="20"/>
-      <c r="U87" s="2"/>
-      <c r="V87" s="2"/>
-      <c r="W87" s="2"/>
-      <c r="X87" s="2"/>
-    </row>
-    <row r="88" ht="24" customHeight="1" spans="1:24">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="23"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="23"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4"/>
-      <c r="W88" s="4"/>
-      <c r="X88" s="4"/>
-    </row>
-    <row r="89" ht="24" customHeight="1" spans="1:24">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="20"/>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" s="2"/>
-      <c r="Q89" s="2"/>
-      <c r="R89" s="2"/>
-      <c r="S89" s="2"/>
-      <c r="T89" s="20"/>
-      <c r="U89" s="2"/>
-      <c r="V89" s="2"/>
-      <c r="W89" s="2"/>
-      <c r="X89" s="2"/>
-    </row>
-    <row r="90" ht="24" customHeight="1" spans="1:24">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="23"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-      <c r="T90" s="23"/>
-      <c r="U90" s="4"/>
-      <c r="V90" s="4"/>
-      <c r="W90" s="4"/>
-      <c r="X90" s="4"/>
-    </row>
-    <row r="91" ht="24" customHeight="1" spans="1:24">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="20"/>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" s="2"/>
-      <c r="Q91" s="2"/>
-      <c r="R91" s="2"/>
-      <c r="S91" s="2"/>
-      <c r="T91" s="20"/>
-      <c r="U91" s="2"/>
-      <c r="V91" s="2"/>
-      <c r="W91" s="2"/>
-      <c r="X91" s="2"/>
-    </row>
-    <row r="92" ht="24" customHeight="1" spans="1:24">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="23"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="23"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="4"/>
-      <c r="X92" s="4"/>
-    </row>
-    <row r="93" ht="24" customHeight="1" spans="1:24">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="L93" s="20"/>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" s="2"/>
-      <c r="Q93" s="2"/>
-      <c r="R93" s="2"/>
-      <c r="S93" s="2"/>
-      <c r="T93" s="20"/>
-      <c r="U93" s="2"/>
-      <c r="V93" s="2"/>
-      <c r="W93" s="2"/>
-      <c r="X93" s="2"/>
-    </row>
-    <row r="94" ht="24" customHeight="1" spans="1:24">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="23"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="23"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4"/>
-      <c r="W94" s="4"/>
-      <c r="X94" s="4"/>
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="23"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4"/>
+      <c r="R85" s="4"/>
+      <c r="S85" s="4"/>
+      <c r="T85" s="23"/>
+      <c r="U85" s="4"/>
+      <c r="V85" s="4"/>
+      <c r="W85" s="4"/>
+      <c r="X85" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11190,181 +10599,166 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17">
-    <cfRule type="cellIs" dxfId="0" priority="79" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="70" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N17:O17">
-    <cfRule type="cellIs" dxfId="1" priority="80" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="71" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T17">
-    <cfRule type="cellIs" dxfId="1" priority="81" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="72" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L22">
-    <cfRule type="cellIs" dxfId="0" priority="73" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22:O22">
-    <cfRule type="cellIs" dxfId="1" priority="74" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T22">
-    <cfRule type="cellIs" dxfId="1" priority="75" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L27">
+  <conditionalFormatting sqref="L18">
     <cfRule type="cellIs" dxfId="0" priority="67" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N27:O27">
+  <conditionalFormatting sqref="N18:O18">
     <cfRule type="cellIs" dxfId="1" priority="68" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T27">
+  <conditionalFormatting sqref="T18">
     <cfRule type="cellIs" dxfId="1" priority="69" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L32">
+  <conditionalFormatting sqref="L23">
     <cfRule type="cellIs" dxfId="0" priority="61" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N32:O32">
+  <conditionalFormatting sqref="N23:O23">
     <cfRule type="cellIs" dxfId="1" priority="62" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T32">
+  <conditionalFormatting sqref="T23">
     <cfRule type="cellIs" dxfId="1" priority="63" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L37">
+  <conditionalFormatting sqref="L28">
     <cfRule type="cellIs" dxfId="0" priority="55" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N37:O37">
+  <conditionalFormatting sqref="N28:O28">
     <cfRule type="cellIs" dxfId="1" priority="56" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T37">
+  <conditionalFormatting sqref="T28">
     <cfRule type="cellIs" dxfId="1" priority="57" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L42">
+  <conditionalFormatting sqref="L33">
     <cfRule type="cellIs" dxfId="0" priority="49" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N42:O42">
+  <conditionalFormatting sqref="N33:O33">
     <cfRule type="cellIs" dxfId="1" priority="50" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T42">
+  <conditionalFormatting sqref="T33">
     <cfRule type="cellIs" dxfId="1" priority="51" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L47">
+  <conditionalFormatting sqref="L38">
     <cfRule type="cellIs" dxfId="0" priority="43" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N47:O47">
+  <conditionalFormatting sqref="N38:O38">
     <cfRule type="cellIs" dxfId="1" priority="44" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T47">
+  <conditionalFormatting sqref="T38">
     <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L52">
+  <conditionalFormatting sqref="L43">
     <cfRule type="cellIs" dxfId="0" priority="37" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N52:O52">
+  <conditionalFormatting sqref="N43:O43">
     <cfRule type="cellIs" dxfId="1" priority="38" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T52">
+  <conditionalFormatting sqref="T43">
     <cfRule type="cellIs" dxfId="1" priority="39" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L57">
+  <conditionalFormatting sqref="L48">
     <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N57:O57">
+  <conditionalFormatting sqref="N48:O48">
     <cfRule type="cellIs" dxfId="1" priority="32" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T57">
+  <conditionalFormatting sqref="T48">
     <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L62">
+  <conditionalFormatting sqref="L53">
     <cfRule type="cellIs" dxfId="0" priority="25" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N62:O62">
+  <conditionalFormatting sqref="N53:O53">
     <cfRule type="cellIs" dxfId="1" priority="26" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T62">
+  <conditionalFormatting sqref="T53">
     <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L67">
+  <conditionalFormatting sqref="L58">
     <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N67:O67">
+  <conditionalFormatting sqref="N58:O58">
     <cfRule type="cellIs" dxfId="1" priority="20" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T67">
+  <conditionalFormatting sqref="T58">
     <cfRule type="cellIs" dxfId="1" priority="21" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L72">
+  <conditionalFormatting sqref="L63">
     <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N72:O72">
+  <conditionalFormatting sqref="N63:O63">
     <cfRule type="cellIs" dxfId="1" priority="14" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T72">
+  <conditionalFormatting sqref="T63">
     <cfRule type="cellIs" dxfId="1" priority="15" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -11374,62 +10768,52 @@
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L18:L21">
-    <cfRule type="cellIs" dxfId="0" priority="76" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L23:L26">
-    <cfRule type="cellIs" dxfId="0" priority="70" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L28:L31">
+  <conditionalFormatting sqref="L19:L22">
     <cfRule type="cellIs" dxfId="0" priority="64" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L33:L36">
+  <conditionalFormatting sqref="L24:L27">
     <cfRule type="cellIs" dxfId="0" priority="58" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L38:L41">
+  <conditionalFormatting sqref="L29:L32">
     <cfRule type="cellIs" dxfId="0" priority="52" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L43:L46">
+  <conditionalFormatting sqref="L34:L37">
     <cfRule type="cellIs" dxfId="0" priority="46" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L48:L51">
+  <conditionalFormatting sqref="L39:L42">
     <cfRule type="cellIs" dxfId="0" priority="40" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L53:L56">
+  <conditionalFormatting sqref="L44:L47">
     <cfRule type="cellIs" dxfId="0" priority="34" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L58:L61">
+  <conditionalFormatting sqref="L49:L52">
     <cfRule type="cellIs" dxfId="0" priority="28" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L63:L66">
+  <conditionalFormatting sqref="L54:L57">
     <cfRule type="cellIs" dxfId="0" priority="22" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L68:L71">
+  <conditionalFormatting sqref="L59:L62">
     <cfRule type="cellIs" dxfId="0" priority="16" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L73:L76">
+  <conditionalFormatting sqref="L64:L67">
     <cfRule type="cellIs" dxfId="0" priority="10" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
@@ -11439,77 +10823,67 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T18:T21">
-    <cfRule type="cellIs" dxfId="1" priority="78" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T23:T26">
-    <cfRule type="cellIs" dxfId="1" priority="72" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T28:T31">
+  <conditionalFormatting sqref="T19:T22">
     <cfRule type="cellIs" dxfId="1" priority="66" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T33:T36">
+  <conditionalFormatting sqref="T24:T27">
     <cfRule type="cellIs" dxfId="1" priority="60" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T38:T41">
+  <conditionalFormatting sqref="T29:T32">
     <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T43:T46">
+  <conditionalFormatting sqref="T34:T37">
     <cfRule type="cellIs" dxfId="1" priority="48" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T48:T51">
+  <conditionalFormatting sqref="T39:T42">
     <cfRule type="cellIs" dxfId="1" priority="42" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T53:T56">
+  <conditionalFormatting sqref="T44:T47">
     <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T58:T61">
+  <conditionalFormatting sqref="T49:T52">
     <cfRule type="cellIs" dxfId="1" priority="30" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T63:T66">
+  <conditionalFormatting sqref="T54:T57">
     <cfRule type="cellIs" dxfId="1" priority="24" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T68:T71">
+  <conditionalFormatting sqref="T59:T62">
     <cfRule type="cellIs" dxfId="1" priority="18" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T73:T76">
+  <conditionalFormatting sqref="T64:T67">
     <cfRule type="cellIs" dxfId="1" priority="12" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L8 L77:L94">
+  <conditionalFormatting sqref="L4:L8 L68:L85">
     <cfRule type="cellIs" dxfId="0" priority="97" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O8 N77:O94">
+  <conditionalFormatting sqref="N4:O8 N68:O85">
     <cfRule type="cellIs" dxfId="1" priority="98" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T4:T8 T77:T94">
+  <conditionalFormatting sqref="T4:T8 T68:T85">
     <cfRule type="cellIs" dxfId="1" priority="99" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -11519,68 +10893,58 @@
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18:O21">
-    <cfRule type="cellIs" dxfId="1" priority="77" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N23:O26">
-    <cfRule type="cellIs" dxfId="1" priority="71" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N28:O31">
+  <conditionalFormatting sqref="N19:O22">
     <cfRule type="cellIs" dxfId="1" priority="65" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N33:O36">
+  <conditionalFormatting sqref="N24:O27">
     <cfRule type="cellIs" dxfId="1" priority="59" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N38:O41">
+  <conditionalFormatting sqref="N29:O32">
     <cfRule type="cellIs" dxfId="1" priority="53" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N43:O46">
+  <conditionalFormatting sqref="N34:O37">
     <cfRule type="cellIs" dxfId="1" priority="47" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N48:O51">
+  <conditionalFormatting sqref="N39:O42">
     <cfRule type="cellIs" dxfId="1" priority="41" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N53:O56">
+  <conditionalFormatting sqref="N44:O47">
     <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N58:O61">
+  <conditionalFormatting sqref="N49:O52">
     <cfRule type="cellIs" dxfId="1" priority="29" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N63:O66">
+  <conditionalFormatting sqref="N54:O57">
     <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N68:O71">
+  <conditionalFormatting sqref="N59:O62">
     <cfRule type="cellIs" dxfId="1" priority="17" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N73:O76">
+  <conditionalFormatting sqref="N64:O67">
     <cfRule type="cellIs" dxfId="1" priority="11" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="V4:V12 V13:V94">
+    <dataValidation type="list" allowBlank="1" sqref="V4:V16 V17:V85">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11610,7 +10974,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -11630,16 +10994,16 @@
         <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>182</v>
@@ -11648,7 +11012,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -11662,19 +11026,19 @@
         <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -11691,22 +11055,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -11723,22 +11087,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11761,16 +11125,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11811,10 +11175,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11830,25 +11194,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11859,22 +11223,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -11883,7 +11247,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11891,22 +11255,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11923,22 +11287,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11947,7 +11311,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11955,22 +11319,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="01_业务总览" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="424">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1041,34 +1041,21 @@
     <t>R24</t>
   </si>
   <si>
-    <t>W07</t>
-  </si>
-  <si>
-    <t>R25</t>
-  </si>
-  <si>
-    <t>R26</t>
+    <t>600~700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.在长达 13 分钟的压力测试中，系统平均每秒处理了 1138个请求，不具有报错。
+2.小程序未有卡顿等情况。
+</t>
   </si>
   <si>
     <t>R27</t>
   </si>
   <si>
-    <t>R28</t>
-  </si>
-  <si>
-    <t>W08</t>
-  </si>
-  <si>
-    <t>R29</t>
+    <t>R31</t>
   </si>
   <si>
     <t>赏柜商品</t>
-  </si>
-  <si>
-    <t>R30</t>
-  </si>
-  <si>
-    <t>R31</t>
   </si>
   <si>
     <t>R32</t>
@@ -1560,7 +1547,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1624,6 +1611,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1996,7 +1989,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2020,16 +2013,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2038,89 +2031,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2185,13 +2178,22 @@
     <xf numFmtId="10" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3831,6 +3833,216 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>143510</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>249555</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1051560</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>840740</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="图片 32"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="29934535" y="29129355"/>
+          <a:ext cx="908050" cy="591185"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>523240</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1164590</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1129030</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1613535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="图片 39"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="30314265" y="30044390"/>
+          <a:ext cx="605790" cy="448945"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1480185</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>290195</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2270760</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>864235</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="图片 40"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31271210" y="29169995"/>
+          <a:ext cx="790575" cy="574040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1539240</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1031875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2332355</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1700530</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="图片 41"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31330265" y="29911675"/>
+          <a:ext cx="793115" cy="668655"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>493395</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1901190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1125855</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>2489835</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="图片 42"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30284420" y="30780990"/>
+          <a:ext cx="632460" cy="588645"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4122,237 +4334,237 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18" style="30" customWidth="1"/>
-    <col min="2" max="2" width="34" style="30" customWidth="1"/>
-    <col min="3" max="3" width="42" style="30" customWidth="1"/>
-    <col min="4" max="4" width="14" style="30" customWidth="1"/>
-    <col min="5" max="5" width="22.75" style="30" customWidth="1"/>
-    <col min="6" max="6" width="25.25" style="30" customWidth="1"/>
-    <col min="7" max="7" width="14" style="30" customWidth="1"/>
-    <col min="8" max="8" width="30" style="30" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="30"/>
+    <col min="1" max="1" width="18" style="33" customWidth="1"/>
+    <col min="2" max="2" width="34" style="33" customWidth="1"/>
+    <col min="3" max="3" width="42" style="33" customWidth="1"/>
+    <col min="4" max="4" width="14" style="33" customWidth="1"/>
+    <col min="5" max="5" width="22.75" style="33" customWidth="1"/>
+    <col min="6" max="6" width="25.25" style="33" customWidth="1"/>
+    <col min="7" max="7" width="14" style="33" customWidth="1"/>
+    <col min="8" max="8" width="30" style="33" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="35" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="33" t="s">
+      <c r="F4" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:8">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="36" t="s">
+      <c r="D5" s="40"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="39" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="33" t="s">
+      <c r="D6" s="40"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="39">
         <v>500</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="37"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="36" t="s">
+      <c r="D7" s="40"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="39" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="33" t="s">
+      <c r="D8" s="40"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="H8" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="39"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="36" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="39" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8">
       <c r="A14" s="7" t="s">
@@ -5600,176 +5812,176 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:9">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:9">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="31">
         <v>500</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="31">
         <v>500</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="31" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:9">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="32" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:9">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="31" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:9">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="G7" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="29" t="s">
+      <c r="G7" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="32" t="s">
         <v>265</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="32" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:9">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="28" t="s">
+      <c r="G8" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="31" t="s">
         <v>273</v>
       </c>
     </row>
@@ -5790,7 +6002,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X85"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6253,7 +6465,7 @@
       <c r="U8" s="12">
         <v>433</v>
       </c>
-      <c r="V8" s="25" t="s">
+      <c r="V8" s="26" t="s">
         <v>15</v>
       </c>
       <c r="W8" s="12" t="s">
@@ -6326,10 +6538,10 @@
       <c r="U9" s="2">
         <v>520</v>
       </c>
-      <c r="V9" s="25" t="s">
+      <c r="V9" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="W9" s="27" t="s">
         <v>311</v>
       </c>
       <c r="X9" s="2" t="s">
@@ -6401,7 +6613,7 @@
       <c r="U10" s="14">
         <v>141</v>
       </c>
-      <c r="V10" s="26" t="s">
+      <c r="V10" s="28" t="s">
         <v>15</v>
       </c>
       <c r="W10" s="14" t="s">
@@ -6586,7 +6798,7 @@
         <v>14</v>
       </c>
       <c r="L13" s="19" t="e">
-        <f t="shared" ref="L13:L16" si="1">IF(I13&gt;0,K13/I13,0)</f>
+        <f t="shared" ref="L13:L17" si="1">IF(I13&gt;0,K13/I13,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M13" s="12" t="s">
@@ -6849,121 +7061,154 @@
         <v>315</v>
       </c>
       <c r="G17" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="23" t="e">
-        <f>IF(I17&gt;0,K17/I17,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4" t="s">
-        <v>14</v>
+      <c r="I17" s="4">
+        <v>888339</v>
+      </c>
+      <c r="J17" s="4">
+        <v>888338</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="23">
+        <f t="shared" si="1"/>
+        <v>1.12569638392551e-6</v>
+      </c>
+      <c r="M17" s="4">
+        <v>330.27</v>
+      </c>
+      <c r="N17" s="4">
+        <v>990</v>
+      </c>
+      <c r="O17" s="24">
+        <v>1138</v>
+      </c>
+      <c r="P17" s="4">
+        <v>1254.1</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T17" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U17" s="4" t="s">
-        <v>14</v>
+        <v>323</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="T17" s="23">
+        <v>0.03</v>
+      </c>
+      <c r="U17" s="4">
+        <v>400</v>
       </c>
       <c r="V17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W17" s="4"/>
+      <c r="W17" s="29" t="s">
+        <v>324</v>
+      </c>
       <c r="X17" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A18" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F18" s="4">
-        <v>50</v>
-      </c>
-      <c r="G18" s="4">
+    <row r="18" customFormat="1" ht="255" customHeight="1" spans="1:24">
+      <c r="A18" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G18" s="2">
         <v>10</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
+      <c r="H18" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18" s="20" t="e">
+        <f>IF(I18&gt;0,K18/I18,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T18" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A19" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>88</v>
+        <v>327</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F19" s="2">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G19" s="2">
         <v>10</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>14</v>
@@ -6973,7 +7218,7 @@
         <v>14</v>
       </c>
       <c r="L19" s="20" t="e">
-        <f t="shared" ref="L19:L22" si="2">IF(I19&gt;0,K19/I19,0)</f>
+        <f>IF(I19&gt;0,K19/I19,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M19" s="2" t="s">
@@ -7011,25 +7256,25 @@
     </row>
     <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A20" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>88</v>
+        <v>327</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="F20" s="4">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G20" s="4">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>142</v>
@@ -7042,2543 +7287,2541 @@
         <v>14</v>
       </c>
       <c r="L20" s="23" t="e">
+        <f>IF(I20&gt;0,K20/I20,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T20" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A21" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="4">
+        <v>50</v>
+      </c>
+      <c r="G21" s="4">
+        <v>10</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+    </row>
+    <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A22" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="2">
+        <v>100</v>
+      </c>
+      <c r="G22" s="2">
+        <v>10</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L22" s="20" t="e">
+        <f t="shared" ref="L22:L25" si="2">IF(I22&gt;0,K22/I22,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T22" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A23" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23" s="4">
+        <v>300</v>
+      </c>
+      <c r="G23" s="4">
+        <v>10</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T20" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V20" s="4" t="s">
+      <c r="M23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T23" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A21" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="W23" s="4"/>
+      <c r="X23" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A24" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F24" s="2">
         <v>500</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G24" s="2">
         <v>10</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" s="20" t="e">
+      <c r="I24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24" s="20" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T21" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V21" s="2" t="s">
+      <c r="M24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T24" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A22" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="W24" s="2"/>
+      <c r="X24" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A25" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="D25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F25" s="4">
         <v>500</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G25" s="4">
         <v>500</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L22" s="23" t="e">
+      <c r="I25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" s="23" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T22" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V22" s="4" t="s">
+      <c r="M25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T25" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A23" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
+      <c r="W25" s="4"/>
+      <c r="X25" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A26" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F26" s="4">
         <v>50</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G26" s="4">
         <v>10</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H26" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="4" t="s">
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-    </row>
-    <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A24" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+    </row>
+    <row r="27" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A27" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="D27" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F27" s="12">
         <v>100</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G27" s="12">
         <v>10</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H27" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="20" t="e">
-        <f t="shared" ref="L24:L27" si="3">IF(I24&gt;0,K24/I24,0)</f>
+      <c r="I27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="19" t="e">
+        <f t="shared" ref="L27:L30" si="3">IF(I27&gt;0,K27/I27,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T24" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V24" s="2" t="s">
+      <c r="M27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T27" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V27" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A25" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="W27" s="12"/>
+      <c r="X27" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A28" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="D28" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F28" s="12">
         <v>300</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G28" s="12">
         <v>10</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H28" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" s="23" t="e">
+      <c r="I28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="19" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T25" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" s="4" t="s">
+      <c r="M28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T28" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A26" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="W28" s="12"/>
+      <c r="X28" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A29" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="D29" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F29" s="12">
         <v>500</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G29" s="12">
         <v>10</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H29" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L26" s="20" t="e">
+      <c r="I29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="19" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T26" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V26" s="2" t="s">
+      <c r="M29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T29" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V29" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A27" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="W29" s="12"/>
+      <c r="X29" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A30" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E27" s="4" t="s">
+      <c r="D30" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F30" s="12">
         <v>500</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G30" s="12">
         <v>500</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H30" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="23" t="e">
+      <c r="I30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30" s="19" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T27" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V27" s="4" t="s">
+      <c r="M30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T30" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V30" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A28" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4" t="s">
+      <c r="W30" s="12"/>
+      <c r="X30" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E28" s="4" t="s">
+      <c r="D31" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F31" s="4">
         <v>50</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G31" s="4">
         <v>10</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H31" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="4" t="s">
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-    </row>
-    <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A29" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+    </row>
+    <row r="32" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A32" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="E32" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F32" s="12">
         <v>100</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G32" s="12">
         <v>10</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H32" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="20" t="e">
-        <f t="shared" ref="L29:L32" si="4">IF(I29&gt;0,K29/I29,0)</f>
+      <c r="I32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="25"/>
+      <c r="K32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32" s="19" t="e">
+        <f t="shared" ref="L32:L35" si="4">IF(I32&gt;0,K32/I32,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T29" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V29" s="2" t="s">
+      <c r="M32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T32" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V32" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A30" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="W32" s="12"/>
+      <c r="X32" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A33" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F33" s="12">
         <v>300</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G33" s="12">
         <v>10</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H33" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L30" s="23" t="e">
+      <c r="I33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="25"/>
+      <c r="K33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="19" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T30" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V30" s="4" t="s">
+      <c r="M33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T33" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V33" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A31" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="W33" s="12"/>
+      <c r="X33" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A34" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F34" s="12">
         <v>500</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G34" s="12">
         <v>10</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H34" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="20" t="e">
+      <c r="I34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="25"/>
+      <c r="K34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34" s="19" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T31" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V31" s="2" t="s">
+      <c r="M34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O34" s="12"/>
+      <c r="P34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T34" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V34" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A32" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="W34" s="12"/>
+      <c r="X34" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A35" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="E35" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F35" s="12">
         <v>500</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G35" s="12">
         <v>500</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H35" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L32" s="23" t="e">
+      <c r="I35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="25"/>
+      <c r="K35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="19" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T32" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V32" s="4" t="s">
+      <c r="M35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T35" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V35" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A33" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4" t="s">
+      <c r="W35" s="12"/>
+      <c r="X35" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A36" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="D36" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F36" s="4">
         <v>50</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G36" s="4">
         <v>10</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H36" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="4" t="s">
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-    </row>
-    <row r="34" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A34" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="12" t="s">
+      <c r="W36" s="4"/>
+      <c r="X36" s="4"/>
+    </row>
+    <row r="37" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A37" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G37" s="12">
         <v>10</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H37" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L34" s="19" t="e">
-        <f t="shared" ref="L34:L37" si="5">IF(I34&gt;0,K34/I34,0)</f>
+      <c r="I37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="25"/>
+      <c r="K37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" s="19" t="e">
+        <f t="shared" ref="L37:L40" si="5">IF(I37&gt;0,K37/I37,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T34" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V34" s="12" t="s">
+      <c r="M37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O37" s="12"/>
+      <c r="P37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T37" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V37" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W34" s="12"/>
-      <c r="X34" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A35" s="12" t="s">
+      <c r="W37" s="12"/>
+      <c r="X37" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A38" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" s="12" t="s">
+      <c r="D38" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="E38" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F38" s="12">
         <v>300</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G38" s="12">
         <v>10</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H38" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L35" s="19" t="e">
+      <c r="I38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" s="25"/>
+      <c r="K38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L38" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T35" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V35" s="12" t="s">
+      <c r="M38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O38" s="12"/>
+      <c r="P38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T38" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V38" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W35" s="12"/>
-      <c r="X35" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A36" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" s="12" t="s">
+      <c r="W38" s="12"/>
+      <c r="X38" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A39" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="E39" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F39" s="12">
         <v>500</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G39" s="12">
         <v>10</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H39" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L36" s="19" t="e">
+      <c r="I39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="25"/>
+      <c r="K39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O36" s="12"/>
-      <c r="P36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T36" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V36" s="12" t="s">
+      <c r="M39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O39" s="12"/>
+      <c r="P39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T39" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V39" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W36" s="12"/>
-      <c r="X36" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A37" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E37" s="12" t="s">
+      <c r="W39" s="12"/>
+      <c r="X39" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A40" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="E40" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F40" s="12">
         <v>500</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G40" s="12">
         <v>500</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H40" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L37" s="19" t="e">
+      <c r="I40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="25"/>
+      <c r="K40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O37" s="12"/>
-      <c r="P37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T37" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V37" s="12" t="s">
+      <c r="M40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T40" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V40" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A38" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4" t="s">
+      <c r="W40" s="12"/>
+      <c r="X40" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A41" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F41" s="4">
         <v>50</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G41" s="4">
         <v>10</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="4" t="s">
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="16"/>
+      <c r="U41" s="15"/>
+      <c r="V41" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-    </row>
-    <row r="39" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A39" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="E39" s="12" t="s">
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+    </row>
+    <row r="42" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A42" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F42" s="12">
         <v>100</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G42" s="12">
         <v>10</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H42" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" s="24"/>
-      <c r="K39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L39" s="19" t="e">
-        <f t="shared" ref="L39:L42" si="6">IF(I39&gt;0,K39/I39,0)</f>
+      <c r="I42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="25"/>
+      <c r="K42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42" s="19" t="e">
+        <f t="shared" ref="L42:L45" si="6">IF(I42&gt;0,K42/I42,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O39" s="12"/>
-      <c r="P39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T39" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V39" s="12" t="s">
+      <c r="M42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O42" s="12"/>
+      <c r="P42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T42" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V42" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A40" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="E40" s="12" t="s">
+      <c r="W42" s="12"/>
+      <c r="X42" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A43" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E43" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F43" s="12">
         <v>300</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G43" s="12">
         <v>10</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H43" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" s="24"/>
-      <c r="K40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L40" s="19" t="e">
+      <c r="I43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="25"/>
+      <c r="K43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="19" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O40" s="12"/>
-      <c r="P40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T40" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V40" s="12" t="s">
+      <c r="M43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O43" s="12"/>
+      <c r="P43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T43" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V43" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W40" s="12"/>
-      <c r="X40" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A41" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="E41" s="12" t="s">
+      <c r="W43" s="12"/>
+      <c r="X43" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A44" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F44" s="12">
         <v>500</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G44" s="12">
         <v>10</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H44" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41" s="24"/>
-      <c r="K41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L41" s="19" t="e">
+      <c r="I44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="25"/>
+      <c r="K44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" s="19" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O41" s="12"/>
-      <c r="P41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T41" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V41" s="12" t="s">
+      <c r="M44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O44" s="12"/>
+      <c r="P44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T44" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V44" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W41" s="12"/>
-      <c r="X41" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A42" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="E42" s="12" t="s">
+      <c r="W44" s="12"/>
+      <c r="X44" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A45" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F45" s="12">
         <v>500</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G45" s="12">
         <v>500</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H45" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42" s="24"/>
-      <c r="K42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L42" s="19" t="e">
+      <c r="I45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J45" s="25"/>
+      <c r="K45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L45" s="19" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O42" s="12"/>
-      <c r="P42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T42" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V42" s="12" t="s">
+      <c r="M45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O45" s="12"/>
+      <c r="P45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T45" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V45" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W42" s="12"/>
-      <c r="X42" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A43" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4" t="s">
+      <c r="W45" s="12"/>
+      <c r="X45" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A46" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F46" s="4">
         <v>50</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G46" s="4">
         <v>10</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H46" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="15"/>
-      <c r="R43" s="15"/>
-      <c r="S43" s="15"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="15"/>
-      <c r="V43" s="4" t="s">
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="15"/>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15"/>
+      <c r="R46" s="15"/>
+      <c r="S46" s="15"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="15"/>
+      <c r="V46" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
-    </row>
-    <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A44" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="E44" s="12" t="s">
+      <c r="W46" s="4"/>
+      <c r="X46" s="4"/>
+    </row>
+    <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A47" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E47" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F47" s="12">
         <v>100</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G47" s="12">
         <v>10</v>
       </c>
-      <c r="H44" s="12" t="s">
+      <c r="H47" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J44" s="24"/>
-      <c r="K44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L44" s="19" t="e">
-        <f t="shared" ref="L44:L47" si="7">IF(I44&gt;0,K44/I44,0)</f>
+      <c r="I47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" s="25"/>
+      <c r="K47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L47" s="19" t="e">
+        <f t="shared" ref="L47:L50" si="7">IF(I47&gt;0,K47/I47,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O44" s="12"/>
-      <c r="P44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T44" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V44" s="12" t="s">
+      <c r="M47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O47" s="12"/>
+      <c r="P47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T47" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U47" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V47" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W44" s="12"/>
-      <c r="X44" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A45" s="12" t="s">
+      <c r="W47" s="12"/>
+      <c r="X47" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A48" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="E45" s="12" t="s">
+      <c r="E48" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F48" s="12">
         <v>300</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G48" s="12">
         <v>10</v>
       </c>
-      <c r="H45" s="12" t="s">
+      <c r="H48" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J45" s="24"/>
-      <c r="K45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L45" s="19" t="e">
+      <c r="I48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" s="25"/>
+      <c r="K48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L48" s="19" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T45" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V45" s="12" t="s">
+      <c r="M48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O48" s="12"/>
+      <c r="P48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T48" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U48" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V48" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A46" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="E46" s="12" t="s">
+      <c r="W48" s="12"/>
+      <c r="X48" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A49" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E49" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F49" s="12">
         <v>500</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G49" s="12">
         <v>10</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H49" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J46" s="24"/>
-      <c r="K46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L46" s="19" t="e">
+      <c r="I49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J49" s="25"/>
+      <c r="K49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L49" s="19" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T46" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U46" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V46" s="12" t="s">
+      <c r="M49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O49" s="12"/>
+      <c r="P49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T49" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V49" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W46" s="12"/>
-      <c r="X46" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A47" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="E47" s="12" t="s">
+      <c r="W49" s="12"/>
+      <c r="X49" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A50" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E50" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F50" s="12">
         <v>500</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G50" s="12">
         <v>500</v>
       </c>
-      <c r="H47" s="12" t="s">
+      <c r="H50" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J47" s="24"/>
-      <c r="K47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L47" s="19" t="e">
+      <c r="I50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" s="25"/>
+      <c r="K50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L50" s="19" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O47" s="12"/>
-      <c r="P47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T47" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V47" s="12" t="s">
+      <c r="M50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O50" s="12"/>
+      <c r="P50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T50" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V50" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W47" s="12"/>
-      <c r="X47" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A48" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4" t="s">
+      <c r="W50" s="12"/>
+      <c r="X50" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A51" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E48" s="4" t="s">
+      <c r="D51" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F51" s="4">
         <v>50</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G51" s="4">
         <v>10</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H51" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15"/>
-      <c r="R48" s="15"/>
-      <c r="S48" s="15"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="15"/>
-      <c r="V48" s="4" t="s">
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
+      <c r="R51" s="15"/>
+      <c r="S51" s="15"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="15"/>
+      <c r="V51" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
-    </row>
-    <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A49" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E49" s="12" t="s">
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+    </row>
+    <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A52" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E52" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F52" s="12">
         <v>100</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G52" s="12">
         <v>10</v>
       </c>
-      <c r="H49" s="12" t="s">
+      <c r="H52" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J49" s="24"/>
-      <c r="K49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L49" s="19" t="e">
-        <f t="shared" ref="L49:L52" si="8">IF(I49&gt;0,K49/I49,0)</f>
+      <c r="I52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" s="19" t="e">
+        <f t="shared" ref="L52:L55" si="8">IF(I52&gt;0,K52/I52,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O49" s="12"/>
-      <c r="P49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T49" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V49" s="12" t="s">
+      <c r="M52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O52" s="12"/>
+      <c r="P52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T52" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U52" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V52" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W49" s="12"/>
-      <c r="X49" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A50" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E50" s="12" t="s">
+      <c r="W52" s="12"/>
+      <c r="X52" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A53" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E53" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F53" s="12">
         <v>300</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G53" s="12">
         <v>10</v>
       </c>
-      <c r="H50" s="12" t="s">
+      <c r="H53" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J50" s="24"/>
-      <c r="K50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L50" s="19" t="e">
+      <c r="I53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" s="19" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O50" s="12"/>
-      <c r="P50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T50" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V50" s="12" t="s">
+      <c r="M53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O53" s="12"/>
+      <c r="P53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T53" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U53" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V53" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W50" s="12"/>
-      <c r="X50" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A51" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E51" s="12" t="s">
+      <c r="W53" s="12"/>
+      <c r="X53" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A54" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E54" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F54" s="12">
         <v>500</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G54" s="12">
         <v>10</v>
       </c>
-      <c r="H51" s="12" t="s">
+      <c r="H54" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J51" s="24"/>
-      <c r="K51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L51" s="19" t="e">
+      <c r="I54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L54" s="19" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O51" s="12"/>
-      <c r="P51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T51" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V51" s="12" t="s">
+      <c r="M54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T54" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V54" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W51" s="12"/>
-      <c r="X51" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A52" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E52" s="12" t="s">
+      <c r="W54" s="12"/>
+      <c r="X54" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A55" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E55" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F55" s="12">
         <v>500</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G55" s="12">
         <v>500</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="H55" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J52" s="24"/>
-      <c r="K52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L52" s="19" t="e">
+      <c r="I55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L55" s="19" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O52" s="12"/>
-      <c r="P52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T52" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V52" s="12" t="s">
+      <c r="M55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O55" s="12"/>
+      <c r="P55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T55" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U55" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V55" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W52" s="12"/>
-      <c r="X52" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A53" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4" t="s">
+      <c r="W55" s="12"/>
+      <c r="X55" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A56" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E53" s="4" t="s">
+      <c r="D56" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F56" s="4">
         <v>50</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G56" s="4">
         <v>10</v>
       </c>
-      <c r="H53" s="4" t="s">
+      <c r="H56" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="15"/>
-      <c r="N53" s="15"/>
-      <c r="O53" s="15"/>
-      <c r="P53" s="15"/>
-      <c r="Q53" s="15"/>
-      <c r="R53" s="15"/>
-      <c r="S53" s="15"/>
-      <c r="T53" s="16"/>
-      <c r="U53" s="15"/>
-      <c r="V53" s="4" t="s">
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
+      <c r="P56" s="15"/>
+      <c r="Q56" s="15"/>
+      <c r="R56" s="15"/>
+      <c r="S56" s="15"/>
+      <c r="T56" s="16"/>
+      <c r="U56" s="15"/>
+      <c r="V56" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-    </row>
-    <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A54" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E54" s="12" t="s">
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+    </row>
+    <row r="57" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A57" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E57" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F54" s="12">
+      <c r="F57" s="12">
         <v>100</v>
       </c>
-      <c r="G54" s="12">
+      <c r="G57" s="12">
         <v>10</v>
       </c>
-      <c r="H54" s="12" t="s">
+      <c r="H57" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J54" s="24"/>
-      <c r="K54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L54" s="19" t="e">
-        <f t="shared" ref="L54:L57" si="9">IF(I54&gt;0,K54/I54,0)</f>
+      <c r="I57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L57" s="19" t="e">
+        <f t="shared" ref="L57:L60" si="9">IF(I57&gt;0,K57/I57,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O54" s="12"/>
-      <c r="P54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T54" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V54" s="12" t="s">
+      <c r="M57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O57" s="12"/>
+      <c r="P57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T57" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U57" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V57" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W54" s="12"/>
-      <c r="X54" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A55" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E55" s="12" t="s">
+      <c r="W57" s="12"/>
+      <c r="X57" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A58" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F58" s="12">
         <v>300</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G58" s="12">
         <v>10</v>
       </c>
-      <c r="H55" s="12" t="s">
+      <c r="H58" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J55" s="24"/>
-      <c r="K55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L55" s="19" t="e">
+      <c r="I58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L58" s="19" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O55" s="12"/>
-      <c r="P55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T55" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V55" s="12" t="s">
+      <c r="M58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O58" s="12"/>
+      <c r="P58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T58" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U58" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V58" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W55" s="12"/>
-      <c r="X55" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A56" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E56" s="12" t="s">
+      <c r="W58" s="12"/>
+      <c r="X58" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A59" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E59" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F59" s="12">
         <v>500</v>
       </c>
-      <c r="G56" s="12">
+      <c r="G59" s="12">
         <v>10</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="H59" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J56" s="24"/>
-      <c r="K56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L56" s="19" t="e">
+      <c r="I59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L59" s="19" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O56" s="12"/>
-      <c r="P56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T56" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V56" s="12" t="s">
+      <c r="M59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O59" s="12"/>
+      <c r="P59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T59" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U59" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V59" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W56" s="12"/>
-      <c r="X56" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A57" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E57" s="12" t="s">
+      <c r="W59" s="12"/>
+      <c r="X59" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A60" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E60" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F60" s="12">
         <v>500</v>
       </c>
-      <c r="G57" s="12">
+      <c r="G60" s="12">
         <v>500</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="H60" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J57" s="24"/>
-      <c r="K57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L57" s="19" t="e">
+      <c r="I60" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L60" s="19" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T57" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V57" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W57" s="12"/>
-      <c r="X57" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A58" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F58" s="4">
-        <v>50</v>
-      </c>
-      <c r="G58" s="4">
-        <v>10</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="15"/>
-      <c r="N58" s="15"/>
-      <c r="O58" s="15"/>
-      <c r="P58" s="15"/>
-      <c r="Q58" s="15"/>
-      <c r="R58" s="15"/>
-      <c r="S58" s="15"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="15"/>
-      <c r="V58" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W58" s="4"/>
-      <c r="X58" s="4"/>
-    </row>
-    <row r="59" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A59" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F59" s="12">
-        <v>100</v>
-      </c>
-      <c r="G59" s="12">
-        <v>10</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L59" s="19" t="e">
-        <f t="shared" ref="L59:L62" si="10">IF(I59&gt;0,K59/I59,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O59" s="12"/>
-      <c r="P59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T59" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V59" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W59" s="12"/>
-      <c r="X59" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A60" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F60" s="12">
-        <v>300</v>
-      </c>
-      <c r="G60" s="12">
-        <v>10</v>
-      </c>
-      <c r="H60" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J60" s="12"/>
-      <c r="K60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L60" s="19" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
       <c r="M60" s="12" t="s">
         <v>14</v>
       </c>
@@ -9612,927 +9855,473 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A61" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F61" s="12">
-        <v>500</v>
-      </c>
-      <c r="G61" s="12">
-        <v>10</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L61" s="19" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O61" s="12"/>
-      <c r="P61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T61" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U61" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V61" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W61" s="12"/>
-      <c r="X61" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A62" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F62" s="12">
-        <v>500</v>
-      </c>
-      <c r="G62" s="12">
-        <v>500</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J62" s="12"/>
-      <c r="K62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L62" s="19" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O62" s="12"/>
-      <c r="P62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T62" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U62" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V62" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W62" s="12"/>
-      <c r="X62" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A63" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F63" s="4">
-        <v>50</v>
-      </c>
-      <c r="G63" s="4">
-        <v>10</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="15"/>
-      <c r="O63" s="15"/>
-      <c r="P63" s="15"/>
-      <c r="Q63" s="15"/>
-      <c r="R63" s="15"/>
-      <c r="S63" s="15"/>
-      <c r="T63" s="16"/>
-      <c r="U63" s="15"/>
-      <c r="V63" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
-    </row>
-    <row r="64" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A64" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F64" s="12">
-        <v>100</v>
-      </c>
-      <c r="G64" s="12">
-        <v>10</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L64" s="19" t="e">
-        <f t="shared" ref="L64:L67" si="11">IF(I64&gt;0,K64/I64,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O64" s="12"/>
-      <c r="P64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T64" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V64" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W64" s="12"/>
-      <c r="X64" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A65" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F65" s="12">
-        <v>300</v>
-      </c>
-      <c r="G65" s="12">
-        <v>10</v>
-      </c>
-      <c r="H65" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L65" s="19" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O65" s="12"/>
-      <c r="P65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T65" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U65" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V65" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W65" s="12"/>
-      <c r="X65" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A66" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F66" s="12">
-        <v>500</v>
-      </c>
-      <c r="G66" s="12">
-        <v>10</v>
-      </c>
-      <c r="H66" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J66" s="12"/>
-      <c r="K66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L66" s="19" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O66" s="12"/>
-      <c r="P66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T66" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V66" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W66" s="12"/>
-      <c r="X66" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A67" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F67" s="12">
-        <v>500</v>
-      </c>
-      <c r="G67" s="12">
-        <v>500</v>
-      </c>
-      <c r="H67" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L67" s="19" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O67" s="12"/>
-      <c r="P67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T67" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V67" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W67" s="12"/>
-      <c r="X67" s="12" t="s">
-        <v>14</v>
-      </c>
+    <row r="61" ht="24" customHeight="1" spans="1:24">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="20"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
+      <c r="T61" s="20"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="2"/>
+      <c r="W61" s="2"/>
+      <c r="X61" s="2"/>
+    </row>
+    <row r="62" ht="24" customHeight="1" spans="1:24">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="23"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="23"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+    </row>
+    <row r="63" ht="24" customHeight="1" spans="1:24">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="2"/>
+      <c r="X63" s="2"/>
+    </row>
+    <row r="64" ht="24" customHeight="1" spans="1:24">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="23"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="23"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+    </row>
+    <row r="65" ht="24" customHeight="1" spans="1:24">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2"/>
+    </row>
+    <row r="66" ht="24" customHeight="1" spans="1:24">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="23"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="23"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+    </row>
+    <row r="67" ht="24" customHeight="1" spans="1:24">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="20"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
+      <c r="T67" s="20"/>
+      <c r="U67" s="2"/>
+      <c r="V67" s="2"/>
+      <c r="W67" s="2"/>
+      <c r="X67" s="2"/>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:24">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="20"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
-      <c r="T68" s="20"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="23"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:24">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="23"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="20"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
+      <c r="T69" s="20"/>
+      <c r="U69" s="2"/>
+      <c r="V69" s="2"/>
+      <c r="W69" s="2"/>
+      <c r="X69" s="2"/>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:24">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" s="20"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="2"/>
-      <c r="T70" s="20"/>
-      <c r="U70" s="2"/>
-      <c r="V70" s="2"/>
-      <c r="W70" s="2"/>
-      <c r="X70" s="2"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="23"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="23"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:24">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="23"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="23"/>
-      <c r="U71" s="4"/>
-      <c r="V71" s="4"/>
-      <c r="W71" s="4"/>
-      <c r="X71" s="4"/>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="20"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="20"/>
+      <c r="U71" s="2"/>
+      <c r="V71" s="2"/>
+      <c r="W71" s="2"/>
+      <c r="X71" s="2"/>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:24">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="20"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
-      <c r="T72" s="20"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="2"/>
-      <c r="W72" s="2"/>
-      <c r="X72" s="2"/>
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="23"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="23"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:24">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="23"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="23"/>
-      <c r="U73" s="4"/>
-      <c r="V73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73" s="4"/>
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="20"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="2"/>
+      <c r="T73" s="20"/>
+      <c r="U73" s="2"/>
+      <c r="V73" s="2"/>
+      <c r="W73" s="2"/>
+      <c r="X73" s="2"/>
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:24">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="20"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="2"/>
-      <c r="T74" s="20"/>
-      <c r="U74" s="2"/>
-      <c r="V74" s="2"/>
-      <c r="W74" s="2"/>
-      <c r="X74" s="2"/>
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="23"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+      <c r="T74" s="23"/>
+      <c r="U74" s="4"/>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:24">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="23"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="23"/>
-      <c r="U75" s="4"/>
-      <c r="V75" s="4"/>
-      <c r="W75" s="4"/>
-      <c r="X75" s="4"/>
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="20"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="2"/>
+      <c r="T75" s="20"/>
+      <c r="U75" s="2"/>
+      <c r="V75" s="2"/>
+      <c r="W75" s="2"/>
+      <c r="X75" s="2"/>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:24">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="20"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
-      <c r="T76" s="20"/>
-      <c r="U76" s="2"/>
-      <c r="V76" s="2"/>
-      <c r="W76" s="2"/>
-      <c r="X76" s="2"/>
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="23"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="23"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:24">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="23"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="23"/>
-      <c r="U77" s="4"/>
-      <c r="V77" s="4"/>
-      <c r="W77" s="4"/>
-      <c r="X77" s="4"/>
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="20"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="2"/>
+      <c r="T77" s="20"/>
+      <c r="U77" s="2"/>
+      <c r="V77" s="2"/>
+      <c r="W77" s="2"/>
+      <c r="X77" s="2"/>
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:24">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="20"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="20"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
-      <c r="X78" s="2"/>
-    </row>
-    <row r="79" ht="24" customHeight="1" spans="1:24">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="23"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="23"/>
-      <c r="U79" s="4"/>
-      <c r="V79" s="4"/>
-      <c r="W79" s="4"/>
-      <c r="X79" s="4"/>
-    </row>
-    <row r="80" ht="24" customHeight="1" spans="1:24">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="20"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
-      <c r="T80" s="20"/>
-      <c r="U80" s="2"/>
-      <c r="V80" s="2"/>
-      <c r="W80" s="2"/>
-      <c r="X80" s="2"/>
-    </row>
-    <row r="81" ht="24" customHeight="1" spans="1:24">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="23"/>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
-      <c r="O81" s="4"/>
-      <c r="P81" s="4"/>
-      <c r="Q81" s="4"/>
-      <c r="R81" s="4"/>
-      <c r="S81" s="4"/>
-      <c r="T81" s="23"/>
-      <c r="U81" s="4"/>
-      <c r="V81" s="4"/>
-      <c r="W81" s="4"/>
-      <c r="X81" s="4"/>
-    </row>
-    <row r="82" ht="24" customHeight="1" spans="1:24">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="20"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" s="2"/>
-      <c r="Q82" s="2"/>
-      <c r="R82" s="2"/>
-      <c r="S82" s="2"/>
-      <c r="T82" s="20"/>
-      <c r="U82" s="2"/>
-      <c r="V82" s="2"/>
-      <c r="W82" s="2"/>
-      <c r="X82" s="2"/>
-    </row>
-    <row r="83" ht="24" customHeight="1" spans="1:24">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="23"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
-      <c r="Q83" s="4"/>
-      <c r="R83" s="4"/>
-      <c r="S83" s="4"/>
-      <c r="T83" s="23"/>
-      <c r="U83" s="4"/>
-      <c r="V83" s="4"/>
-      <c r="W83" s="4"/>
-      <c r="X83" s="4"/>
-    </row>
-    <row r="84" ht="24" customHeight="1" spans="1:24">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="20"/>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
-      <c r="Q84" s="2"/>
-      <c r="R84" s="2"/>
-      <c r="S84" s="2"/>
-      <c r="T84" s="20"/>
-      <c r="U84" s="2"/>
-      <c r="V84" s="2"/>
-      <c r="W84" s="2"/>
-      <c r="X84" s="2"/>
-    </row>
-    <row r="85" ht="24" customHeight="1" spans="1:24">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="23"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="4"/>
-      <c r="Q85" s="4"/>
-      <c r="R85" s="4"/>
-      <c r="S85" s="4"/>
-      <c r="T85" s="23"/>
-      <c r="U85" s="4"/>
-      <c r="V85" s="4"/>
-      <c r="W85" s="4"/>
-      <c r="X85" s="4"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="23"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="23"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10614,151 +10403,136 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
-    <cfRule type="cellIs" dxfId="0" priority="67" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="64" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="cellIs" dxfId="1" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="65" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18">
-    <cfRule type="cellIs" dxfId="1" priority="69" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="66" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L23">
-    <cfRule type="cellIs" dxfId="0" priority="61" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N23:O23">
-    <cfRule type="cellIs" dxfId="1" priority="62" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T23">
-    <cfRule type="cellIs" dxfId="1" priority="63" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L28">
+  <conditionalFormatting sqref="L21">
     <cfRule type="cellIs" dxfId="0" priority="55" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N28:O28">
+  <conditionalFormatting sqref="N21:O21">
     <cfRule type="cellIs" dxfId="1" priority="56" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T28">
+  <conditionalFormatting sqref="T21">
     <cfRule type="cellIs" dxfId="1" priority="57" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L33">
+  <conditionalFormatting sqref="L26">
     <cfRule type="cellIs" dxfId="0" priority="49" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N33:O33">
+  <conditionalFormatting sqref="N26:O26">
     <cfRule type="cellIs" dxfId="1" priority="50" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T33">
+  <conditionalFormatting sqref="T26">
     <cfRule type="cellIs" dxfId="1" priority="51" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L38">
+  <conditionalFormatting sqref="L31">
     <cfRule type="cellIs" dxfId="0" priority="43" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N38:O38">
+  <conditionalFormatting sqref="N31:O31">
     <cfRule type="cellIs" dxfId="1" priority="44" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T38">
+  <conditionalFormatting sqref="T31">
     <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L43">
+  <conditionalFormatting sqref="L36">
     <cfRule type="cellIs" dxfId="0" priority="37" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N43:O43">
+  <conditionalFormatting sqref="N36:O36">
     <cfRule type="cellIs" dxfId="1" priority="38" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T43">
+  <conditionalFormatting sqref="T36">
     <cfRule type="cellIs" dxfId="1" priority="39" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L48">
+  <conditionalFormatting sqref="L41">
     <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N48:O48">
+  <conditionalFormatting sqref="N41:O41">
     <cfRule type="cellIs" dxfId="1" priority="32" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T48">
+  <conditionalFormatting sqref="T41">
     <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L53">
+  <conditionalFormatting sqref="L46">
     <cfRule type="cellIs" dxfId="0" priority="25" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N53:O53">
+  <conditionalFormatting sqref="N46:O46">
     <cfRule type="cellIs" dxfId="1" priority="26" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T53">
+  <conditionalFormatting sqref="T46">
     <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L58">
+  <conditionalFormatting sqref="L51">
     <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N58:O58">
+  <conditionalFormatting sqref="N51:O51">
     <cfRule type="cellIs" dxfId="1" priority="20" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T58">
+  <conditionalFormatting sqref="T51">
     <cfRule type="cellIs" dxfId="1" priority="21" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L63">
+  <conditionalFormatting sqref="L56">
     <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N63:O63">
+  <conditionalFormatting sqref="N56:O56">
     <cfRule type="cellIs" dxfId="1" priority="14" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T63">
+  <conditionalFormatting sqref="T56">
     <cfRule type="cellIs" dxfId="1" priority="15" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -10768,52 +10542,47 @@
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19:L22">
-    <cfRule type="cellIs" dxfId="0" priority="64" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L24:L27">
+  <conditionalFormatting sqref="L19:L20">
     <cfRule type="cellIs" dxfId="0" priority="58" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L29:L32">
+  <conditionalFormatting sqref="L22:L25">
     <cfRule type="cellIs" dxfId="0" priority="52" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L34:L37">
+  <conditionalFormatting sqref="L27:L30">
     <cfRule type="cellIs" dxfId="0" priority="46" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L39:L42">
+  <conditionalFormatting sqref="L32:L35">
     <cfRule type="cellIs" dxfId="0" priority="40" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L44:L47">
+  <conditionalFormatting sqref="L37:L40">
     <cfRule type="cellIs" dxfId="0" priority="34" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L49:L52">
+  <conditionalFormatting sqref="L42:L45">
     <cfRule type="cellIs" dxfId="0" priority="28" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L54:L57">
+  <conditionalFormatting sqref="L47:L50">
     <cfRule type="cellIs" dxfId="0" priority="22" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L59:L62">
+  <conditionalFormatting sqref="L52:L55">
     <cfRule type="cellIs" dxfId="0" priority="16" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L64:L67">
+  <conditionalFormatting sqref="L57:L60">
     <cfRule type="cellIs" dxfId="0" priority="10" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
@@ -10823,67 +10592,62 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T19:T22">
-    <cfRule type="cellIs" dxfId="1" priority="66" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T24:T27">
+  <conditionalFormatting sqref="T19:T20">
     <cfRule type="cellIs" dxfId="1" priority="60" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T29:T32">
+  <conditionalFormatting sqref="T22:T25">
     <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T34:T37">
+  <conditionalFormatting sqref="T27:T30">
     <cfRule type="cellIs" dxfId="1" priority="48" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T39:T42">
+  <conditionalFormatting sqref="T32:T35">
     <cfRule type="cellIs" dxfId="1" priority="42" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T44:T47">
+  <conditionalFormatting sqref="T37:T40">
     <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T49:T52">
+  <conditionalFormatting sqref="T42:T45">
     <cfRule type="cellIs" dxfId="1" priority="30" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T54:T57">
+  <conditionalFormatting sqref="T47:T50">
     <cfRule type="cellIs" dxfId="1" priority="24" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T59:T62">
+  <conditionalFormatting sqref="T52:T55">
     <cfRule type="cellIs" dxfId="1" priority="18" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T64:T67">
+  <conditionalFormatting sqref="T57:T60">
     <cfRule type="cellIs" dxfId="1" priority="12" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L8 L68:L85">
+  <conditionalFormatting sqref="L4:L8 L61:L78">
     <cfRule type="cellIs" dxfId="0" priority="97" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O8 N68:O85">
+  <conditionalFormatting sqref="N4:O8 N61:O78">
     <cfRule type="cellIs" dxfId="1" priority="98" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T4:T8 T68:T85">
+  <conditionalFormatting sqref="T4:T8 T61:T78">
     <cfRule type="cellIs" dxfId="1" priority="99" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -10893,58 +10657,53 @@
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N19:O22">
-    <cfRule type="cellIs" dxfId="1" priority="65" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N24:O27">
+  <conditionalFormatting sqref="N19:O20">
     <cfRule type="cellIs" dxfId="1" priority="59" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N29:O32">
+  <conditionalFormatting sqref="N22:O25">
     <cfRule type="cellIs" dxfId="1" priority="53" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N34:O37">
+  <conditionalFormatting sqref="N27:O30">
     <cfRule type="cellIs" dxfId="1" priority="47" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N39:O42">
+  <conditionalFormatting sqref="N32:O35">
     <cfRule type="cellIs" dxfId="1" priority="41" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N44:O47">
+  <conditionalFormatting sqref="N37:O40">
     <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N49:O52">
+  <conditionalFormatting sqref="N42:O45">
     <cfRule type="cellIs" dxfId="1" priority="29" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N54:O57">
+  <conditionalFormatting sqref="N47:O50">
     <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N59:O62">
+  <conditionalFormatting sqref="N52:O55">
     <cfRule type="cellIs" dxfId="1" priority="17" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N64:O67">
+  <conditionalFormatting sqref="N57:O60">
     <cfRule type="cellIs" dxfId="1" priority="11" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="V4:V16 V17:V85">
+    <dataValidation type="list" allowBlank="1" sqref="V18 V4:V17 V19:V78">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10974,7 +10733,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -10994,16 +10753,16 @@
         <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>182</v>
@@ -11012,7 +10771,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -11026,19 +10785,19 @@
         <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -11055,22 +10814,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -11087,22 +10846,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11125,16 +10884,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11175,10 +10934,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11194,25 +10953,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11223,22 +10982,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -11247,7 +11006,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11255,22 +11014,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11287,22 +11046,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11311,7 +11070,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11319,22 +11078,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="425">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1050,6 +1050,11 @@
   </si>
   <si>
     <t>R27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.在长达 13 分钟的压力测试中，系统平均每秒处理了 673个请求，不具有报错。
+2.小程序有一点卡顿等情况。
+</t>
   </si>
   <si>
     <t>R31</t>
@@ -4043,6 +4048,258 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>635635</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>280035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1356995</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1080135</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="图片 38"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30426660" y="31725235"/>
+          <a:ext cx="721360" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1788160</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>267970</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2561590</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>966470</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="图片 43"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31579185" y="31713170"/>
+          <a:ext cx="773430" cy="698500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>408940</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1556385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1315085</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2113280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="图片 44"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="30199965" y="33001585"/>
+          <a:ext cx="906145" cy="556895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1494790</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1577975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2343785</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2099310</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="图片 45"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31285815" y="33023175"/>
+          <a:ext cx="848995" cy="521335"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>300355</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2408555</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1350010</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>3045460</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="图片 46"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30091380" y="33853755"/>
+          <a:ext cx="1049655" cy="636905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1471930</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2464435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2168525</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>3054985</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="图片 47"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31262955" y="33909635"/>
+          <a:ext cx="696595" cy="590550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6798,7 +7055,7 @@
         <v>14</v>
       </c>
       <c r="L13" s="19" t="e">
-        <f t="shared" ref="L13:L17" si="1">IF(I13&gt;0,K13/I13,0)</f>
+        <f t="shared" ref="L13:L20" si="1">IF(I13&gt;0,K13/I13,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M13" s="12" t="s">
@@ -7141,53 +7398,59 @@
       <c r="H18" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" s="20" t="e">
-        <f>IF(I18&gt;0,K18/I18,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>14</v>
+      <c r="I18" s="2">
+        <v>524977</v>
+      </c>
+      <c r="J18" s="2">
+        <v>524977</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>559.4</v>
+      </c>
+      <c r="N18" s="2">
+        <v>1900</v>
+      </c>
+      <c r="O18" s="2">
+        <v>673</v>
+      </c>
+      <c r="P18" s="2">
+        <v>628.9</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>1000</v>
+      </c>
+      <c r="R18" s="2">
+        <v>70</v>
       </c>
       <c r="S18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="T18" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>14</v>
+      <c r="T18" s="20">
+        <v>0.11</v>
+      </c>
+      <c r="U18" s="2">
+        <v>528</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W18" s="2"/>
+      <c r="W18" s="2" t="s">
+        <v>326</v>
+      </c>
       <c r="X18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A19" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
@@ -7196,7 +7459,7 @@
         <v>302</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>149</v>
@@ -7218,7 +7481,7 @@
         <v>14</v>
       </c>
       <c r="L19" s="20" t="e">
-        <f>IF(I19&gt;0,K19/I19,0)</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="M19" s="2" t="s">
@@ -7256,7 +7519,7 @@
     </row>
     <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A20" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>14</v>
@@ -7265,7 +7528,7 @@
         <v>321</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>155</v>
@@ -7287,7 +7550,7 @@
         <v>14</v>
       </c>
       <c r="L20" s="23" t="e">
-        <f>IF(I20&gt;0,K20/I20,0)</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="M20" s="4" t="s">
@@ -7325,7 +7588,7 @@
     </row>
     <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A21" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
@@ -7367,7 +7630,7 @@
     </row>
     <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A22" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>14</v>
@@ -7436,7 +7699,7 @@
     </row>
     <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A23" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>14</v>
@@ -7505,7 +7768,7 @@
     </row>
     <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A24" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>14</v>
@@ -7574,7 +7837,7 @@
     </row>
     <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A25" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>14</v>
@@ -7643,7 +7906,7 @@
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A26" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4" t="s">
@@ -7685,7 +7948,7 @@
     </row>
     <row r="27" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A27" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>14</v>
@@ -7754,7 +8017,7 @@
     </row>
     <row r="28" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A28" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>14</v>
@@ -7823,7 +8086,7 @@
     </row>
     <row r="29" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A29" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>14</v>
@@ -7892,7 +8155,7 @@
     </row>
     <row r="30" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A30" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>14</v>
@@ -7961,7 +8224,7 @@
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A31" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4" t="s">
@@ -8003,16 +8266,16 @@
     </row>
     <row r="32" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A32" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>137</v>
@@ -8072,14 +8335,14 @@
     </row>
     <row r="33" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A33" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>143</v>
@@ -8139,16 +8402,16 @@
     </row>
     <row r="34" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A34" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>149</v>
@@ -8208,16 +8471,16 @@
     </row>
     <row r="35" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A35" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>155</v>
@@ -8277,7 +8540,7 @@
     </row>
     <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A36" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
@@ -8319,16 +8582,16 @@
     </row>
     <row r="37" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A37" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>137</v>
@@ -8388,14 +8651,14 @@
     </row>
     <row r="38" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A38" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>143</v>
@@ -8455,16 +8718,16 @@
     </row>
     <row r="39" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A39" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>149</v>
@@ -8524,16 +8787,16 @@
     </row>
     <row r="40" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A40" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>155</v>
@@ -8593,7 +8856,7 @@
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A41" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4" t="s">
@@ -8635,16 +8898,16 @@
     </row>
     <row r="42" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A42" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>137</v>
@@ -8704,14 +8967,14 @@
     </row>
     <row r="43" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A43" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>143</v>
@@ -8771,16 +9034,16 @@
     </row>
     <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A44" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>149</v>
@@ -8840,16 +9103,16 @@
     </row>
     <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A45" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>155</v>
@@ -8909,7 +9172,7 @@
     </row>
     <row r="46" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A46" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4" t="s">
@@ -8951,16 +9214,16 @@
     </row>
     <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A47" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>137</v>
@@ -9020,14 +9283,14 @@
     </row>
     <row r="48" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A48" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>143</v>
@@ -9087,16 +9350,16 @@
     </row>
     <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A49" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>149</v>
@@ -9156,16 +9419,16 @@
     </row>
     <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A50" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>155</v>
@@ -9225,7 +9488,7 @@
     </row>
     <row r="51" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A51" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
@@ -9267,16 +9530,16 @@
     </row>
     <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A52" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>137</v>
@@ -9336,14 +9599,14 @@
     </row>
     <row r="53" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A53" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>143</v>
@@ -9403,16 +9666,16 @@
     </row>
     <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A54" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>149</v>
@@ -9472,16 +9735,16 @@
     </row>
     <row r="55" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A55" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>155</v>
@@ -9541,7 +9804,7 @@
     </row>
     <row r="56" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A56" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4" t="s">
@@ -9583,16 +9846,16 @@
     </row>
     <row r="57" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A57" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>137</v>
@@ -9652,14 +9915,14 @@
     </row>
     <row r="58" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A58" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>143</v>
@@ -9719,16 +9982,16 @@
     </row>
     <row r="59" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A59" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>149</v>
@@ -9788,16 +10051,16 @@
     </row>
     <row r="60" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A60" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>155</v>
@@ -10703,7 +10966,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="V18 V4:V17 V19:V78">
+    <dataValidation type="list" allowBlank="1" sqref="V4:V78">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10733,7 +10996,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -10753,16 +11016,16 @@
         <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>182</v>
@@ -10771,7 +11034,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -10785,19 +11048,19 @@
         <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -10814,22 +11077,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -10846,22 +11109,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -10884,16 +11147,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -10934,10 +11197,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -10953,25 +11216,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -10982,22 +11245,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -11006,7 +11269,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11014,22 +11277,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11046,22 +11309,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11070,7 +11333,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11078,22 +11341,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="01_业务总览" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="425">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -7448,7 +7448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="24" customHeight="1" spans="1:24">
+    <row r="19" customFormat="1" ht="118" customHeight="1" spans="1:24">
       <c r="A19" s="4" t="s">
         <v>327</v>
       </c>
@@ -7462,16 +7462,16 @@
         <v>328</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F19" s="2">
-        <v>500</v>
+        <v>303</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>315</v>
       </c>
       <c r="G19" s="2">
         <v>10</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>148</v>
+        <v>316</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="01_业务总览" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="421">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1063,19 +1063,10 @@
     <t>赏柜商品</t>
   </si>
   <si>
-    <t>R32</t>
-  </si>
-  <si>
-    <t>W09</t>
-  </si>
-  <si>
-    <t>R33</t>
-  </si>
-  <si>
-    <t>R34</t>
-  </si>
-  <si>
-    <t>R35</t>
+    <t xml:space="preserve">1.在长达 13 分钟的压力测试中，系统平均每秒处理了 645个请求，不具有报错。
+2.小程序有一点卡顿等情况。
+3.接口有明显的性能拐点，users数增加时，rps有明显降低
+</t>
   </si>
   <si>
     <t>R36</t>
@@ -4300,6 +4291,216 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>278765</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>109855</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1178560</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>676275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="图片 48"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30069790" y="34793555"/>
+          <a:ext cx="899795" cy="566420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1409065</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>100965</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2249170</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>680720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="图片 49"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31200090" y="34784665"/>
+          <a:ext cx="840105" cy="579755"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>111125</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>762000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1062355</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1457325</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="图片 50"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="29902150" y="35445700"/>
+          <a:ext cx="951230" cy="695325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1261745</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>997585</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2437765</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1685925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="图片 51"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31052770" y="35681285"/>
+          <a:ext cx="1176020" cy="688340"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>401320</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2038350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1584960</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2541905</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="图片 52"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30192345" y="36722050"/>
+          <a:ext cx="1183640" cy="503555"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6259,7 +6460,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X78"/>
+  <dimension ref="A1:X73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7429,8 +7630,8 @@
       <c r="R18" s="2">
         <v>70</v>
       </c>
-      <c r="S18" s="2" t="s">
-        <v>14</v>
+      <c r="S18" s="2">
+        <v>1.8</v>
       </c>
       <c r="T18" s="20">
         <v>0.11</v>
@@ -7448,7 +7649,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="118" customHeight="1" spans="1:24">
+    <row r="19" customFormat="1" ht="242" customHeight="1" spans="1:24">
       <c r="A19" s="4" t="s">
         <v>327</v>
       </c>
@@ -7473,38 +7674,42 @@
       <c r="H19" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="20" t="e">
+      <c r="I19" s="2">
+        <v>503840</v>
+      </c>
+      <c r="J19" s="2">
+        <v>503840</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="20">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <v>584.13</v>
+      </c>
+      <c r="N19" s="2">
+        <v>2000</v>
+      </c>
+      <c r="O19" s="2">
+        <v>645</v>
+      </c>
+      <c r="P19" s="2">
+        <v>419.4</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>440</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T19" s="20" t="s">
-        <v>14</v>
+      <c r="S19" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="T19" s="20">
+        <v>0.0492</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>14</v>
@@ -7512,26 +7717,28 @@
       <c r="V19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W19" s="2"/>
+      <c r="W19" s="2" t="s">
+        <v>329</v>
+      </c>
       <c r="X19" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A20" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>155</v>
+        <v>95</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="F20" s="4">
         <v>500</v>
@@ -7550,7 +7757,7 @@
         <v>14</v>
       </c>
       <c r="L20" s="23" t="e">
-        <f t="shared" si="1"/>
+        <f>IF(I20&gt;0,K20/I20,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M20" s="4" t="s">
@@ -7588,7 +7795,7 @@
     </row>
     <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A21" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
@@ -7628,292 +7835,292 @@
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A22" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2" t="s">
+    <row r="22" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A22" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="12">
         <v>100</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="12">
         <v>10</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L22" s="20" t="e">
+      <c r="I22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L22" s="19" t="e">
         <f t="shared" ref="L22:L25" si="2">IF(I22&gt;0,K22/I22,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T22" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V22" s="2" t="s">
+      <c r="M22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T22" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V22" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A23" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="W22" s="12"/>
+      <c r="X22" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A23" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="D23" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="12">
         <v>300</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="12">
         <v>10</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L23" s="23" t="e">
+      <c r="I23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="19" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T23" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V23" s="4" t="s">
+      <c r="M23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T23" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A24" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="W23" s="12"/>
+      <c r="X23" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A24" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="D24" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="12">
         <v>500</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="12">
         <v>10</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="20" t="e">
+      <c r="I24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24" s="19" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T24" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V24" s="2" t="s">
+      <c r="M24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V24" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A25" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="W24" s="12"/>
+      <c r="X24" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A25" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="D25" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="12">
         <v>500</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="12">
         <v>500</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" s="23" t="e">
+      <c r="I25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" s="19" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T25" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" s="4" t="s">
+      <c r="M25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T25" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V25" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4" t="s">
+      <c r="W25" s="12"/>
+      <c r="X25" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A26" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4" t="s">
         <v>125</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>292</v>
+        <v>160</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>128</v>
@@ -7948,16 +8155,16 @@
     </row>
     <row r="27" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A27" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>137</v>
@@ -7974,7 +8181,7 @@
       <c r="I27" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="12"/>
+      <c r="J27" s="25"/>
       <c r="K27" s="12" t="s">
         <v>14</v>
       </c>
@@ -8017,16 +8224,14 @@
     </row>
     <row r="28" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A28" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="B28" s="12"/>
       <c r="C28" s="12" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>143</v>
@@ -8043,7 +8248,7 @@
       <c r="I28" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="25"/>
       <c r="K28" s="12" t="s">
         <v>14</v>
       </c>
@@ -8086,16 +8291,16 @@
     </row>
     <row r="29" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A29" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>295</v>
-      </c>
       <c r="D29" s="12" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>149</v>
@@ -8112,7 +8317,7 @@
       <c r="I29" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="25"/>
       <c r="K29" s="12" t="s">
         <v>14</v>
       </c>
@@ -8155,16 +8360,16 @@
     </row>
     <row r="30" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A30" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>339</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>98</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>155</v>
@@ -8181,7 +8386,7 @@
       <c r="I30" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J30" s="12"/>
+      <c r="J30" s="25"/>
       <c r="K30" s="12" t="s">
         <v>14</v>
       </c>
@@ -8224,7 +8429,7 @@
     </row>
     <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A31" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4" t="s">
@@ -8266,16 +8471,16 @@
     </row>
     <row r="32" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A32" s="12" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>137</v>
@@ -8335,14 +8540,14 @@
     </row>
     <row r="33" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A33" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>143</v>
@@ -8402,16 +8607,16 @@
     </row>
     <row r="34" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A34" s="12" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>149</v>
@@ -8471,16 +8676,16 @@
     </row>
     <row r="35" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A35" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>346</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>343</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>155</v>
@@ -8540,7 +8745,7 @@
     </row>
     <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A36" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
@@ -8582,16 +8787,16 @@
     </row>
     <row r="37" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A37" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>137</v>
@@ -8651,14 +8856,14 @@
     </row>
     <row r="38" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A38" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>143</v>
@@ -8718,16 +8923,16 @@
     </row>
     <row r="39" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A39" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>352</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>350</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>149</v>
@@ -8787,16 +8992,16 @@
     </row>
     <row r="40" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A40" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>155</v>
@@ -8856,7 +9061,7 @@
     </row>
     <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A41" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4" t="s">
@@ -8898,16 +9103,16 @@
     </row>
     <row r="42" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A42" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>137</v>
@@ -8967,14 +9172,14 @@
     </row>
     <row r="43" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A43" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>143</v>
@@ -9034,16 +9239,16 @@
     </row>
     <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A44" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>149</v>
@@ -9103,16 +9308,16 @@
     </row>
     <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A45" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>155</v>
@@ -9172,14 +9377,14 @@
     </row>
     <row r="46" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A46" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4" t="s">
         <v>125</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>128</v>
@@ -9214,16 +9419,16 @@
     </row>
     <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A47" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>137</v>
@@ -9240,7 +9445,7 @@
       <c r="I47" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J47" s="25"/>
+      <c r="J47" s="12"/>
       <c r="K47" s="12" t="s">
         <v>14</v>
       </c>
@@ -9283,14 +9488,14 @@
     </row>
     <row r="48" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A48" s="12" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>143</v>
@@ -9307,7 +9512,7 @@
       <c r="I48" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J48" s="25"/>
+      <c r="J48" s="12"/>
       <c r="K48" s="12" t="s">
         <v>14</v>
       </c>
@@ -9350,16 +9555,16 @@
     </row>
     <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A49" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>363</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>356</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>149</v>
@@ -9376,7 +9581,7 @@
       <c r="I49" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J49" s="25"/>
+      <c r="J49" s="12"/>
       <c r="K49" s="12" t="s">
         <v>14</v>
       </c>
@@ -9419,16 +9624,16 @@
     </row>
     <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A50" s="12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>155</v>
@@ -9445,7 +9650,7 @@
       <c r="I50" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J50" s="25"/>
+      <c r="J50" s="12"/>
       <c r="K50" s="12" t="s">
         <v>14</v>
       </c>
@@ -9488,7 +9693,7 @@
     </row>
     <row r="51" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A51" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
@@ -9530,16 +9735,16 @@
     </row>
     <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A52" s="12" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>137</v>
@@ -9599,14 +9804,14 @@
     </row>
     <row r="53" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A53" s="12" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>143</v>
@@ -9666,16 +9871,16 @@
     </row>
     <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A54" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>369</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>367</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>149</v>
@@ -9735,16 +9940,16 @@
     </row>
     <row r="55" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A55" s="12" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>155</v>
@@ -9802,789 +10007,473 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A56" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F56" s="4">
-        <v>50</v>
-      </c>
-      <c r="G56" s="4">
-        <v>10</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="15"/>
-      <c r="S56" s="15"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="15"/>
-      <c r="V56" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
-    </row>
-    <row r="57" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A57" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F57" s="12">
-        <v>100</v>
-      </c>
-      <c r="G57" s="12">
-        <v>10</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L57" s="19" t="e">
-        <f t="shared" ref="L57:L60" si="9">IF(I57&gt;0,K57/I57,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T57" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U57" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V57" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W57" s="12"/>
-      <c r="X57" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A58" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F58" s="12">
-        <v>300</v>
-      </c>
-      <c r="G58" s="12">
-        <v>10</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J58" s="12"/>
-      <c r="K58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L58" s="19" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O58" s="12"/>
-      <c r="P58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T58" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V58" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W58" s="12"/>
-      <c r="X58" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A59" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F59" s="12">
-        <v>500</v>
-      </c>
-      <c r="G59" s="12">
-        <v>10</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L59" s="19" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O59" s="12"/>
-      <c r="P59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T59" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V59" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W59" s="12"/>
-      <c r="X59" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A60" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F60" s="12">
-        <v>500</v>
-      </c>
-      <c r="G60" s="12">
-        <v>500</v>
-      </c>
-      <c r="H60" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J60" s="12"/>
-      <c r="K60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L60" s="19" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O60" s="12"/>
-      <c r="P60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T60" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U60" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V60" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W60" s="12"/>
-      <c r="X60" s="12" t="s">
-        <v>14</v>
-      </c>
+    <row r="56" ht="24" customHeight="1" spans="1:24">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="20"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+    </row>
+    <row r="57" ht="24" customHeight="1" spans="1:24">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="23"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="23"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+    </row>
+    <row r="58" ht="24" customHeight="1" spans="1:24">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+      <c r="T58" s="20"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="2"/>
+      <c r="W58" s="2"/>
+      <c r="X58" s="2"/>
+    </row>
+    <row r="59" ht="24" customHeight="1" spans="1:24">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="23"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="23"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+    </row>
+    <row r="60" ht="24" customHeight="1" spans="1:24">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="20"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2"/>
+      <c r="W60" s="2"/>
+      <c r="X60" s="2"/>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:24">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="L61" s="20"/>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" s="2"/>
-      <c r="Q61" s="2"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="2"/>
-      <c r="T61" s="20"/>
-      <c r="U61" s="2"/>
-      <c r="V61" s="2"/>
-      <c r="W61" s="2"/>
-      <c r="X61" s="2"/>
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="23"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="23"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:24">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="23"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="23"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="4"/>
-      <c r="X62" s="4"/>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="20"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2"/>
+      <c r="W62" s="2"/>
+      <c r="X62" s="2"/>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:24">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-      <c r="T63" s="20"/>
-      <c r="U63" s="2"/>
-      <c r="V63" s="2"/>
-      <c r="W63" s="2"/>
-      <c r="X63" s="2"/>
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="23"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="23"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:24">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="4"/>
-      <c r="V64" s="4"/>
-      <c r="W64" s="4"/>
-      <c r="X64" s="4"/>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="20"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="2"/>
+      <c r="X64" s="2"/>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:24">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="2"/>
-      <c r="T65" s="20"/>
-      <c r="U65" s="2"/>
-      <c r="V65" s="2"/>
-      <c r="W65" s="2"/>
-      <c r="X65" s="2"/>
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="23"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="23"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:24">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="23"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="23"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+      <c r="T66" s="20"/>
+      <c r="U66" s="2"/>
+      <c r="V66" s="2"/>
+      <c r="W66" s="2"/>
+      <c r="X66" s="2"/>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:24">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="20"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
-      <c r="T67" s="20"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="23"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="23"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:24">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="23"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="23"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="20"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="20"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:24">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="20"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="2"/>
-      <c r="T69" s="20"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="2"/>
-      <c r="W69" s="2"/>
-      <c r="X69" s="2"/>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="23"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="23"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:24">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="23"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="23"/>
-      <c r="U70" s="4"/>
-      <c r="V70" s="4"/>
-      <c r="W70" s="4"/>
-      <c r="X70" s="4"/>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="20"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:24">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="20"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
-      <c r="T71" s="20"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="2"/>
-      <c r="W71" s="2"/>
-      <c r="X71" s="2"/>
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="23"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:24">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="23"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="23"/>
-      <c r="U72" s="4"/>
-      <c r="V72" s="4"/>
-      <c r="W72" s="4"/>
-      <c r="X72" s="4"/>
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="20"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="20"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="2"/>
+      <c r="W72" s="2"/>
+      <c r="X72" s="2"/>
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:24">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="20"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="2"/>
-      <c r="T73" s="20"/>
-      <c r="U73" s="2"/>
-      <c r="V73" s="2"/>
-      <c r="W73" s="2"/>
-      <c r="X73" s="2"/>
-    </row>
-    <row r="74" ht="24" customHeight="1" spans="1:24">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="23"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="23"/>
-      <c r="U74" s="4"/>
-      <c r="V74" s="4"/>
-      <c r="W74" s="4"/>
-      <c r="X74" s="4"/>
-    </row>
-    <row r="75" ht="24" customHeight="1" spans="1:24">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="20"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
-      <c r="T75" s="20"/>
-      <c r="U75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
-      <c r="X75" s="2"/>
-    </row>
-    <row r="76" ht="24" customHeight="1" spans="1:24">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="23"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="23"/>
-      <c r="U76" s="4"/>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
-      <c r="X76" s="4"/>
-    </row>
-    <row r="77" ht="24" customHeight="1" spans="1:24">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="20"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
-      <c r="T77" s="20"/>
-      <c r="U77" s="2"/>
-      <c r="V77" s="2"/>
-      <c r="W77" s="2"/>
-      <c r="X77" s="2"/>
-    </row>
-    <row r="78" ht="24" customHeight="1" spans="1:24">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="23"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="23"/>
-      <c r="U78" s="4"/>
-      <c r="V78" s="4"/>
-      <c r="W78" s="4"/>
-      <c r="X78" s="4"/>
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="23"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+      <c r="S73" s="4"/>
+      <c r="T73" s="23"/>
+      <c r="U73" s="4"/>
+      <c r="V73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10680,122 +10569,137 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L19">
+    <cfRule type="cellIs" dxfId="0" priority="58" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19:O19">
+    <cfRule type="cellIs" dxfId="1" priority="59" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T19">
+    <cfRule type="cellIs" dxfId="1" priority="60" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20">
+    <cfRule type="cellIs" dxfId="0" priority="52" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N20:O20">
+    <cfRule type="cellIs" dxfId="1" priority="53" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T20">
+    <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L21">
-    <cfRule type="cellIs" dxfId="0" priority="55" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="49" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21:O21">
-    <cfRule type="cellIs" dxfId="1" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="50" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T21">
-    <cfRule type="cellIs" dxfId="1" priority="57" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="51" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="cellIs" dxfId="0" priority="49" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="43" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26:O26">
-    <cfRule type="cellIs" dxfId="1" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="44" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T26">
-    <cfRule type="cellIs" dxfId="1" priority="51" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L31">
-    <cfRule type="cellIs" dxfId="0" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="37" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="cellIs" dxfId="1" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="38" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31">
-    <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="39" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36">
-    <cfRule type="cellIs" dxfId="0" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N36:O36">
-    <cfRule type="cellIs" dxfId="1" priority="38" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="32" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T36">
-    <cfRule type="cellIs" dxfId="1" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41">
-    <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="25" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N41:O41">
-    <cfRule type="cellIs" dxfId="1" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="26" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T41">
-    <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L46">
-    <cfRule type="cellIs" dxfId="0" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N46:O46">
-    <cfRule type="cellIs" dxfId="1" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="20" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T46">
-    <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="21" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51">
-    <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N51:O51">
-    <cfRule type="cellIs" dxfId="1" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T51">
-    <cfRule type="cellIs" dxfId="1" priority="21" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L56">
-    <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N56:O56">
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T56">
     <cfRule type="cellIs" dxfId="1" priority="15" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -10805,47 +10709,37 @@
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19:L20">
-    <cfRule type="cellIs" dxfId="0" priority="58" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="L22:L25">
-    <cfRule type="cellIs" dxfId="0" priority="52" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="46" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27:L30">
-    <cfRule type="cellIs" dxfId="0" priority="46" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="40" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32:L35">
-    <cfRule type="cellIs" dxfId="0" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="34" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L37:L40">
-    <cfRule type="cellIs" dxfId="0" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="28" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L42:L45">
-    <cfRule type="cellIs" dxfId="0" priority="28" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="22" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47:L50">
-    <cfRule type="cellIs" dxfId="0" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="16" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:L55">
-    <cfRule type="cellIs" dxfId="0" priority="16" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L57:L60">
     <cfRule type="cellIs" dxfId="0" priority="10" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
@@ -10855,62 +10749,52 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T19:T20">
-    <cfRule type="cellIs" dxfId="1" priority="60" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T22:T25">
-    <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="48" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T27:T30">
-    <cfRule type="cellIs" dxfId="1" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="42" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:T35">
-    <cfRule type="cellIs" dxfId="1" priority="42" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T37:T40">
-    <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="30" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T42:T45">
-    <cfRule type="cellIs" dxfId="1" priority="30" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="24" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T47:T50">
-    <cfRule type="cellIs" dxfId="1" priority="24" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T52:T55">
-    <cfRule type="cellIs" dxfId="1" priority="18" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T57:T60">
     <cfRule type="cellIs" dxfId="1" priority="12" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L8 L61:L78">
+  <conditionalFormatting sqref="L4:L8 L56:L73">
     <cfRule type="cellIs" dxfId="0" priority="97" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O8 N61:O78">
+  <conditionalFormatting sqref="N4:O8 N56:O73">
     <cfRule type="cellIs" dxfId="1" priority="98" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T4:T8 T61:T78">
+  <conditionalFormatting sqref="T4:T8 T56:T73">
     <cfRule type="cellIs" dxfId="1" priority="99" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -10920,53 +10804,43 @@
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N19:O20">
-    <cfRule type="cellIs" dxfId="1" priority="59" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N22:O25">
-    <cfRule type="cellIs" dxfId="1" priority="53" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="47" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N27:O30">
-    <cfRule type="cellIs" dxfId="1" priority="47" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="41" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O35">
-    <cfRule type="cellIs" dxfId="1" priority="41" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37:O40">
-    <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="29" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N42:O45">
-    <cfRule type="cellIs" dxfId="1" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O50">
-    <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="17" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N52:O55">
-    <cfRule type="cellIs" dxfId="1" priority="17" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N57:O60">
     <cfRule type="cellIs" dxfId="1" priority="11" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="V4:V78">
+    <dataValidation type="list" allowBlank="1" sqref="V4:V19 V20:V73">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10996,7 +10870,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -11016,16 +10890,16 @@
         <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>182</v>
@@ -11034,7 +10908,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -11048,19 +10922,19 @@
         <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -11077,22 +10951,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -11109,22 +10983,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11147,16 +11021,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11197,10 +11071,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11216,25 +11090,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11245,22 +11119,22 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>14</v>
@@ -11269,7 +11143,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11277,22 +11151,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11309,22 +11183,22 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -11333,7 +11207,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11341,22 +11215,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="01_业务总览" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="419">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1001,6 +1001,9 @@
     <t>只读节点最高达14%，读写节点最高达4%</t>
   </si>
   <si>
+    <t>有条件通过</t>
+  </si>
+  <si>
     <t>1.在长达 15 分钟的压力测试中，系统平均每秒处理了 53个请求，不具有报错。
 2.小程序有明显白屏卡顿延迟，但未有大面积接口崩溃情况。</t>
   </si>
@@ -1063,25 +1066,38 @@
     <t>赏柜商品</t>
   </si>
   <si>
-    <t xml:space="preserve">1.在长达 13 分钟的压力测试中，系统平均每秒处理了 645个请求，不具有报错。
+    <r>
+      <t xml:space="preserve">1.在长达 13 分钟的压力测试中，系统平均每秒处理了 645个请求，不具有报错。
 2.小程序有一点卡顿等情况。
-3.接口有明显的性能拐点，users数增加时，rps有明显降低
 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3.接口有明显的性能拐点，users数增加时，rps有明显降低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
   <si>
     <t>R36</t>
   </si>
   <si>
-    <t>W10</t>
-  </si>
-  <si>
-    <t>R37</t>
-  </si>
-  <si>
-    <t>R38</t>
-  </si>
-  <si>
-    <t>R39</t>
+    <t>1.在长达 13 分钟的压力测试中，系统平均每秒处理了 645个请求，不具有报错。
+2.小程序有一点卡顿等情况。
+3.接口无明显的性能拐点，users数增加时，rps趋势平稳</t>
   </si>
   <si>
     <t>R40</t>
@@ -1352,7 +1368,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1534,6 +1550,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -4501,6 +4523,216 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>229235</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>81280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>989330</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>669290</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="图片 53"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30020260" y="37838380"/>
+          <a:ext cx="760095" cy="588010"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1370330</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104140</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2452370</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>807085</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="图片 54"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31161355" y="37861240"/>
+          <a:ext cx="1082040" cy="702945"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>326390</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>977900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1115695</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1605915</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="图片 55"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30117415" y="38735000"/>
+          <a:ext cx="789305" cy="628015"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1736090</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1058545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2618105</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1687830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="图片 56"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31527115" y="38815645"/>
+          <a:ext cx="882015" cy="629285"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>394970</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1942465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1530985</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>18415</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="图片 57"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30185995" y="39699565"/>
+          <a:ext cx="1136015" cy="755650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6460,7 +6692,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X73"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6996,11 +7228,11 @@
       <c r="U9" s="2">
         <v>520</v>
       </c>
-      <c r="V9" s="26" t="s">
-        <v>15</v>
+      <c r="V9" s="11" t="s">
+        <v>311</v>
       </c>
       <c r="W9" s="27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="X9" s="2" t="s">
         <v>14</v>
@@ -7008,7 +7240,7 @@
     </row>
     <row r="10" s="10" customFormat="1" ht="309" customHeight="1" spans="1:24">
       <c r="A10" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>14</v>
@@ -7075,7 +7307,7 @@
         <v>15</v>
       </c>
       <c r="W10" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X10" s="14" t="s">
         <v>14</v>
@@ -7083,7 +7315,7 @@
     </row>
     <row r="11" s="10" customFormat="1" ht="309" customHeight="1" spans="1:24">
       <c r="A11" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>14</v>
@@ -7144,11 +7376,11 @@
         <v>0.04</v>
       </c>
       <c r="U11" s="14"/>
-      <c r="V11" s="14" t="s">
+      <c r="V11" s="28" t="s">
         <v>15</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="X11" s="14" t="s">
         <v>14</v>
@@ -7156,7 +7388,7 @@
     </row>
     <row r="12" s="10" customFormat="1" ht="309" customHeight="1" spans="1:24">
       <c r="A12" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>14</v>
@@ -7171,13 +7403,13 @@
         <v>303</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G12" s="12">
         <v>10</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>14</v>
@@ -7225,7 +7457,7 @@
     </row>
     <row r="13" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A13" s="12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>14</v>
@@ -7256,7 +7488,7 @@
         <v>14</v>
       </c>
       <c r="L13" s="19" t="e">
-        <f t="shared" ref="L13:L20" si="1">IF(I13&gt;0,K13/I13,0)</f>
+        <f t="shared" ref="L13:L21" si="1">IF(I13&gt;0,K13/I13,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M13" s="12" t="s">
@@ -7294,7 +7526,7 @@
     </row>
     <row r="14" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A14" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>14</v>
@@ -7363,7 +7595,7 @@
     </row>
     <row r="15" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A15" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>14</v>
@@ -7432,13 +7664,13 @@
     </row>
     <row r="16" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A16" s="12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>82</v>
@@ -7501,7 +7733,7 @@
     </row>
     <row r="17" customFormat="1" ht="202" customHeight="1" spans="1:24">
       <c r="A17" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
@@ -7516,13 +7748,13 @@
         <v>303</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G17" s="4">
         <v>13</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I17" s="4">
         <v>888339</v>
@@ -7550,7 +7782,7 @@
         <v>1254.1</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="R17" s="4">
         <v>0</v>
@@ -7564,11 +7796,11 @@
       <c r="U17" s="4">
         <v>400</v>
       </c>
-      <c r="V17" s="4" t="s">
-        <v>29</v>
+      <c r="V17" s="26" t="s">
+        <v>15</v>
       </c>
       <c r="W17" s="29" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="X17" s="4" t="s">
         <v>14</v>
@@ -7576,7 +7808,7 @@
     </row>
     <row r="18" customFormat="1" ht="255" customHeight="1" spans="1:24">
       <c r="A18" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>14</v>
@@ -7591,13 +7823,13 @@
         <v>303</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G18" s="2">
         <v>10</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I18" s="2">
         <v>524977</v>
@@ -7639,11 +7871,11 @@
       <c r="U18" s="2">
         <v>528</v>
       </c>
-      <c r="V18" s="2" t="s">
-        <v>29</v>
+      <c r="V18" s="26" t="s">
+        <v>15</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>14</v>
@@ -7651,7 +7883,7 @@
     </row>
     <row r="19" customFormat="1" ht="242" customHeight="1" spans="1:24">
       <c r="A19" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
@@ -7660,19 +7892,19 @@
         <v>302</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>303</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G19" s="2">
         <v>10</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I19" s="2">
         <v>503840</v>
@@ -7715,18 +7947,18 @@
         <v>14</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>29</v>
+        <v>311</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="24" customHeight="1" spans="1:24">
+    <row r="20" customFormat="1" ht="211" customHeight="1" spans="1:24">
       <c r="A20" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>14</v>
@@ -7740,104 +7972,135 @@
       <c r="E20" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F20" s="4">
-        <v>500</v>
-      </c>
-      <c r="G20" s="4">
-        <v>500</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="F20" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G20" s="2">
+        <v>10</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I20" s="4">
+        <v>478232</v>
+      </c>
+      <c r="J20" s="4">
+        <v>478232</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
+        <v>612.69</v>
+      </c>
+      <c r="N20" s="4">
+        <v>2400</v>
+      </c>
+      <c r="O20" s="4">
+        <v>613</v>
+      </c>
+      <c r="P20" s="4">
+        <v>598.2</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>2700</v>
+      </c>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4">
+        <v>2</v>
+      </c>
+      <c r="T20" s="23">
+        <v>0.0747</v>
+      </c>
+      <c r="U20" s="4">
+        <v>608</v>
+      </c>
+      <c r="V20" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A21" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="F21" s="12">
+        <v>200</v>
+      </c>
+      <c r="G21" s="12">
+        <v>10</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L20" s="23" t="e">
-        <f>IF(I20&gt;0,K20/I20,0)</f>
+      <c r="I21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21" s="19" t="e">
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T20" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V20" s="4" t="s">
+      <c r="M21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T21" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A21" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" s="4">
-        <v>50</v>
-      </c>
-      <c r="G21" s="4">
-        <v>10</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A22" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>14</v>
@@ -7849,16 +8112,16 @@
         <v>98</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>137</v>
+        <v>303</v>
       </c>
       <c r="F22" s="12">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G22" s="12">
         <v>10</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>14</v>
@@ -7868,7 +8131,7 @@
         <v>14</v>
       </c>
       <c r="L22" s="19" t="e">
-        <f t="shared" ref="L22:L25" si="2">IF(I22&gt;0,K22/I22,0)</f>
+        <f>IF(I22&gt;0,K22/I22,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M22" s="12" t="s">
@@ -7918,10 +8181,10 @@
         <v>98</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>143</v>
+        <v>303</v>
       </c>
       <c r="F23" s="12">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G23" s="12">
         <v>10</v>
@@ -7937,394 +8200,394 @@
         <v>14</v>
       </c>
       <c r="L23" s="19" t="e">
+        <f>IF(I23&gt;0,K23/I23,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T23" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V23" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A24" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="G24" s="12">
+        <v>10</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24" s="19" t="e">
+        <f>IF(I24&gt;0,K24/I24,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V24" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A25" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="4">
+        <v>50</v>
+      </c>
+      <c r="G25" s="4">
+        <v>10</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="15"/>
+      <c r="T25" s="16"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+    </row>
+    <row r="26" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A26" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="12">
+        <v>100</v>
+      </c>
+      <c r="G26" s="12">
+        <v>10</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="25"/>
+      <c r="K26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26" s="19" t="e">
+        <f t="shared" ref="L26:L29" si="2">IF(I26&gt;0,K26/I26,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T26" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A27" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F27" s="12">
+        <v>300</v>
+      </c>
+      <c r="G27" s="12">
+        <v>10</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="25"/>
+      <c r="K27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="19" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T23" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V23" s="12" t="s">
+      <c r="M27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T27" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V27" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A24" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="12" t="s">
+      <c r="W27" s="12"/>
+      <c r="X27" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A28" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F28" s="12">
         <v>500</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G28" s="12">
         <v>10</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H28" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="19" t="e">
+      <c r="I28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="25"/>
+      <c r="K28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="19" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T24" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V24" s="12" t="s">
+      <c r="M28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T28" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A25" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="12" t="s">
+      <c r="W28" s="12"/>
+      <c r="X28" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A29" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F29" s="12">
         <v>500</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G29" s="12">
         <v>500</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H29" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" s="19" t="e">
+      <c r="I29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="25"/>
+      <c r="K29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="19" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T25" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A26" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F26" s="4">
-        <v>50</v>
-      </c>
-      <c r="G26" s="4">
-        <v>10</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-    </row>
-    <row r="27" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A27" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F27" s="12">
-        <v>100</v>
-      </c>
-      <c r="G27" s="12">
-        <v>10</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="25"/>
-      <c r="K27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="19" t="e">
-        <f t="shared" ref="L27:L30" si="3">IF(I27&gt;0,K27/I27,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T27" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V27" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A28" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F28" s="12">
-        <v>300</v>
-      </c>
-      <c r="G28" s="12">
-        <v>10</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="25"/>
-      <c r="K28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L28" s="19" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T28" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V28" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A29" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F29" s="12">
-        <v>500</v>
-      </c>
-      <c r="G29" s="12">
-        <v>10</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="25"/>
-      <c r="K29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="19" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
       <c r="M29" s="12" t="s">
         <v>14</v>
       </c>
@@ -8358,141 +8621,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A30" s="12" t="s">
+    <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A30" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="4">
+        <v>50</v>
+      </c>
+      <c r="G30" s="4">
+        <v>10</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+    </row>
+    <row r="31" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A31" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F30" s="12">
-        <v>500</v>
-      </c>
-      <c r="G30" s="12">
-        <v>500</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30" s="25"/>
-      <c r="K30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L30" s="19" t="e">
-        <f t="shared" si="3"/>
+      <c r="B31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="12">
+        <v>100</v>
+      </c>
+      <c r="G31" s="12">
+        <v>10</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="25"/>
+      <c r="K31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="19" t="e">
+        <f t="shared" ref="L31:L34" si="3">IF(I31&gt;0,K31/I31,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T30" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V30" s="12" t="s">
+      <c r="M31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T31" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U31" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V31" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A31" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" s="4">
-        <v>50</v>
-      </c>
-      <c r="G31" s="4">
-        <v>10</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="32" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A32" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="B32" s="12"/>
       <c r="C32" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F32" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G32" s="12">
         <v>10</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I32" s="12" t="s">
         <v>14</v>
@@ -8502,7 +8763,7 @@
         <v>14</v>
       </c>
       <c r="L32" s="19" t="e">
-        <f t="shared" ref="L32:L35" si="4">IF(I32&gt;0,K32/I32,0)</f>
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="M32" s="12" t="s">
@@ -8540,26 +8801,28 @@
     </row>
     <row r="33" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A33" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="B33" s="12"/>
+        <v>346</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C33" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F33" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G33" s="12">
         <v>10</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I33" s="12" t="s">
         <v>14</v>
@@ -8569,7 +8832,7 @@
         <v>14</v>
       </c>
       <c r="L33" s="19" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="M33" s="12" t="s">
@@ -8607,28 +8870,28 @@
     </row>
     <row r="34" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A34" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F34" s="12">
         <v>500</v>
       </c>
       <c r="G34" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I34" s="12" t="s">
         <v>14</v>
@@ -8638,7 +8901,7 @@
         <v>14</v>
       </c>
       <c r="L34" s="19" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="M34" s="12" t="s">
@@ -8674,141 +8937,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A35" s="12" t="s">
+    <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A35" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="4">
+        <v>50</v>
+      </c>
+      <c r="G35" s="4">
+        <v>10</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W35" s="4"/>
+      <c r="X35" s="4"/>
+    </row>
+    <row r="36" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A36" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F35" s="12">
-        <v>500</v>
-      </c>
-      <c r="G35" s="12">
-        <v>500</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="25"/>
-      <c r="K35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L35" s="19" t="e">
-        <f t="shared" si="4"/>
+      <c r="B36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="12">
+        <v>100</v>
+      </c>
+      <c r="G36" s="12">
+        <v>10</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="25"/>
+      <c r="K36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="19" t="e">
+        <f t="shared" ref="L36:L39" si="4">IF(I36&gt;0,K36/I36,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T35" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V35" s="12" t="s">
+      <c r="M36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O36" s="12"/>
+      <c r="P36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T36" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V36" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W35" s="12"/>
-      <c r="X35" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A36" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F36" s="4">
-        <v>50</v>
-      </c>
-      <c r="G36" s="4">
-        <v>10</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
+      <c r="W36" s="12"/>
+      <c r="X36" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="37" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A37" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="B37" s="12"/>
       <c r="C37" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F37" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G37" s="12">
         <v>10</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I37" s="12" t="s">
         <v>14</v>
@@ -8818,7 +9079,7 @@
         <v>14</v>
       </c>
       <c r="L37" s="19" t="e">
-        <f t="shared" ref="L37:L40" si="5">IF(I37&gt;0,K37/I37,0)</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="M37" s="12" t="s">
@@ -8856,26 +9117,28 @@
     </row>
     <row r="38" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A38" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="B38" s="12"/>
+        <v>352</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C38" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F38" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G38" s="12">
         <v>10</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I38" s="12" t="s">
         <v>14</v>
@@ -8885,394 +9148,394 @@
         <v>14</v>
       </c>
       <c r="L38" s="19" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O38" s="12"/>
+      <c r="P38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T38" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V38" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A39" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" s="12">
+        <v>500</v>
+      </c>
+      <c r="G39" s="12">
+        <v>500</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="25"/>
+      <c r="K39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39" s="19" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O39" s="12"/>
+      <c r="P39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T39" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U39" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V39" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W39" s="12"/>
+      <c r="X39" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A40" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" s="4">
+        <v>50</v>
+      </c>
+      <c r="G40" s="4">
+        <v>10</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+    </row>
+    <row r="41" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A41" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F41" s="12">
+        <v>100</v>
+      </c>
+      <c r="G41" s="12">
+        <v>10</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="25"/>
+      <c r="K41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="19" t="e">
+        <f t="shared" ref="L41:L44" si="5">IF(I41&gt;0,K41/I41,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O41" s="12"/>
+      <c r="P41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T41" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U41" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V41" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W41" s="12"/>
+      <c r="X41" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A42" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F42" s="12">
+        <v>300</v>
+      </c>
+      <c r="G42" s="12">
+        <v>10</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="25"/>
+      <c r="K42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M38" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N38" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O38" s="12"/>
-      <c r="P38" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q38" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R38" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S38" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T38" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U38" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V38" s="12" t="s">
+      <c r="M42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O42" s="12"/>
+      <c r="P42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T42" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V42" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W38" s="12"/>
-      <c r="X38" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A39" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E39" s="12" t="s">
+      <c r="W42" s="12"/>
+      <c r="X42" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A43" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E43" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F43" s="12">
         <v>500</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G43" s="12">
         <v>10</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H43" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" s="25"/>
-      <c r="K39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L39" s="19" t="e">
+      <c r="I43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="25"/>
+      <c r="K43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O39" s="12"/>
-      <c r="P39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T39" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V39" s="12" t="s">
+      <c r="M43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O43" s="12"/>
+      <c r="P43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T43" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U43" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V43" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A40" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E40" s="12" t="s">
+      <c r="W43" s="12"/>
+      <c r="X43" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A44" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F44" s="12">
         <v>500</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G44" s="12">
         <v>500</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H44" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" s="25"/>
-      <c r="K40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L40" s="19" t="e">
+      <c r="I44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="25"/>
+      <c r="K44" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" s="19" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O40" s="12"/>
-      <c r="P40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T40" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V40" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W40" s="12"/>
-      <c r="X40" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A41" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F41" s="4">
-        <v>50</v>
-      </c>
-      <c r="G41" s="4">
-        <v>10</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="15"/>
-      <c r="R41" s="15"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="16"/>
-      <c r="U41" s="15"/>
-      <c r="V41" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-    </row>
-    <row r="42" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A42" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="12">
-        <v>100</v>
-      </c>
-      <c r="G42" s="12">
-        <v>10</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42" s="25"/>
-      <c r="K42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L42" s="19" t="e">
-        <f t="shared" ref="L42:L45" si="6">IF(I42&gt;0,K42/I42,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O42" s="12"/>
-      <c r="P42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T42" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V42" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W42" s="12"/>
-      <c r="X42" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A43" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F43" s="12">
-        <v>300</v>
-      </c>
-      <c r="G43" s="12">
-        <v>10</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" s="25"/>
-      <c r="K43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L43" s="19" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O43" s="12"/>
-      <c r="P43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T43" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V43" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W43" s="12"/>
-      <c r="X43" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A44" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F44" s="12">
-        <v>500</v>
-      </c>
-      <c r="G44" s="12">
-        <v>10</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J44" s="25"/>
-      <c r="K44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L44" s="19" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
       <c r="M44" s="12" t="s">
         <v>14</v>
       </c>
@@ -9306,141 +9569,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A45" s="12" t="s">
+    <row r="45" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A45" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" s="4">
+        <v>50</v>
+      </c>
+      <c r="G45" s="4">
+        <v>10</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="15"/>
+      <c r="R45" s="15"/>
+      <c r="S45" s="15"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="15"/>
+      <c r="V45" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+    </row>
+    <row r="46" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A46" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F45" s="12">
-        <v>500</v>
-      </c>
-      <c r="G45" s="12">
-        <v>500</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J45" s="25"/>
-      <c r="K45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L45" s="19" t="e">
-        <f t="shared" si="6"/>
+      <c r="B46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="12">
+        <v>100</v>
+      </c>
+      <c r="G46" s="12">
+        <v>10</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L46" s="19" t="e">
+        <f t="shared" ref="L46:L49" si="6">IF(I46&gt;0,K46/I46,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T45" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U45" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V45" s="12" t="s">
+      <c r="M46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T46" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U46" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V46" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A46" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F46" s="4">
-        <v>50</v>
-      </c>
-      <c r="G46" s="4">
-        <v>10</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="15"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="15"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="15"/>
-      <c r="V46" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W46" s="4"/>
-      <c r="X46" s="4"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A47" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="B47" s="12"/>
       <c r="C47" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F47" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G47" s="12">
         <v>10</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I47" s="12" t="s">
         <v>14</v>
@@ -9450,7 +9711,7 @@
         <v>14</v>
       </c>
       <c r="L47" s="19" t="e">
-        <f t="shared" ref="L47:L50" si="7">IF(I47&gt;0,K47/I47,0)</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="M47" s="12" t="s">
@@ -9488,26 +9749,28 @@
     </row>
     <row r="48" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A48" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="B48" s="12"/>
+        <v>363</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C48" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F48" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G48" s="12">
         <v>10</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I48" s="12" t="s">
         <v>14</v>
@@ -9517,7 +9780,7 @@
         <v>14</v>
       </c>
       <c r="L48" s="19" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="M48" s="12" t="s">
@@ -9555,28 +9818,28 @@
     </row>
     <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A49" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F49" s="12">
         <v>500</v>
       </c>
       <c r="G49" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>14</v>
@@ -9586,7 +9849,7 @@
         <v>14</v>
       </c>
       <c r="L49" s="19" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="M49" s="12" t="s">
@@ -9622,141 +9885,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A50" s="12" t="s">
+    <row r="50" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A50" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="4">
+        <v>50</v>
+      </c>
+      <c r="G50" s="4">
+        <v>10</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15"/>
+      <c r="P50" s="15"/>
+      <c r="Q50" s="15"/>
+      <c r="R50" s="15"/>
+      <c r="S50" s="15"/>
+      <c r="T50" s="16"/>
+      <c r="U50" s="15"/>
+      <c r="V50" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+    </row>
+    <row r="51" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A51" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="B50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F50" s="12">
-        <v>500</v>
-      </c>
-      <c r="G50" s="12">
-        <v>500</v>
-      </c>
-      <c r="H50" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L50" s="19" t="e">
-        <f t="shared" si="7"/>
+      <c r="B51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F51" s="12">
+        <v>100</v>
+      </c>
+      <c r="G51" s="12">
+        <v>10</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" s="19" t="e">
+        <f t="shared" ref="L51:L54" si="7">IF(I51&gt;0,K51/I51,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O50" s="12"/>
-      <c r="P50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T50" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U50" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V50" s="12" t="s">
+      <c r="M51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O51" s="12"/>
+      <c r="P51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T51" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U51" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V51" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W50" s="12"/>
-      <c r="X50" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A51" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" s="4">
-        <v>50</v>
-      </c>
-      <c r="G51" s="4">
-        <v>10</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="15"/>
-      <c r="N51" s="15"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="15"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="15"/>
-      <c r="V51" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
+      <c r="W51" s="12"/>
+      <c r="X51" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A52" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="B52" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="B52" s="12"/>
       <c r="C52" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F52" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G52" s="12">
         <v>10</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>14</v>
@@ -9766,7 +10027,7 @@
         <v>14</v>
       </c>
       <c r="L52" s="19" t="e">
-        <f t="shared" ref="L52:L55" si="8">IF(I52&gt;0,K52/I52,0)</f>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="M52" s="12" t="s">
@@ -9804,26 +10065,28 @@
     </row>
     <row r="53" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A53" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="B53" s="12"/>
+        <v>369</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C53" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F53" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G53" s="12">
         <v>10</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>14</v>
@@ -9833,7 +10096,7 @@
         <v>14</v>
       </c>
       <c r="L53" s="19" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="M53" s="12" t="s">
@@ -9871,28 +10134,28 @@
     </row>
     <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A54" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F54" s="12">
         <v>500</v>
       </c>
       <c r="G54" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>14</v>
@@ -9902,7 +10165,7 @@
         <v>14</v>
       </c>
       <c r="L54" s="19" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="M54" s="12" t="s">
@@ -9938,909 +10201,870 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A55" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F55" s="12">
-        <v>500</v>
-      </c>
-      <c r="G55" s="12">
-        <v>500</v>
-      </c>
-      <c r="H55" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L55" s="19" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O55" s="12"/>
-      <c r="P55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T55" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V55" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W55" s="12"/>
-      <c r="X55" s="12" t="s">
-        <v>14</v>
-      </c>
+    <row r="55" ht="24" customHeight="1" spans="1:24">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+      <c r="T55" s="20"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="2"/>
+      <c r="X55" s="2"/>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:24">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="2"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="2"/>
-      <c r="T56" s="20"/>
-      <c r="U56" s="2"/>
-      <c r="V56" s="2"/>
-      <c r="W56" s="2"/>
-      <c r="X56" s="2"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="23"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="23"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:24">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="23"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="20"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
+      <c r="T57" s="20"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="2"/>
+      <c r="W57" s="2"/>
+      <c r="X57" s="2"/>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:24">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
-      <c r="T58" s="20"/>
-      <c r="U58" s="2"/>
-      <c r="V58" s="2"/>
-      <c r="W58" s="2"/>
-      <c r="X58" s="2"/>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="23"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="23"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:24">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="23"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="23"/>
-      <c r="U59" s="4"/>
-      <c r="V59" s="4"/>
-      <c r="W59" s="4"/>
-      <c r="X59" s="4"/>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="2"/>
+      <c r="T59" s="20"/>
+      <c r="U59" s="2"/>
+      <c r="V59" s="2"/>
+      <c r="W59" s="2"/>
+      <c r="X59" s="2"/>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:24">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="2"/>
-      <c r="T60" s="20"/>
-      <c r="U60" s="2"/>
-      <c r="V60" s="2"/>
-      <c r="W60" s="2"/>
-      <c r="X60" s="2"/>
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="23"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="23"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:24">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="23"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="23"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
-      <c r="X61" s="4"/>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="20"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
+      <c r="T61" s="20"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="2"/>
+      <c r="W61" s="2"/>
+      <c r="X61" s="2"/>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:24">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" s="2"/>
-      <c r="Q62" s="2"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="2"/>
-      <c r="T62" s="20"/>
-      <c r="U62" s="2"/>
-      <c r="V62" s="2"/>
-      <c r="W62" s="2"/>
-      <c r="X62" s="2"/>
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="23"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="23"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:24">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="23"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="23"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
-      <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="2"/>
+      <c r="X63" s="2"/>
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:24">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2"/>
-      <c r="Q64" s="2"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="2"/>
-      <c r="T64" s="20"/>
-      <c r="U64" s="2"/>
-      <c r="V64" s="2"/>
-      <c r="W64" s="2"/>
-      <c r="X64" s="2"/>
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="23"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="23"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:24">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="23"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="23"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2"/>
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:24">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="20"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
-      <c r="T66" s="20"/>
-      <c r="U66" s="2"/>
-      <c r="V66" s="2"/>
-      <c r="W66" s="2"/>
-      <c r="X66" s="2"/>
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="23"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="23"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:24">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="23"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="23"/>
-      <c r="U67" s="4"/>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="20"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
+      <c r="T67" s="20"/>
+      <c r="U67" s="2"/>
+      <c r="V67" s="2"/>
+      <c r="W67" s="2"/>
+      <c r="X67" s="2"/>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:24">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="20"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
-      <c r="T68" s="20"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="23"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:24">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="23"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="20"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
+      <c r="T69" s="20"/>
+      <c r="U69" s="2"/>
+      <c r="V69" s="2"/>
+      <c r="W69" s="2"/>
+      <c r="X69" s="2"/>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:24">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" s="20"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="2"/>
-      <c r="T70" s="20"/>
-      <c r="U70" s="2"/>
-      <c r="V70" s="2"/>
-      <c r="W70" s="2"/>
-      <c r="X70" s="2"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="23"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="23"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:24">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="23"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="23"/>
-      <c r="U71" s="4"/>
-      <c r="V71" s="4"/>
-      <c r="W71" s="4"/>
-      <c r="X71" s="4"/>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="20"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="20"/>
+      <c r="U71" s="2"/>
+      <c r="V71" s="2"/>
+      <c r="W71" s="2"/>
+      <c r="X71" s="2"/>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:24">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="20"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
-      <c r="T72" s="20"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="2"/>
-      <c r="W72" s="2"/>
-      <c r="X72" s="2"/>
-    </row>
-    <row r="73" ht="24" customHeight="1" spans="1:24">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="23"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="23"/>
-      <c r="U73" s="4"/>
-      <c r="V73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73" s="4"/>
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="23"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="23"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:U1"/>
   </mergeCells>
   <conditionalFormatting sqref="L9">
-    <cfRule type="cellIs" dxfId="0" priority="94" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="103" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9:O9">
-    <cfRule type="cellIs" dxfId="1" priority="95" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="104" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T9">
-    <cfRule type="cellIs" dxfId="1" priority="96" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="105" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10">
+    <cfRule type="cellIs" dxfId="0" priority="16" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N10:O10">
+    <cfRule type="cellIs" dxfId="1" priority="17" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T10">
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L11">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N11:O11">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T11">
+    <cfRule type="cellIs" dxfId="1" priority="15" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L12">
+    <cfRule type="cellIs" dxfId="0" priority="97" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N12:O12">
+    <cfRule type="cellIs" dxfId="1" priority="98" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T12">
+    <cfRule type="cellIs" dxfId="1" priority="99" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L17">
+    <cfRule type="cellIs" dxfId="0" priority="79" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N17:O17">
+    <cfRule type="cellIs" dxfId="1" priority="80" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T17">
+    <cfRule type="cellIs" dxfId="1" priority="81" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L18">
+    <cfRule type="cellIs" dxfId="0" priority="73" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N18:O18">
+    <cfRule type="cellIs" dxfId="1" priority="74" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T18">
+    <cfRule type="cellIs" dxfId="1" priority="75" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L19">
+    <cfRule type="cellIs" dxfId="0" priority="67" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19:O19">
+    <cfRule type="cellIs" dxfId="1" priority="68" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T19">
+    <cfRule type="cellIs" dxfId="1" priority="69" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20">
+    <cfRule type="cellIs" dxfId="0" priority="61" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N20:O20">
+    <cfRule type="cellIs" dxfId="1" priority="62" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T20">
+    <cfRule type="cellIs" dxfId="1" priority="63" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L21">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N21:O21">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T21">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L22">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N22:O22">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T22">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L23">
     <cfRule type="cellIs" dxfId="0" priority="7" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N10:O10">
+  <conditionalFormatting sqref="N23:O23">
     <cfRule type="cellIs" dxfId="1" priority="8" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T10">
+  <conditionalFormatting sqref="T23">
     <cfRule type="cellIs" dxfId="1" priority="9" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L11">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="L24">
+    <cfRule type="cellIs" dxfId="0" priority="55" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N11:O11">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThan">
+  <conditionalFormatting sqref="N24:O24">
+    <cfRule type="cellIs" dxfId="1" priority="56" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T11">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
+  <conditionalFormatting sqref="T24">
+    <cfRule type="cellIs" dxfId="1" priority="57" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L12">
-    <cfRule type="cellIs" dxfId="0" priority="88" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N12:O12">
-    <cfRule type="cellIs" dxfId="1" priority="89" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T12">
-    <cfRule type="cellIs" dxfId="1" priority="90" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L17">
-    <cfRule type="cellIs" dxfId="0" priority="70" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N17:O17">
-    <cfRule type="cellIs" dxfId="1" priority="71" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T17">
-    <cfRule type="cellIs" dxfId="1" priority="72" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L18">
-    <cfRule type="cellIs" dxfId="0" priority="64" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N18:O18">
-    <cfRule type="cellIs" dxfId="1" priority="65" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T18">
-    <cfRule type="cellIs" dxfId="1" priority="66" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="0" priority="58" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N19:O19">
-    <cfRule type="cellIs" dxfId="1" priority="59" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T19">
-    <cfRule type="cellIs" dxfId="1" priority="60" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
+  <conditionalFormatting sqref="L25">
     <cfRule type="cellIs" dxfId="0" priority="52" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N20:O20">
+  <conditionalFormatting sqref="N25:O25">
     <cfRule type="cellIs" dxfId="1" priority="53" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T20">
+  <conditionalFormatting sqref="T25">
     <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L21">
+  <conditionalFormatting sqref="L30">
+    <cfRule type="cellIs" dxfId="0" priority="46" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N30:O30">
+    <cfRule type="cellIs" dxfId="1" priority="47" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T30">
+    <cfRule type="cellIs" dxfId="1" priority="48" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L35">
+    <cfRule type="cellIs" dxfId="0" priority="40" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N35:O35">
+    <cfRule type="cellIs" dxfId="1" priority="41" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T35">
+    <cfRule type="cellIs" dxfId="1" priority="42" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L40">
+    <cfRule type="cellIs" dxfId="0" priority="34" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N40:O40">
+    <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T40">
+    <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L45">
+    <cfRule type="cellIs" dxfId="0" priority="28" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N45:O45">
+    <cfRule type="cellIs" dxfId="1" priority="29" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T45">
+    <cfRule type="cellIs" dxfId="1" priority="30" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L50">
+    <cfRule type="cellIs" dxfId="0" priority="22" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N50:O50">
+    <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T50">
+    <cfRule type="cellIs" dxfId="1" priority="24" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L13:L16">
+    <cfRule type="cellIs" dxfId="0" priority="91" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L26:L29">
     <cfRule type="cellIs" dxfId="0" priority="49" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N21:O21">
+  <conditionalFormatting sqref="L31:L34">
+    <cfRule type="cellIs" dxfId="0" priority="43" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L36:L39">
+    <cfRule type="cellIs" dxfId="0" priority="37" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L41:L44">
+    <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L46:L49">
+    <cfRule type="cellIs" dxfId="0" priority="25" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L51:L54">
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T13:T16">
+    <cfRule type="cellIs" dxfId="1" priority="93" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T26:T29">
+    <cfRule type="cellIs" dxfId="1" priority="51" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T31:T34">
+    <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T36:T39">
+    <cfRule type="cellIs" dxfId="1" priority="39" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T41:T44">
+    <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T46:T49">
+    <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T51:T54">
+    <cfRule type="cellIs" dxfId="1" priority="21" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L4:L8 L55:L72">
+    <cfRule type="cellIs" dxfId="0" priority="106" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:O8 N55:O72">
+    <cfRule type="cellIs" dxfId="1" priority="107" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T4:T8 T55:T72">
+    <cfRule type="cellIs" dxfId="1" priority="108" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13:O16">
+    <cfRule type="cellIs" dxfId="1" priority="92" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N26:O29">
     <cfRule type="cellIs" dxfId="1" priority="50" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T21">
-    <cfRule type="cellIs" dxfId="1" priority="51" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L26">
-    <cfRule type="cellIs" dxfId="0" priority="43" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N26:O26">
+  <conditionalFormatting sqref="N31:O34">
     <cfRule type="cellIs" dxfId="1" priority="44" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T26">
-    <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L31">
-    <cfRule type="cellIs" dxfId="0" priority="37" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N31:O31">
+  <conditionalFormatting sqref="N36:O39">
     <cfRule type="cellIs" dxfId="1" priority="38" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T31">
-    <cfRule type="cellIs" dxfId="1" priority="39" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L36">
-    <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N36:O36">
+  <conditionalFormatting sqref="N41:O44">
     <cfRule type="cellIs" dxfId="1" priority="32" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T36">
-    <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L41">
-    <cfRule type="cellIs" dxfId="0" priority="25" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N41:O41">
+  <conditionalFormatting sqref="N46:O49">
     <cfRule type="cellIs" dxfId="1" priority="26" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T41">
-    <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L46">
-    <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N46:O46">
+  <conditionalFormatting sqref="N51:O54">
     <cfRule type="cellIs" dxfId="1" priority="20" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T46">
-    <cfRule type="cellIs" dxfId="1" priority="21" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L51">
-    <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N51:O51">
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T51">
-    <cfRule type="cellIs" dxfId="1" priority="15" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L13:L16">
-    <cfRule type="cellIs" dxfId="0" priority="82" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L22:L25">
-    <cfRule type="cellIs" dxfId="0" priority="46" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L27:L30">
-    <cfRule type="cellIs" dxfId="0" priority="40" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L32:L35">
-    <cfRule type="cellIs" dxfId="0" priority="34" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L37:L40">
-    <cfRule type="cellIs" dxfId="0" priority="28" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L42:L45">
-    <cfRule type="cellIs" dxfId="0" priority="22" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L47:L50">
-    <cfRule type="cellIs" dxfId="0" priority="16" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L52:L55">
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T13:T16">
-    <cfRule type="cellIs" dxfId="1" priority="84" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T22:T25">
-    <cfRule type="cellIs" dxfId="1" priority="48" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T27:T30">
-    <cfRule type="cellIs" dxfId="1" priority="42" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T32:T35">
-    <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T37:T40">
-    <cfRule type="cellIs" dxfId="1" priority="30" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T42:T45">
-    <cfRule type="cellIs" dxfId="1" priority="24" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T47:T50">
-    <cfRule type="cellIs" dxfId="1" priority="18" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T52:T55">
-    <cfRule type="cellIs" dxfId="1" priority="12" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L8 L56:L73">
-    <cfRule type="cellIs" dxfId="0" priority="97" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O8 N56:O73">
-    <cfRule type="cellIs" dxfId="1" priority="98" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T4:T8 T56:T73">
-    <cfRule type="cellIs" dxfId="1" priority="99" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:O16">
-    <cfRule type="cellIs" dxfId="1" priority="83" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22:O25">
-    <cfRule type="cellIs" dxfId="1" priority="47" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N27:O30">
-    <cfRule type="cellIs" dxfId="1" priority="41" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N32:O35">
-    <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N37:O40">
-    <cfRule type="cellIs" dxfId="1" priority="29" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N42:O45">
-    <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N47:O50">
-    <cfRule type="cellIs" dxfId="1" priority="17" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N52:O55">
-    <cfRule type="cellIs" dxfId="1" priority="11" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="V4:V19 V20:V73">
+    <dataValidation type="list" allowBlank="1" sqref="V11 V18 V21 V22 V23 V4:V10 V12:V17 V19:V20 V24:V72">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10870,7 +11094,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10">
@@ -10890,16 +11114,16 @@
         <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>182</v>
@@ -10908,7 +11132,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>36</v>
@@ -10922,19 +11146,19 @@
         <v>280</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>14</v>
@@ -10951,22 +11175,22 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -10983,22 +11207,22 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -11021,16 +11245,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -11071,10 +11295,10 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11090,25 +11314,25 @@
         <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>396</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>398</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>7</v>
@@ -11119,31 +11343,31 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="G12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>406</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>14</v>
@@ -11151,22 +11375,22 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -11183,23 +11407,23 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>416</v>
-      </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
       </c>
@@ -11207,7 +11431,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>14</v>
@@ -11215,22 +11439,22 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>

--- a/performance_test_business_optimized.xlsx
+++ b/performance_test_business_optimized.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="419">
   <si>
     <t>压力测试业务总览</t>
   </si>
@@ -1067,6 +1067,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1.在长达 13 分钟的压力测试中，系统平均每秒处理了 645个请求，不具有报错。
 2.小程序有一点卡顿等情况。
 </t>
@@ -1103,7 +1109,8 @@
     <t>R40</t>
   </si>
   <si>
-    <t>W11</t>
+    <t>1.在长达 10 分钟的压力测试中，系统平均每秒处理了 2.8个请求，不具有报错。
+2.小程序整体未有卡顿情况，图册页超时展示</t>
   </si>
   <si>
     <t>R41</t>
@@ -4733,6 +4740,258 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>235585</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>236220</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>909320</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>698500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="图片 58"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30026610" y="40673020"/>
+          <a:ext cx="673735" cy="462280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1297940</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>279400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2187575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>940435</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="图片 59"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31088965" y="40716200"/>
+          <a:ext cx="889635" cy="661035"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>596265</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1480185</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1332230</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2021840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="图片 60"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30387290" y="41916985"/>
+          <a:ext cx="735965" cy="541655"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1755140</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1346200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2569210</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1932940</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="图片 61"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31546165" y="41783000"/>
+          <a:ext cx="814070" cy="586740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>978535</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>960120</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1332865</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="图片 62"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30047565" y="41415335"/>
+          <a:ext cx="703580" cy="354330"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>938530</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>985520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2050415</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1409065</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="图片 63"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30729555" y="41422320"/>
+          <a:ext cx="1111885" cy="423545"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6692,7 +6951,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7488,7 +7747,7 @@
         <v>14</v>
       </c>
       <c r="L13" s="19" t="e">
-        <f t="shared" ref="L13:L21" si="1">IF(I13&gt;0,K13/I13,0)</f>
+        <f t="shared" ref="L13:L24" si="1">IF(I13&gt;0,K13/I13,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M13" s="12" t="s">
@@ -8029,7 +8288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+    <row r="21" s="9" customFormat="1" ht="185" customHeight="1" spans="1:24">
       <c r="A21" s="12" t="s">
         <v>333</v>
       </c>
@@ -8046,7 +8305,7 @@
         <v>303</v>
       </c>
       <c r="F21" s="12">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G21" s="12">
         <v>10</v>
@@ -8054,46 +8313,52 @@
       <c r="H21" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" s="19" t="e">
+      <c r="I21" s="12">
+        <v>1610</v>
+      </c>
+      <c r="J21" s="12">
+        <v>1610</v>
+      </c>
+      <c r="K21" s="12">
+        <v>0</v>
+      </c>
+      <c r="L21" s="19">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="12" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="M21" s="12">
+        <v>35815.54</v>
+      </c>
+      <c r="N21" s="12">
+        <v>64000</v>
+      </c>
+      <c r="O21" s="12">
+        <v>2.68</v>
+      </c>
+      <c r="P21" s="12">
+        <v>2.8</v>
+      </c>
+      <c r="Q21" s="12">
+        <v>19</v>
       </c>
       <c r="R21" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T21" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>14</v>
+      <c r="S21" s="12">
+        <v>1.74</v>
+      </c>
+      <c r="T21" s="19">
+        <v>0.06</v>
+      </c>
+      <c r="U21" s="12">
+        <v>123</v>
       </c>
       <c r="V21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W21" s="12"/>
+      <c r="W21" s="27" t="s">
+        <v>334</v>
+      </c>
       <c r="X21" s="12" t="s">
         <v>14</v>
       </c>
@@ -8131,7 +8396,7 @@
         <v>14</v>
       </c>
       <c r="L22" s="19" t="e">
-        <f>IF(I22&gt;0,K22/I22,0)</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="M22" s="12" t="s">
@@ -8200,7 +8465,7 @@
         <v>14</v>
       </c>
       <c r="L23" s="19" t="e">
-        <f>IF(I23&gt;0,K23/I23,0)</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="M23" s="12" t="s">
@@ -8269,7 +8534,7 @@
         <v>14</v>
       </c>
       <c r="L24" s="19" t="e">
-        <f>IF(I24&gt;0,K24/I24,0)</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="M24" s="12" t="s">
@@ -8305,55 +8570,80 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A25" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F25" s="4">
-        <v>50</v>
-      </c>
-      <c r="G25" s="4">
+    <row r="25" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A25" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25" s="12">
+        <v>100</v>
+      </c>
+      <c r="G25" s="12">
         <v>10</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
+      <c r="H25" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="25"/>
+      <c r="K25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" s="19" t="e">
+        <f t="shared" ref="L25:L28" si="2">IF(I25&gt;0,K25/I25,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T25" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="26" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A26" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="B26" s="12"/>
       <c r="C26" s="12" t="s">
         <v>336</v>
       </c>
@@ -8361,16 +8651,16 @@
         <v>337</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F26" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G26" s="12">
         <v>10</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>14</v>
@@ -8380,7 +8670,7 @@
         <v>14</v>
       </c>
       <c r="L26" s="19" t="e">
-        <f t="shared" ref="L26:L29" si="2">IF(I26&gt;0,K26/I26,0)</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="M26" s="12" t="s">
@@ -8418,9 +8708,11 @@
     </row>
     <row r="27" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A27" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="B27" s="12"/>
+        <v>339</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C27" s="12" t="s">
         <v>336</v>
       </c>
@@ -8428,16 +8720,16 @@
         <v>337</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F27" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G27" s="12">
         <v>10</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I27" s="12" t="s">
         <v>14</v>
@@ -8485,28 +8777,28 @@
     </row>
     <row r="28" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A28" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>337</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F28" s="12">
         <v>500</v>
       </c>
       <c r="G28" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>14</v>
@@ -8552,124 +8844,122 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A29" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F29" s="12">
-        <v>500</v>
-      </c>
-      <c r="G29" s="12">
-        <v>500</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="25"/>
-      <c r="K29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="19" t="e">
-        <f t="shared" si="2"/>
+    <row r="29" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A29" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="4">
+        <v>50</v>
+      </c>
+      <c r="G29" s="4">
+        <v>10</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+    </row>
+    <row r="30" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A30" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="12">
+        <v>100</v>
+      </c>
+      <c r="G30" s="12">
+        <v>10</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="25"/>
+      <c r="K30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30" s="19" t="e">
+        <f t="shared" ref="L30:L33" si="3">IF(I30&gt;0,K30/I30,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T29" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V29" s="12" t="s">
+      <c r="M30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T30" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U30" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V30" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A30" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F30" s="4">
-        <v>50</v>
-      </c>
-      <c r="G30" s="4">
-        <v>10</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="15"/>
-      <c r="S30" s="15"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="31" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A31" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="B31" s="12"/>
       <c r="C31" s="12" t="s">
         <v>336</v>
       </c>
@@ -8677,16 +8967,16 @@
         <v>344</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F31" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G31" s="12">
         <v>10</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I31" s="12" t="s">
         <v>14</v>
@@ -8696,7 +8986,7 @@
         <v>14</v>
       </c>
       <c r="L31" s="19" t="e">
-        <f t="shared" ref="L31:L34" si="3">IF(I31&gt;0,K31/I31,0)</f>
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="M31" s="12" t="s">
@@ -8734,9 +9024,11 @@
     </row>
     <row r="32" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A32" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="B32" s="12"/>
+        <v>346</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C32" s="12" t="s">
         <v>336</v>
       </c>
@@ -8744,16 +9036,16 @@
         <v>344</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F32" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G32" s="12">
         <v>10</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I32" s="12" t="s">
         <v>14</v>
@@ -8801,28 +9093,28 @@
     </row>
     <row r="33" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A33" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>344</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F33" s="12">
         <v>500</v>
       </c>
       <c r="G33" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I33" s="12" t="s">
         <v>14</v>
@@ -8868,124 +9160,122 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A34" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F34" s="12">
-        <v>500</v>
-      </c>
-      <c r="G34" s="12">
-        <v>500</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="25"/>
-      <c r="K34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L34" s="19" t="e">
-        <f t="shared" si="3"/>
+    <row r="34" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="4">
+        <v>50</v>
+      </c>
+      <c r="G34" s="4">
+        <v>10</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W34" s="4"/>
+      <c r="X34" s="4"/>
+    </row>
+    <row r="35" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A35" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="12">
+        <v>100</v>
+      </c>
+      <c r="G35" s="12">
+        <v>10</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="25"/>
+      <c r="K35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="19" t="e">
+        <f t="shared" ref="L35:L38" si="4">IF(I35&gt;0,K35/I35,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T34" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V34" s="12" t="s">
+      <c r="M35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T35" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U35" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V35" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W34" s="12"/>
-      <c r="X34" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A35" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F35" s="4">
-        <v>50</v>
-      </c>
-      <c r="G35" s="4">
-        <v>10</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="15"/>
-      <c r="S35" s="15"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="15"/>
-      <c r="V35" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="36" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A36" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="B36" s="12"/>
       <c r="C36" s="12" t="s">
         <v>336</v>
       </c>
@@ -8993,16 +9283,16 @@
         <v>350</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F36" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G36" s="12">
         <v>10</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>14</v>
@@ -9012,7 +9302,7 @@
         <v>14</v>
       </c>
       <c r="L36" s="19" t="e">
-        <f t="shared" ref="L36:L39" si="4">IF(I36&gt;0,K36/I36,0)</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="M36" s="12" t="s">
@@ -9050,9 +9340,11 @@
     </row>
     <row r="37" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A37" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="B37" s="12"/>
+        <v>352</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C37" s="12" t="s">
         <v>336</v>
       </c>
@@ -9060,16 +9352,16 @@
         <v>350</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F37" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G37" s="12">
         <v>10</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I37" s="12" t="s">
         <v>14</v>
@@ -9117,28 +9409,28 @@
     </row>
     <row r="38" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A38" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>350</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F38" s="12">
         <v>500</v>
       </c>
       <c r="G38" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I38" s="12" t="s">
         <v>14</v>
@@ -9184,124 +9476,122 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A39" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="D39" s="12" t="s">
+    <row r="39" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A39" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" s="4">
+        <v>50</v>
+      </c>
+      <c r="G39" s="4">
+        <v>10</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="16"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+    </row>
+    <row r="40" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A40" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="E39" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F39" s="12">
-        <v>500</v>
-      </c>
-      <c r="G39" s="12">
-        <v>500</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" s="25"/>
-      <c r="K39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L39" s="19" t="e">
-        <f t="shared" si="4"/>
+      <c r="E40" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" s="12">
+        <v>100</v>
+      </c>
+      <c r="G40" s="12">
+        <v>10</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="25"/>
+      <c r="K40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" s="19" t="e">
+        <f t="shared" ref="L40:L43" si="5">IF(I40&gt;0,K40/I40,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O39" s="12"/>
-      <c r="P39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T39" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V39" s="12" t="s">
+      <c r="M40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T40" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U40" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V40" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A40" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F40" s="4">
-        <v>50</v>
-      </c>
-      <c r="G40" s="4">
-        <v>10</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="15"/>
-      <c r="S40" s="15"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="15"/>
-      <c r="V40" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="41" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A41" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="B41" s="12"/>
       <c r="C41" s="12" t="s">
         <v>336</v>
       </c>
@@ -9309,16 +9599,16 @@
         <v>350</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F41" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G41" s="12">
         <v>10</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I41" s="12" t="s">
         <v>14</v>
@@ -9328,7 +9618,7 @@
         <v>14</v>
       </c>
       <c r="L41" s="19" t="e">
-        <f t="shared" ref="L41:L44" si="5">IF(I41&gt;0,K41/I41,0)</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="M41" s="12" t="s">
@@ -9366,9 +9656,11 @@
     </row>
     <row r="42" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A42" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="B42" s="12"/>
+        <v>357</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C42" s="12" t="s">
         <v>336</v>
       </c>
@@ -9376,16 +9668,16 @@
         <v>350</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F42" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G42" s="12">
         <v>10</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I42" s="12" t="s">
         <v>14</v>
@@ -9433,28 +9725,28 @@
     </row>
     <row r="43" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A43" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>350</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F43" s="12">
         <v>500</v>
       </c>
       <c r="G43" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I43" s="12" t="s">
         <v>14</v>
@@ -9500,124 +9792,122 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A44" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F44" s="12">
-        <v>500</v>
-      </c>
-      <c r="G44" s="12">
-        <v>500</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J44" s="25"/>
-      <c r="K44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L44" s="19" t="e">
-        <f t="shared" si="5"/>
+    <row r="44" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A44" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44" s="4">
+        <v>50</v>
+      </c>
+      <c r="G44" s="4">
+        <v>10</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15"/>
+      <c r="R44" s="15"/>
+      <c r="S44" s="15"/>
+      <c r="T44" s="16"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+    </row>
+    <row r="45" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A45" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F45" s="12">
+        <v>100</v>
+      </c>
+      <c r="G45" s="12">
+        <v>10</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L45" s="19" t="e">
+        <f t="shared" ref="L45:L48" si="6">IF(I45&gt;0,K45/I45,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O44" s="12"/>
-      <c r="P44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T44" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U44" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V44" s="12" t="s">
+      <c r="M45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O45" s="12"/>
+      <c r="P45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T45" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U45" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V45" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W44" s="12"/>
-      <c r="X44" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A45" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F45" s="4">
-        <v>50</v>
-      </c>
-      <c r="G45" s="4">
-        <v>10</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="15"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="15"/>
-      <c r="R45" s="15"/>
-      <c r="S45" s="15"/>
-      <c r="T45" s="16"/>
-      <c r="U45" s="15"/>
-      <c r="V45" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W45" s="4"/>
-      <c r="X45" s="4"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="46" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A46" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="B46" s="12"/>
       <c r="C46" s="12" t="s">
         <v>336</v>
       </c>
@@ -9625,16 +9915,16 @@
         <v>361</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F46" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G46" s="12">
         <v>10</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I46" s="12" t="s">
         <v>14</v>
@@ -9644,7 +9934,7 @@
         <v>14</v>
       </c>
       <c r="L46" s="19" t="e">
-        <f t="shared" ref="L46:L49" si="6">IF(I46&gt;0,K46/I46,0)</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="M46" s="12" t="s">
@@ -9682,9 +9972,11 @@
     </row>
     <row r="47" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A47" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="B47" s="12"/>
+        <v>363</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C47" s="12" t="s">
         <v>336</v>
       </c>
@@ -9692,16 +9984,16 @@
         <v>361</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F47" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G47" s="12">
         <v>10</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I47" s="12" t="s">
         <v>14</v>
@@ -9749,28 +10041,28 @@
     </row>
     <row r="48" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A48" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D48" s="12" t="s">
         <v>361</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F48" s="12">
         <v>500</v>
       </c>
       <c r="G48" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I48" s="12" t="s">
         <v>14</v>
@@ -9816,124 +10108,122 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A49" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F49" s="12">
-        <v>500</v>
-      </c>
-      <c r="G49" s="12">
-        <v>500</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L49" s="19" t="e">
-        <f t="shared" si="6"/>
+    <row r="49" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A49" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="4">
+        <v>50</v>
+      </c>
+      <c r="G49" s="4">
+        <v>10</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="15"/>
+      <c r="R49" s="15"/>
+      <c r="S49" s="15"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="15"/>
+      <c r="V49" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+    </row>
+    <row r="50" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
+      <c r="A50" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F50" s="12">
+        <v>100</v>
+      </c>
+      <c r="G50" s="12">
+        <v>10</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L50" s="19" t="e">
+        <f t="shared" ref="L50:L53" si="7">IF(I50&gt;0,K50/I50,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O49" s="12"/>
-      <c r="P49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T49" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U49" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V49" s="12" t="s">
+      <c r="M50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O50" s="12"/>
+      <c r="P50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T50" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V50" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W49" s="12"/>
-      <c r="X49" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A50" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F50" s="4">
-        <v>50</v>
-      </c>
-      <c r="G50" s="4">
-        <v>10</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="15"/>
-      <c r="N50" s="15"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="15"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="15"/>
-      <c r="T50" s="16"/>
-      <c r="U50" s="15"/>
-      <c r="V50" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
+      <c r="W50" s="12"/>
+      <c r="X50" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="51" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A51" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>14</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="B51" s="12"/>
       <c r="C51" s="12" t="s">
         <v>336</v>
       </c>
@@ -9941,16 +10231,16 @@
         <v>367</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F51" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G51" s="12">
         <v>10</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>14</v>
@@ -9960,7 +10250,7 @@
         <v>14</v>
       </c>
       <c r="L51" s="19" t="e">
-        <f t="shared" ref="L51:L54" si="7">IF(I51&gt;0,K51/I51,0)</f>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="M51" s="12" t="s">
@@ -9998,9 +10288,11 @@
     </row>
     <row r="52" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A52" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="B52" s="12"/>
+        <v>369</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="C52" s="12" t="s">
         <v>336</v>
       </c>
@@ -10008,16 +10300,16 @@
         <v>367</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F52" s="12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G52" s="12">
         <v>10</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>14</v>
@@ -10065,28 +10357,28 @@
     </row>
     <row r="53" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
       <c r="A53" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>367</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F53" s="12">
         <v>500</v>
       </c>
       <c r="G53" s="12">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>14</v>
@@ -10132,542 +10424,473 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" s="9" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A54" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F54" s="12">
-        <v>500</v>
-      </c>
-      <c r="G54" s="12">
-        <v>500</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L54" s="19" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O54" s="12"/>
-      <c r="P54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T54" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="U54" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V54" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="W54" s="12"/>
-      <c r="X54" s="12" t="s">
-        <v>14</v>
-      </c>
+    <row r="54" ht="24" customHeight="1" spans="1:24">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="20"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:24">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="2"/>
-      <c r="T55" s="20"/>
-      <c r="U55" s="2"/>
-      <c r="V55" s="2"/>
-      <c r="W55" s="2"/>
-      <c r="X55" s="2"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="23"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="23"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:24">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="23"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="23"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="20"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:24">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="2"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="2"/>
-      <c r="T57" s="20"/>
-      <c r="U57" s="2"/>
-      <c r="V57" s="2"/>
-      <c r="W57" s="2"/>
-      <c r="X57" s="2"/>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="23"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="23"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:24">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="23"/>
-      <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
-      <c r="W58" s="4"/>
-      <c r="X58" s="4"/>
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+      <c r="T58" s="20"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="2"/>
+      <c r="W58" s="2"/>
+      <c r="X58" s="2"/>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:24">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
-      <c r="T59" s="20"/>
-      <c r="U59" s="2"/>
-      <c r="V59" s="2"/>
-      <c r="W59" s="2"/>
-      <c r="X59" s="2"/>
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="23"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="23"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:24">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="23"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="23"/>
-      <c r="U60" s="4"/>
-      <c r="V60" s="4"/>
-      <c r="W60" s="4"/>
-      <c r="X60" s="4"/>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="20"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2"/>
+      <c r="W60" s="2"/>
+      <c r="X60" s="2"/>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:24">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="L61" s="20"/>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" s="2"/>
-      <c r="Q61" s="2"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="2"/>
-      <c r="T61" s="20"/>
-      <c r="U61" s="2"/>
-      <c r="V61" s="2"/>
-      <c r="W61" s="2"/>
-      <c r="X61" s="2"/>
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="23"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="23"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:24">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="23"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="23"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="4"/>
-      <c r="X62" s="4"/>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="20"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2"/>
+      <c r="W62" s="2"/>
+      <c r="X62" s="2"/>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:24">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-      <c r="T63" s="20"/>
-      <c r="U63" s="2"/>
-      <c r="V63" s="2"/>
-      <c r="W63" s="2"/>
-      <c r="X63" s="2"/>
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="23"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="23"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:24">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="4"/>
-      <c r="V64" s="4"/>
-      <c r="W64" s="4"/>
-      <c r="X64" s="4"/>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="20"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="2"/>
+      <c r="X64" s="2"/>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:24">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="2"/>
-      <c r="T65" s="20"/>
-      <c r="U65" s="2"/>
-      <c r="V65" s="2"/>
-      <c r="W65" s="2"/>
-      <c r="X65" s="2"/>
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="23"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="23"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:24">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="23"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="23"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+      <c r="T66" s="20"/>
+      <c r="U66" s="2"/>
+      <c r="V66" s="2"/>
+      <c r="W66" s="2"/>
+      <c r="X66" s="2"/>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:24">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="20"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
-      <c r="T67" s="20"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="23"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="23"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:24">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="23"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="23"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="20"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="20"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:24">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="20"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="2"/>
-      <c r="T69" s="20"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="2"/>
-      <c r="W69" s="2"/>
-      <c r="X69" s="2"/>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="23"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="23"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:24">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="23"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="23"/>
-      <c r="U70" s="4"/>
-      <c r="V70" s="4"/>
-      <c r="W70" s="4"/>
-      <c r="X70" s="4"/>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="20"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:24">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="20"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
-      <c r="T71" s="20"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="2"/>
-      <c r="W71" s="2"/>
-      <c r="X71" s="2"/>
-    </row>
-    <row r="72" ht="24" customHeight="1" spans="1:24">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="23"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="23"/>
-      <c r="U72" s="4"/>
-      <c r="V72" s="4"/>
-      <c r="W72" s="4"/>
-      <c r="X72" s="4"/>
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="23"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10853,92 +11076,77 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L25">
-    <cfRule type="cellIs" dxfId="0" priority="52" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N25:O25">
-    <cfRule type="cellIs" dxfId="1" priority="53" operator="greaterThan">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T25">
-    <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L30">
+  <conditionalFormatting sqref="L29">
     <cfRule type="cellIs" dxfId="0" priority="46" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N30:O30">
+  <conditionalFormatting sqref="N29:O29">
     <cfRule type="cellIs" dxfId="1" priority="47" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T30">
+  <conditionalFormatting sqref="T29">
     <cfRule type="cellIs" dxfId="1" priority="48" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L35">
+  <conditionalFormatting sqref="L34">
     <cfRule type="cellIs" dxfId="0" priority="40" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N35:O35">
+  <conditionalFormatting sqref="N34:O34">
     <cfRule type="cellIs" dxfId="1" priority="41" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T35">
+  <conditionalFormatting sqref="T34">
     <cfRule type="cellIs" dxfId="1" priority="42" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L40">
+  <conditionalFormatting sqref="L39">
     <cfRule type="cellIs" dxfId="0" priority="34" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N40:O40">
+  <conditionalFormatting sqref="N39:O39">
     <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T40">
+  <conditionalFormatting sqref="T39">
     <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L45">
+  <conditionalFormatting sqref="L44">
     <cfRule type="cellIs" dxfId="0" priority="28" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N45:O45">
+  <conditionalFormatting sqref="N44:O44">
     <cfRule type="cellIs" dxfId="1" priority="29" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T45">
+  <conditionalFormatting sqref="T44">
     <cfRule type="cellIs" dxfId="1" priority="30" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L50">
+  <conditionalFormatting sqref="L49">
     <cfRule type="cellIs" dxfId="0" priority="22" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N50:O50">
+  <conditionalFormatting sqref="N49:O49">
     <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T50">
+  <conditionalFormatting sqref="T49">
     <cfRule type="cellIs" dxfId="1" priority="24" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -10948,32 +11156,32 @@
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L26:L29">
+  <conditionalFormatting sqref="L25:L28">
     <cfRule type="cellIs" dxfId="0" priority="49" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L31:L34">
+  <conditionalFormatting sqref="L30:L33">
     <cfRule type="cellIs" dxfId="0" priority="43" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L36:L39">
+  <conditionalFormatting sqref="L35:L38">
     <cfRule type="cellIs" dxfId="0" priority="37" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L41:L44">
+  <conditionalFormatting sqref="L40:L43">
     <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L46:L49">
+  <conditionalFormatting sqref="L45:L48">
     <cfRule type="cellIs" dxfId="0" priority="25" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L51:L54">
+  <conditionalFormatting sqref="L50:L53">
     <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
@@ -10983,47 +11191,47 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T26:T29">
+  <conditionalFormatting sqref="T25:T28">
     <cfRule type="cellIs" dxfId="1" priority="51" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T31:T34">
+  <conditionalFormatting sqref="T30:T33">
     <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T36:T39">
+  <conditionalFormatting sqref="T35:T38">
     <cfRule type="cellIs" dxfId="1" priority="39" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T41:T44">
+  <conditionalFormatting sqref="T40:T43">
     <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T46:T49">
+  <conditionalFormatting sqref="T45:T48">
     <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T51:T54">
+  <conditionalFormatting sqref="T50:T53">
     <cfRule type="cellIs" dxfId="1" priority="21" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L8 L55:L72">
+  <conditionalFormatting sqref="L4:L8 L54:L71">
     <cfRule type="cellIs" dxfId="0" priority="106" operator="greaterThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O8 N55:O72">
+  <conditionalFormatting sqref="N4:O8 N54:O71">
     <cfRule type="cellIs" dxfId="1" priority="107" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T4:T8 T55:T72">
+  <conditionalFormatting sqref="T4:T8 T54:T71">
     <cfRule type="cellIs" dxfId="1" priority="108" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -11033,38 +11241,38 @@
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N26:O29">
+  <conditionalFormatting sqref="N25:O28">
     <cfRule type="cellIs" dxfId="1" priority="50" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N31:O34">
+  <conditionalFormatting sqref="N30:O33">
     <cfRule type="cellIs" dxfId="1" priority="44" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N36:O39">
+  <conditionalFormatting sqref="N35:O38">
     <cfRule type="cellIs" dxfId="1" priority="38" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N41:O44">
+  <conditionalFormatting sqref="N40:O43">
     <cfRule type="cellIs" dxfId="1" priority="32" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N46:O49">
+  <conditionalFormatting sqref="N45:O48">
     <cfRule type="cellIs" dxfId="1" priority="26" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N51:O54">
+  <conditionalFormatting sqref="N50:O53">
     <cfRule type="cellIs" dxfId="1" priority="20" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="V11 V18 V21 V22 V23 V4:V10 V12:V17 V19:V20 V24:V72">
+    <dataValidation type="list" allowBlank="1" sqref="V4:V24 V25:V71">
       <formula1>"待测试,通过,有条件通过,不通过,不入报告"</formula1>
     </dataValidation>
   </dataValidations>
